--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Isadora/Documents/GitHub/rehearsal-schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55F4E39-DC3A-124E-9CA8-78FB76005A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21290AE-2EB6-B247-A970-595850BD930E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4120" yWindow="920" windowWidth="27240" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4120" yWindow="780" windowWidth="27240" windowHeight="20420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="classes" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3319" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3320" uniqueCount="325">
   <si>
     <t>class_name</t>
   </si>
@@ -880,9 +880,6 @@
     <t>Black leotard.</t>
   </si>
   <si>
-    <t>Red sequin flapper dress and footed tights.</t>
-  </si>
-  <si>
     <t>Tap shoes.</t>
   </si>
   <si>
@@ -917,9 +914,6 @@
   </si>
   <si>
     <t>Pale blue sequin dress OR white turtleneck, black tights, pale blue cumberbund.</t>
-  </si>
-  <si>
-    <t>Dark rose dress, and white leotard mesh skirt OR maroon button down and white button down and white pants.</t>
   </si>
   <si>
     <t>Black cropped long sleeve and purple sweatpants.</t>
@@ -964,19 +958,7 @@
     <t>Bright colored blazer.</t>
   </si>
   <si>
-    <t>Black tank top or leotard and wide leg pants. Black jazz shoes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black tank top and black blazer. </t>
-  </si>
-  <si>
-    <t>Black wide leg pants. Tap shoes.</t>
-  </si>
-  <si>
     <t>Black country top OR red country top. Black cowboy hat.</t>
-  </si>
-  <si>
-    <t>Dark blue jeans and a black or brown belt. Tap shoes.</t>
   </si>
   <si>
     <t>Pale green dress and ballet tights OR pale green sequin vest.</t>
@@ -985,20 +967,59 @@
     <t>For vest: black pants. Ballet tights and ballet shoes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Maroon mesh top and skirt. </t>
-  </si>
-  <si>
     <t>Black leotard and shorts.</t>
   </si>
   <si>
     <t>Yellow sequin dress and black tights OR white button down with a silver sequin vest and black pants.</t>
+  </si>
+  <si>
+    <t>Dark rose dress baby doll dress OR rose button down with white pants. White leotard with mesh skirt OR white button down and white pants.</t>
+  </si>
+  <si>
+    <t>Beige/skin-toned leotard or fitted tank.</t>
+  </si>
+  <si>
+    <t>Black/white/gray Accessories, tank top/leo if applicable. Hip hop sneakers.</t>
+  </si>
+  <si>
+    <t>Blakc socks and hip hop sneakers.</t>
+  </si>
+  <si>
+    <t>Black jazz shoes. Tan bra or leotard if needed. Black socks if needed.</t>
+  </si>
+  <si>
+    <t>Black tank top or leotard and wide leg pants. Black jazz shoes. Black socks if needed.</t>
+  </si>
+  <si>
+    <t>Nude leotard or bra with black spandex shorts. Black jazz shoes.</t>
+  </si>
+  <si>
+    <t>Black socks and tap shoes.</t>
+  </si>
+  <si>
+    <t>Red sequin flapper dress and footed tights. Headband.</t>
+  </si>
+  <si>
+    <t>Tan bra or leotard if needed. Tap shoes.</t>
+  </si>
+  <si>
+    <t>Black tank top and black blazer.</t>
+  </si>
+  <si>
+    <t>Black wide leg pants. Black socks and tap shoes.</t>
+  </si>
+  <si>
+    <t>Maroon mesh top and skirt.</t>
+  </si>
+  <si>
+    <t>Dark blue jeans and a black or brown belt. Black socks and tap shoes.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1060,12 +1081,6 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1088,7 +1103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1116,7 +1131,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1368,7 +1382,7 @@
       <c r="G1" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="H1" s="19"/>
+      <c r="H1"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -1389,7 +1403,6 @@
       <c r="F2" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1408,12 +1421,11 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="F3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G3" t="s">
         <v>268</v>
       </c>
-      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1432,12 +1444,11 @@
         <v>0.59375</v>
       </c>
       <c r="F4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G4" t="s">
         <v>268</v>
       </c>
-      <c r="H4" s="19"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1458,7 +1469,6 @@
       <c r="G5" t="s">
         <v>268</v>
       </c>
-      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1474,12 +1484,11 @@
         <v>0.40625</v>
       </c>
       <c r="F6" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="G6" t="s">
         <v>268</v>
       </c>
-      <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1500,7 +1509,6 @@
       <c r="G7" t="s">
         <v>268</v>
       </c>
-      <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1521,7 +1529,6 @@
       <c r="G8" t="s">
         <v>268</v>
       </c>
-      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1536,7 +1543,6 @@
       <c r="G9" t="s">
         <v>268</v>
       </c>
-      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1557,7 +1563,6 @@
       <c r="G10" t="s">
         <v>273</v>
       </c>
-      <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1575,7 +1580,9 @@
       <c r="F11" t="s">
         <v>262</v>
       </c>
-      <c r="H11" s="19"/>
+      <c r="G11" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -1594,12 +1601,11 @@
         <v>0.375</v>
       </c>
       <c r="F12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G12" t="s">
-        <v>306</v>
-      </c>
-      <c r="H12" s="19"/>
+        <v>304</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1620,7 +1626,6 @@
       <c r="G13" t="s">
         <v>276</v>
       </c>
-      <c r="H13" s="19"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -1636,12 +1641,11 @@
         <v>0.6875</v>
       </c>
       <c r="F14" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G14" t="s">
-        <v>276</v>
-      </c>
-      <c r="H14" s="19"/>
+        <v>313</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1657,12 +1661,11 @@
         <v>0.8125</v>
       </c>
       <c r="F15" t="s">
+        <v>284</v>
+      </c>
+      <c r="G15" t="s">
         <v>285</v>
       </c>
-      <c r="G15" t="s">
-        <v>286</v>
-      </c>
-      <c r="H15" s="19"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -1678,14 +1681,13 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="F16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G16" t="s">
-        <v>276</v>
-      </c>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>227</v>
       </c>
@@ -1699,14 +1701,13 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="F17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G17" t="s">
-        <v>277</v>
-      </c>
-      <c r="H17" s="19"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>228</v>
       </c>
@@ -1720,14 +1721,13 @@
         <v>0.65625</v>
       </c>
       <c r="F18" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G18" t="s">
-        <v>308</v>
-      </c>
-      <c r="H18" s="19"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>229</v>
       </c>
@@ -1744,11 +1744,10 @@
         <v>278</v>
       </c>
       <c r="G19" t="s">
-        <v>277</v>
-      </c>
-      <c r="H19" s="19"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1765,14 +1764,13 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F20" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="G20" t="s">
         <v>277</v>
       </c>
-      <c r="H20" s="19"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>230</v>
       </c>
@@ -1791,9 +1789,8 @@
       <c r="F21" t="s">
         <v>263</v>
       </c>
-      <c r="H21" s="19"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>231</v>
       </c>
@@ -1809,9 +1806,8 @@
       <c r="F22" t="s">
         <v>264</v>
       </c>
-      <c r="H22" s="19"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>232</v>
       </c>
@@ -1828,14 +1824,13 @@
         <v>0.65625</v>
       </c>
       <c r="F23" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G23" t="s">
         <v>276</v>
       </c>
-      <c r="H23" s="19"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>233</v>
       </c>
@@ -1849,14 +1844,13 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="F24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G24" t="s">
         <v>276</v>
       </c>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>234</v>
       </c>
@@ -1870,14 +1864,13 @@
         <v>0.75</v>
       </c>
       <c r="F25" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G25" t="s">
         <v>276</v>
       </c>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>235</v>
       </c>
@@ -1891,14 +1884,13 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="F26" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G26" t="s">
         <v>276</v>
       </c>
-      <c r="H26" s="19"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1915,14 +1907,13 @@
         <v>0.65625</v>
       </c>
       <c r="F27" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G27" t="s">
         <v>277</v>
       </c>
-      <c r="H27" s="19"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1936,14 +1927,13 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="F28" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" t="s">
         <v>287</v>
       </c>
-      <c r="G28" t="s">
-        <v>288</v>
-      </c>
-      <c r="H28" s="19"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -1962,9 +1952,8 @@
       <c r="F29" t="s">
         <v>259</v>
       </c>
-      <c r="H29" s="19"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -1978,14 +1967,13 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="F30" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G30" t="s">
         <v>279</v>
       </c>
-      <c r="H30" s="19"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>236</v>
       </c>
@@ -1999,14 +1987,13 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F31" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G31" t="s">
-        <v>281</v>
-      </c>
-      <c r="H31" s="19"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>237</v>
       </c>
@@ -2020,14 +2007,13 @@
         <v>0.65625</v>
       </c>
       <c r="F32" t="s">
-        <v>280</v>
+        <v>319</v>
       </c>
       <c r="G32" t="s">
-        <v>281</v>
-      </c>
-      <c r="H32" s="19"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -2043,9 +2029,8 @@
       <c r="F33" t="s">
         <v>260</v>
       </c>
-      <c r="H33" s="19"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -2059,14 +2044,13 @@
         <v>0.75</v>
       </c>
       <c r="F34" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G34" t="s">
-        <v>310</v>
-      </c>
-      <c r="H34" s="19"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -2080,14 +2064,13 @@
         <v>0.6875</v>
       </c>
       <c r="F35" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="G35" t="s">
-        <v>316</v>
-      </c>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -2106,9 +2089,8 @@
       <c r="F36" t="s">
         <v>261</v>
       </c>
-      <c r="H36" s="19"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -2122,14 +2104,13 @@
         <v>0.75</v>
       </c>
       <c r="F37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G37" t="s">
         <v>268</v>
       </c>
-      <c r="H37" s="19"/>
-    </row>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>238</v>
       </c>
@@ -2143,14 +2124,13 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="F38" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G38" t="s">
-        <v>282</v>
-      </c>
-      <c r="H38" s="19"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>239</v>
       </c>
@@ -2164,14 +2144,13 @@
         <v>0.625</v>
       </c>
       <c r="F39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G39" t="s">
-        <v>282</v>
-      </c>
-      <c r="H39" s="19"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -2185,14 +2164,13 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="F40" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G40" t="s">
         <v>268</v>
       </c>
-      <c r="H40" s="19"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -2211,9 +2189,8 @@
       <c r="G41" t="s">
         <v>268</v>
       </c>
-      <c r="H41" s="19"/>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2230,14 +2207,13 @@
         <v>0.375</v>
       </c>
       <c r="F42" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="G42" t="s">
-        <v>314</v>
-      </c>
-      <c r="H42" s="19"/>
-    </row>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>80</v>
       </c>
@@ -2248,9 +2224,8 @@
       <c r="F43" t="s">
         <v>265</v>
       </c>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>240</v>
       </c>
@@ -2267,14 +2242,13 @@
         <v>0.8125</v>
       </c>
       <c r="F44" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="G44" t="s">
-        <v>312</v>
-      </c>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>82</v>
       </c>
@@ -2291,14 +2265,13 @@
         <v>0.65625</v>
       </c>
       <c r="F45" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G45" t="s">
-        <v>281</v>
-      </c>
-      <c r="H45" s="19"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -2315,907 +2288,907 @@
         <v>260</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -31624,7 +31597,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F2" s="13">
         <v>0.41666666666666669</v>
@@ -31656,7 +31629,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F3" s="13">
         <v>0.41666666666666669</v>
@@ -31688,7 +31661,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4" s="13">
         <v>0.41666666666666669</v>
@@ -31720,7 +31693,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F5" s="16">
         <v>0.43055555555555558</v>
@@ -31752,7 +31725,7 @@
         <v>73</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F6" s="16">
         <v>0.4375</v>
@@ -31784,7 +31757,7 @@
         <v>206</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F7" s="16">
         <v>0.4513888888888889</v>
@@ -31816,7 +31789,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F8" s="16">
         <v>0.46180555555555558</v>
@@ -31848,7 +31821,7 @@
         <v>238</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F9" s="16">
         <v>0.47569444444444442</v>
@@ -31880,7 +31853,7 @@
         <v>185</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F10" s="16">
         <v>0.47569444444444442</v>
@@ -31912,7 +31885,7 @@
         <v>17</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F11" s="16">
         <v>0.4861111111111111</v>
@@ -31944,7 +31917,7 @@
         <v>18</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F12" s="16">
         <v>0.4861111111111111</v>
@@ -31976,7 +31949,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F13" s="16">
         <v>0.4861111111111111</v>
@@ -32008,7 +31981,7 @@
         <v>73</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F14" s="16">
         <v>0.4861111111111111</v>
@@ -32040,7 +32013,7 @@
         <v>206</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F15" s="16">
         <v>0.4861111111111111</v>
@@ -32072,7 +32045,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F16" s="16">
         <v>0.4861111111111111</v>
@@ -32104,7 +32077,7 @@
         <v>238</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F17" s="16">
         <v>0.4861111111111111</v>
@@ -32136,7 +32109,7 @@
         <v>185</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F18" s="16">
         <v>0.4861111111111111</v>
@@ -32168,7 +32141,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F19" s="13">
         <v>0.5</v>
@@ -32200,7 +32173,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F20" s="13">
         <v>0.54166666666666663</v>
@@ -32232,7 +32205,7 @@
         <v>17</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F21" s="13">
         <v>0.55555555555555558</v>
@@ -32264,7 +32237,7 @@
         <v>15</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F22" s="13">
         <v>0.56597222222222221</v>
@@ -32296,7 +32269,7 @@
         <v>239</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F23" s="13">
         <v>0.57986111111111105</v>
@@ -32328,7 +32301,7 @@
         <v>18</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F24" s="13">
         <v>0.58680555555555558</v>
@@ -32360,7 +32333,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F25" s="13">
         <v>0.59722222222222221</v>
@@ -32392,7 +32365,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F26" s="13">
         <v>0.59722222222222221</v>
@@ -32424,7 +32397,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F27" s="13">
         <v>0.59722222222222221</v>
@@ -32456,7 +32429,7 @@
         <v>239</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F28" s="13">
         <v>0.59722222222222221</v>
@@ -32488,7 +32461,7 @@
         <v>18</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F29" s="13">
         <v>0.59722222222222221</v>
@@ -32520,7 +32493,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F30" s="13">
         <v>0.61458333333333337</v>
@@ -32552,7 +32525,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F31" s="13">
         <v>0.61458333333333337</v>
@@ -32584,7 +32557,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F32" s="13">
         <v>0.61458333333333337</v>
@@ -32616,7 +32589,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F33" s="13">
         <v>0.61458333333333337</v>
@@ -32648,7 +32621,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F34" s="13">
         <v>0.61458333333333337</v>
@@ -32680,7 +32653,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F35" s="13">
         <v>0.61458333333333337</v>
@@ -32712,7 +32685,7 @@
         <v>206</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F36" s="13">
         <v>0.61458333333333337</v>
@@ -32744,7 +32717,7 @@
         <v>73</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F37" s="13">
         <v>0.61458333333333337</v>
@@ -32776,7 +32749,7 @@
         <v>238</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F38" s="13">
         <v>0.61458333333333337</v>
@@ -32808,7 +32781,7 @@
         <v>239</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F39" s="13">
         <v>0.61458333333333337</v>
@@ -32840,7 +32813,7 @@
         <v>185</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F40" s="13">
         <v>0.61458333333333337</v>
@@ -32872,7 +32845,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F41" s="13">
         <v>0.3611111111111111</v>
@@ -32904,7 +32877,7 @@
         <v>18</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F42" s="13">
         <v>0.3611111111111111</v>
@@ -32936,7 +32909,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F43" s="13">
         <v>0.3611111111111111</v>
@@ -32968,7 +32941,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F44" s="13">
         <v>0.39583333333333331</v>
@@ -33000,7 +32973,7 @@
         <v>73</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F45" s="13">
         <v>0.40625</v>
@@ -33032,7 +33005,7 @@
         <v>206</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F46" s="13">
         <v>0.42708333333333331</v>
@@ -33064,7 +33037,7 @@
         <v>12</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F47" s="13">
         <v>0.44791666666666669</v>
@@ -33096,7 +33069,7 @@
         <v>238</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F48" s="13">
         <v>0.46875</v>
@@ -33128,7 +33101,7 @@
         <v>185</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F49" s="13">
         <v>0.46875</v>
@@ -33160,7 +33133,7 @@
         <v>17</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F50" s="13">
         <v>0.5</v>
@@ -33192,7 +33165,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F51" s="13">
         <v>0.5</v>
@@ -33224,7 +33197,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F52" s="13">
         <v>0.5</v>
@@ -33256,7 +33229,7 @@
         <v>73</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F53" s="13">
         <v>0.5</v>
@@ -33288,7 +33261,7 @@
         <v>206</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F54" s="13">
         <v>0.5</v>
@@ -33320,7 +33293,7 @@
         <v>12</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F55" s="13">
         <v>0.5</v>
@@ -33352,7 +33325,7 @@
         <v>238</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F56" s="13">
         <v>0.5</v>
@@ -33384,7 +33357,7 @@
         <v>185</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F57" s="13">
         <v>0.5</v>
@@ -33416,7 +33389,7 @@
         <v>9</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F58" s="13">
         <v>0.51041666666666663</v>
@@ -33448,7 +33421,7 @@
         <v>12</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F59" s="13">
         <v>0.51041666666666663</v>
@@ -33480,7 +33453,7 @@
         <v>15</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F60" s="13">
         <v>0.51041666666666663</v>
@@ -33512,7 +33485,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F61" s="13">
         <v>0.51041666666666663</v>
@@ -33544,7 +33517,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F62" s="13">
         <v>0.51041666666666663</v>
@@ -33576,7 +33549,7 @@
         <v>20</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F63" s="13">
         <v>0.51041666666666663</v>
@@ -33608,7 +33581,7 @@
         <v>206</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F64" s="13">
         <v>0.51041666666666663</v>
@@ -33640,7 +33613,7 @@
         <v>73</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F65" s="13">
         <v>0.51041666666666663</v>
@@ -33672,7 +33645,7 @@
         <v>238</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F66" s="13">
         <v>0.51041666666666663</v>
@@ -33704,7 +33677,7 @@
         <v>239</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F67" s="13">
         <v>0.51041666666666663</v>
@@ -33736,7 +33709,7 @@
         <v>185</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F68" s="13">
         <v>0.51041666666666663</v>
@@ -33768,7 +33741,7 @@
         <v>9</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F69" s="13">
         <v>0.55208333333333337</v>
@@ -33800,7 +33773,7 @@
         <v>17</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F70" s="13">
         <v>0.57291666666666663</v>
@@ -33832,7 +33805,7 @@
         <v>15</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F71" s="13">
         <v>0.59375</v>
@@ -33864,7 +33837,7 @@
         <v>239</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F72" s="13">
         <v>0.61458333333333337</v>
@@ -33896,7 +33869,7 @@
         <v>18</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F73" s="13">
         <v>0.63541666666666663</v>
@@ -33928,7 +33901,7 @@
         <v>9</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F74" s="13">
         <v>0.65625</v>
@@ -33960,7 +33933,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F75" s="13">
         <v>0.65625</v>
@@ -33992,7 +33965,7 @@
         <v>15</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F76" s="13">
         <v>0.65625</v>
@@ -34024,7 +33997,7 @@
         <v>239</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F77" s="13">
         <v>0.65625</v>
@@ -34056,7 +34029,7 @@
         <v>18</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F78" s="13">
         <v>0.65625</v>
@@ -34088,7 +34061,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F79" s="13">
         <v>0.67708333333333337</v>
@@ -34120,7 +34093,7 @@
         <v>58</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F80" s="13">
         <v>0.73958333333333337</v>
@@ -34152,7 +34125,7 @@
         <v>55</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F81" s="13">
         <v>0.76041666666666663</v>
@@ -34184,7 +34157,7 @@
         <v>80</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F82" s="13">
         <v>0.78125</v>
@@ -34216,7 +34189,7 @@
         <v>66</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F83" s="13">
         <v>0.80208333333333337</v>
@@ -34248,7 +34221,7 @@
         <v>66</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F84" s="13">
         <v>0.83333333333333337</v>
@@ -34280,7 +34253,7 @@
         <v>66</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F85" s="13">
         <v>0.85416666666666663</v>
@@ -34312,7 +34285,7 @@
         <v>85</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F86" s="13">
         <v>0.85416666666666663</v>
@@ -34344,7 +34317,7 @@
         <v>85</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F87" s="13">
         <v>0.875</v>
@@ -34376,7 +34349,7 @@
         <v>85</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F88" s="13">
         <v>0.88888888888888884</v>
@@ -34408,7 +34381,7 @@
         <v>85</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F89" s="13">
         <v>0.90277777777777779</v>
@@ -34440,7 +34413,7 @@
         <v>228</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F90" s="13">
         <v>0.65625</v>
@@ -34472,7 +34445,7 @@
         <v>44</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F91" s="13">
         <v>0.67708333333333337</v>
@@ -34504,7 +34477,7 @@
         <v>236</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F92" s="13">
         <v>0.69791666666666663</v>
@@ -34536,7 +34509,7 @@
         <v>226</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F93" s="13">
         <v>0.71875</v>
@@ -34568,7 +34541,7 @@
         <v>237</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F94" s="13">
         <v>0.73958333333333337</v>
@@ -34600,7 +34573,7 @@
         <v>59</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F95" s="13">
         <v>0.76041666666666663</v>
@@ -34632,7 +34605,7 @@
         <v>62</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F96" s="13">
         <v>0.78125</v>
@@ -34664,7 +34637,7 @@
         <v>227</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F97" s="13">
         <v>0.80208333333333337</v>
@@ -34696,7 +34669,7 @@
         <v>67</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F98" s="13">
         <v>0.84375</v>
@@ -34728,7 +34701,7 @@
         <v>240</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F99" s="13">
         <v>0.86458333333333337</v>
@@ -34760,7 +34733,7 @@
         <v>85</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F100" s="13">
         <v>0.88541666666666663</v>
@@ -34792,7 +34765,7 @@
         <v>71</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F101" s="13">
         <v>0.65625</v>
@@ -34824,7 +34797,7 @@
         <v>68</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F102" s="13">
         <v>0.67708333333333337</v>
@@ -34856,7 +34829,7 @@
         <v>66</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F103" s="13">
         <v>0.69791666666666663</v>
@@ -34888,7 +34861,7 @@
         <v>66</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F104" s="13">
         <v>0.71875</v>
@@ -34920,7 +34893,7 @@
         <v>66</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F105" s="13">
         <v>0.73958333333333337</v>
@@ -34952,7 +34925,7 @@
         <v>221</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F106" s="13">
         <v>0.76041666666666663</v>
@@ -34984,7 +34957,7 @@
         <v>222</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F107" s="13">
         <v>0.78125</v>
@@ -35016,7 +34989,7 @@
         <v>85</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F108" s="13">
         <v>0.82291666666666663</v>
@@ -35048,7 +35021,7 @@
         <v>229</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F109" s="13">
         <v>0.84375</v>
@@ -35080,7 +35053,7 @@
         <v>85</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F110" s="13">
         <v>0.86458333333333337</v>
@@ -35112,7 +35085,7 @@
         <v>85</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F111" s="13">
         <v>0.89583333333333337</v>
@@ -35144,7 +35117,7 @@
         <v>230</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F112" s="13">
         <v>0.65625</v>
@@ -35176,7 +35149,7 @@
         <v>220</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F113" s="13">
         <v>0.67708333333333337</v>
@@ -35208,7 +35181,7 @@
         <v>231</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F114" s="13">
         <v>0.69791666666666663</v>
@@ -35240,7 +35213,7 @@
         <v>82</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F115" s="13">
         <v>0.71875</v>
@@ -35272,7 +35245,7 @@
         <v>232</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F116" s="13">
         <v>0.73958333333333337</v>
@@ -35304,7 +35277,7 @@
         <v>233</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F117" s="13">
         <v>0.76041666666666663</v>
@@ -35336,7 +35309,7 @@
         <v>234</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F118" s="13">
         <v>0.78125</v>
@@ -35368,7 +35341,7 @@
         <v>235</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F119" s="13">
         <v>0.80208333333333337</v>
@@ -35400,7 +35373,7 @@
         <v>223</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F120" s="13">
         <v>0.84375</v>
@@ -35432,7 +35405,7 @@
         <v>224</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F121" s="13">
         <v>0.86458333333333337</v>
@@ -35464,7 +35437,7 @@
         <v>225</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F122" s="13">
         <v>0.89583333333333337</v>
@@ -35496,7 +35469,7 @@
         <v>17</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F123" s="13">
         <v>0.65625</v>
@@ -35528,7 +35501,7 @@
         <v>18</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F124" s="13">
         <v>0.65625</v>
@@ -35560,7 +35533,7 @@
         <v>20</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F125" s="13">
         <v>0.65625</v>
@@ -35592,7 +35565,7 @@
         <v>73</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F126" s="13">
         <v>0.65625</v>
@@ -35624,7 +35597,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F127" s="13">
         <v>0.69791666666666663</v>
@@ -35656,7 +35629,7 @@
         <v>12</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F128" s="13">
         <v>0.69791666666666663</v>
@@ -35688,7 +35661,7 @@
         <v>15</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F129" s="13">
         <v>0.69791666666666663</v>
@@ -35720,7 +35693,7 @@
         <v>17</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F130" s="13">
         <v>0.69791666666666663</v>
@@ -35752,7 +35725,7 @@
         <v>18</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F131" s="13">
         <v>0.69791666666666663</v>
@@ -35784,7 +35757,7 @@
         <v>20</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F132" s="13">
         <v>0.69791666666666663</v>
@@ -35816,7 +35789,7 @@
         <v>206</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F133" s="13">
         <v>0.69791666666666663</v>
@@ -35848,7 +35821,7 @@
         <v>73</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F134" s="13">
         <v>0.69791666666666663</v>
@@ -35880,7 +35853,7 @@
         <v>185</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F135" s="13">
         <v>0.69791666666666663</v>
@@ -35912,7 +35885,7 @@
         <v>238</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F136" s="13">
         <v>0.69791666666666663</v>
@@ -35944,7 +35917,7 @@
         <v>239</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F137" s="13">
         <v>0.69791666666666663</v>
@@ -35976,7 +35949,7 @@
         <v>220</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F138" s="13">
         <v>0.75</v>
@@ -36008,7 +35981,7 @@
         <v>226</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F139" s="13">
         <v>0.75</v>
@@ -36040,7 +36013,7 @@
         <v>44</v>
       </c>
       <c r="E140" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F140" s="13">
         <v>0.75</v>
@@ -36072,7 +36045,7 @@
         <v>230</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F141" s="13">
         <v>0.75</v>
@@ -36104,7 +36077,7 @@
         <v>231</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F142" s="13">
         <v>0.75</v>
@@ -36136,7 +36109,7 @@
         <v>232</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F143" s="13">
         <v>0.75</v>
@@ -36168,7 +36141,7 @@
         <v>233</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F144" s="13">
         <v>0.75</v>
@@ -36200,7 +36173,7 @@
         <v>234</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F145" s="13">
         <v>0.75</v>
@@ -36232,7 +36205,7 @@
         <v>55</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F146" s="13">
         <v>0.75</v>
@@ -36264,7 +36237,7 @@
         <v>59</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F147" s="13">
         <v>0.75</v>
@@ -36296,7 +36269,7 @@
         <v>236</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F148" s="13">
         <v>0.75</v>
@@ -36328,7 +36301,7 @@
         <v>237</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F149" s="13">
         <v>0.75</v>
@@ -36360,7 +36333,7 @@
         <v>66</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F150" s="13">
         <v>0.75</v>
@@ -36392,7 +36365,7 @@
         <v>71</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F151" s="13">
         <v>0.75</v>
@@ -36424,7 +36397,7 @@
         <v>82</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F152" s="13">
         <v>0.75</v>
@@ -36456,7 +36429,7 @@
         <v>85</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F153" s="13">
         <v>0.75</v>
@@ -36488,7 +36461,7 @@
         <v>221</v>
       </c>
       <c r="E154" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F154" s="13">
         <v>0.84375</v>
@@ -36520,7 +36493,7 @@
         <v>222</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F155" s="13">
         <v>0.84375</v>
@@ -36552,7 +36525,7 @@
         <v>223</v>
       </c>
       <c r="E156" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F156" s="13">
         <v>0.84375</v>
@@ -36584,7 +36557,7 @@
         <v>224</v>
       </c>
       <c r="E157" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F157" s="13">
         <v>0.84375</v>
@@ -36616,7 +36589,7 @@
         <v>225</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F158" s="13">
         <v>0.84375</v>
@@ -36648,7 +36621,7 @@
         <v>227</v>
       </c>
       <c r="E159" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F159" s="13">
         <v>0.84375</v>
@@ -36680,7 +36653,7 @@
         <v>228</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F160" s="13">
         <v>0.84375</v>
@@ -36712,7 +36685,7 @@
         <v>229</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F161" s="13">
         <v>0.84375</v>
@@ -36744,7 +36717,7 @@
         <v>235</v>
       </c>
       <c r="E162" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F162" s="13">
         <v>0.84375</v>
@@ -36776,7 +36749,7 @@
         <v>58</v>
       </c>
       <c r="E163" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F163" s="13">
         <v>0.84375</v>
@@ -36808,7 +36781,7 @@
         <v>62</v>
       </c>
       <c r="E164" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F164" s="13">
         <v>0.84375</v>
@@ -36840,7 +36813,7 @@
         <v>66</v>
       </c>
       <c r="E165" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F165" s="13">
         <v>0.84375</v>
@@ -36872,7 +36845,7 @@
         <v>67</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F166" s="13">
         <v>0.84375</v>
@@ -36904,7 +36877,7 @@
         <v>68</v>
       </c>
       <c r="E167" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F167" s="13">
         <v>0.84375</v>
@@ -36936,7 +36909,7 @@
         <v>80</v>
       </c>
       <c r="E168" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F168" s="13">
         <v>0.84375</v>
@@ -36968,7 +36941,7 @@
         <v>240</v>
       </c>
       <c r="E169" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F169" s="13">
         <v>0.84375</v>
@@ -37000,7 +36973,7 @@
         <v>85</v>
       </c>
       <c r="E170" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F170" s="13">
         <v>0.84375</v>
@@ -40386,18 +40359,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
-          <x14:formula1>
-            <xm:f>classes!$A:$A</xm:f>
-          </x14:formula1>
-          <xm:sqref>D20:D57 D2:D18</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Isadora/Documents/GitHub/rehearsal-schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21290AE-2EB6-B247-A970-595850BD930E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F056CD-31E9-3C44-A812-97EA6E8AF61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4120" yWindow="780" windowWidth="27240" windowHeight="20420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4120" yWindow="780" windowWidth="27240" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="classes" sheetId="1" r:id="rId1"/>
@@ -1103,7 +1103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1131,6 +1131,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1350,14 +1352,15 @@
   <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" customWidth="1"/>
-    <col min="4" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="107.33203125" customWidth="1"/>
-    <col min="7" max="7" width="51" customWidth="1"/>
-    <col min="8" max="8" width="94" customWidth="1"/>
-    <col min="9" max="23" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" style="19" customWidth="1"/>
+    <col min="4" max="5" width="15.83203125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="107.33203125" style="19" customWidth="1"/>
+    <col min="7" max="7" width="51" style="19" customWidth="1"/>
+    <col min="8" max="8" width="94" style="19" customWidth="1"/>
+    <col min="9" max="23" width="10.5" style="19" customWidth="1"/>
+    <col min="24" max="16384" width="11.1640625" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1382,1813 +1385,1813 @@
       <c r="G1" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="H1"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="20">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="19" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="20">
+        <v>0.59375</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="20">
+        <v>0.40625</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0.46875</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="20">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="20">
+        <v>0.8125</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="20">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0.6875</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="20">
+        <v>0.8125</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="20">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="20">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="20">
+        <v>0.8125</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="20">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="20">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="20">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="20">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D29" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="20">
+        <v>0.71875</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="20">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="20">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="20">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="20">
+        <v>0.6875</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="20">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="E39" s="20">
+        <v>0.625</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="20">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G40" s="19" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="13">
-        <v>0.59375</v>
-      </c>
-      <c r="F4" t="s">
-        <v>291</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="E41" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="G41" s="19" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" t="s">
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="13">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="E42" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0.40625</v>
-      </c>
-      <c r="F6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="E43" s="20"/>
+      <c r="F43" s="19" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="20">
+        <v>0.8125</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="13">
-        <v>0.46875</v>
-      </c>
-      <c r="F7" t="s">
-        <v>270</v>
-      </c>
-      <c r="G7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="13">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="F8" t="s">
-        <v>271</v>
-      </c>
-      <c r="G8" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G9" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>221</v>
-      </c>
-      <c r="B10" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F10" t="s">
-        <v>274</v>
-      </c>
-      <c r="G10" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F11" t="s">
-        <v>262</v>
-      </c>
-      <c r="G11" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="F12" t="s">
-        <v>303</v>
-      </c>
-      <c r="G12" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>223</v>
-      </c>
-      <c r="B13" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="13">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F13" t="s">
-        <v>275</v>
-      </c>
-      <c r="G13" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="13">
-        <v>0.6875</v>
-      </c>
-      <c r="F14" t="s">
-        <v>292</v>
-      </c>
-      <c r="G14" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>225</v>
-      </c>
-      <c r="B15" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F15" t="s">
-        <v>284</v>
-      </c>
-      <c r="G15" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>226</v>
-      </c>
-      <c r="B16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D46" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="13">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F16" t="s">
-        <v>293</v>
-      </c>
-      <c r="G16" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>227</v>
-      </c>
-      <c r="B17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="13">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F17" t="s">
-        <v>294</v>
-      </c>
-      <c r="G17" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>228</v>
-      </c>
-      <c r="B18" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F18" t="s">
-        <v>305</v>
-      </c>
-      <c r="G18" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F19" t="s">
-        <v>278</v>
-      </c>
-      <c r="G19" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F20" t="s">
-        <v>310</v>
-      </c>
-      <c r="G20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F21" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="F22" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>232</v>
-      </c>
-      <c r="B23" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D23" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F23" t="s">
-        <v>295</v>
-      </c>
-      <c r="G23" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="13">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F24" t="s">
-        <v>296</v>
-      </c>
-      <c r="G24" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>234</v>
-      </c>
-      <c r="B25" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="F25" t="s">
-        <v>297</v>
-      </c>
-      <c r="G25" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>235</v>
-      </c>
-      <c r="B26" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="13">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="F26" t="s">
-        <v>298</v>
-      </c>
-      <c r="G26" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F27" t="s">
-        <v>299</v>
-      </c>
-      <c r="G27" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="13">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F28" t="s">
-        <v>286</v>
-      </c>
-      <c r="G28" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="13">
-        <v>0.71875</v>
-      </c>
-      <c r="F29" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="13">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="F30" t="s">
-        <v>300</v>
-      </c>
-      <c r="G30" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>236</v>
-      </c>
-      <c r="B31" t="s">
-        <v>193</v>
-      </c>
-      <c r="D31" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="13">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F31" t="s">
-        <v>301</v>
-      </c>
-      <c r="G31" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>237</v>
-      </c>
-      <c r="B32" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F32" t="s">
-        <v>319</v>
-      </c>
-      <c r="G32" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="13">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F33" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D34" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="F34" t="s">
-        <v>321</v>
-      </c>
-      <c r="G34" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="13">
-        <v>0.6875</v>
-      </c>
-      <c r="F35" t="s">
-        <v>323</v>
-      </c>
-      <c r="G35" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F36" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="F37" t="s">
-        <v>283</v>
-      </c>
-      <c r="G37" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>238</v>
-      </c>
-      <c r="B38" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="13">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F38" t="s">
-        <v>282</v>
-      </c>
-      <c r="G38" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>239</v>
-      </c>
-      <c r="B39" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="13">
-        <v>0.625</v>
-      </c>
-      <c r="F39" t="s">
-        <v>288</v>
-      </c>
-      <c r="G39" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" t="s">
-        <v>187</v>
-      </c>
-      <c r="D40" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="13">
+      <c r="E46" s="20">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F40" t="s">
-        <v>282</v>
-      </c>
-      <c r="G40" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" t="s">
-        <v>194</v>
-      </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F41" t="s">
-        <v>259</v>
-      </c>
-      <c r="G41" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C42" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="F42" t="s">
-        <v>307</v>
-      </c>
-      <c r="G42" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>240</v>
-      </c>
-      <c r="B44" t="s">
-        <v>193</v>
-      </c>
-      <c r="C44" t="s">
-        <v>202</v>
-      </c>
-      <c r="D44" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F44" t="s">
-        <v>306</v>
-      </c>
-      <c r="G44" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F45" t="s">
-        <v>302</v>
-      </c>
-      <c r="G45" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="13">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="F46" s="19" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="49" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" s="19" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -40359,6 +40362,18 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
+          <x14:formula1>
+            <xm:f>classes!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>D20:D57 D2:D18</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 

--- a/input.xlsx
+++ b/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wsp/Documents/GitHub/rehearsal-schedule/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Isadora/Documents/GitHub/rehearsal-schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55F4E39-DC3A-124E-9CA8-78FB76005A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F056CD-31E9-3C44-A812-97EA6E8AF61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4120" yWindow="920" windowWidth="27240" windowHeight="20420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4120" yWindow="780" windowWidth="27240" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="classes" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3319" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3320" uniqueCount="325">
   <si>
     <t>class_name</t>
   </si>
@@ -880,9 +880,6 @@
     <t>Black leotard.</t>
   </si>
   <si>
-    <t>Red sequin flapper dress and footed tights.</t>
-  </si>
-  <si>
     <t>Tap shoes.</t>
   </si>
   <si>
@@ -917,9 +914,6 @@
   </si>
   <si>
     <t>Pale blue sequin dress OR white turtleneck, black tights, pale blue cumberbund.</t>
-  </si>
-  <si>
-    <t>Dark rose dress, and white leotard mesh skirt OR maroon button down and white button down and white pants.</t>
   </si>
   <si>
     <t>Black cropped long sleeve and purple sweatpants.</t>
@@ -964,19 +958,7 @@
     <t>Bright colored blazer.</t>
   </si>
   <si>
-    <t>Black tank top or leotard and wide leg pants. Black jazz shoes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black tank top and black blazer. </t>
-  </si>
-  <si>
-    <t>Black wide leg pants. Tap shoes.</t>
-  </si>
-  <si>
     <t>Black country top OR red country top. Black cowboy hat.</t>
-  </si>
-  <si>
-    <t>Dark blue jeans and a black or brown belt. Tap shoes.</t>
   </si>
   <si>
     <t>Pale green dress and ballet tights OR pale green sequin vest.</t>
@@ -985,20 +967,59 @@
     <t>For vest: black pants. Ballet tights and ballet shoes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Maroon mesh top and skirt. </t>
-  </si>
-  <si>
     <t>Black leotard and shorts.</t>
   </si>
   <si>
     <t>Yellow sequin dress and black tights OR white button down with a silver sequin vest and black pants.</t>
+  </si>
+  <si>
+    <t>Dark rose dress baby doll dress OR rose button down with white pants. White leotard with mesh skirt OR white button down and white pants.</t>
+  </si>
+  <si>
+    <t>Beige/skin-toned leotard or fitted tank.</t>
+  </si>
+  <si>
+    <t>Black/white/gray Accessories, tank top/leo if applicable. Hip hop sneakers.</t>
+  </si>
+  <si>
+    <t>Blakc socks and hip hop sneakers.</t>
+  </si>
+  <si>
+    <t>Black jazz shoes. Tan bra or leotard if needed. Black socks if needed.</t>
+  </si>
+  <si>
+    <t>Black tank top or leotard and wide leg pants. Black jazz shoes. Black socks if needed.</t>
+  </si>
+  <si>
+    <t>Nude leotard or bra with black spandex shorts. Black jazz shoes.</t>
+  </si>
+  <si>
+    <t>Black socks and tap shoes.</t>
+  </si>
+  <si>
+    <t>Red sequin flapper dress and footed tights. Headband.</t>
+  </si>
+  <si>
+    <t>Tan bra or leotard if needed. Tap shoes.</t>
+  </si>
+  <si>
+    <t>Black tank top and black blazer.</t>
+  </si>
+  <si>
+    <t>Black wide leg pants. Black socks and tap shoes.</t>
+  </si>
+  <si>
+    <t>Maroon mesh top and skirt.</t>
+  </si>
+  <si>
+    <t>Dark blue jeans and a black or brown belt. Black socks and tap shoes.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1060,12 +1081,6 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1088,7 +1103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1116,7 +1131,8 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1336,14 +1352,15 @@
   <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" customWidth="1"/>
-    <col min="4" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="107.33203125" customWidth="1"/>
-    <col min="7" max="7" width="51" customWidth="1"/>
-    <col min="8" max="8" width="94" customWidth="1"/>
-    <col min="9" max="23" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" style="19" customWidth="1"/>
+    <col min="4" max="5" width="15.83203125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="107.33203125" style="19" customWidth="1"/>
+    <col min="7" max="7" width="51" style="19" customWidth="1"/>
+    <col min="8" max="8" width="94" style="19" customWidth="1"/>
+    <col min="9" max="23" width="10.5" style="19" customWidth="1"/>
+    <col min="24" max="16384" width="11.1640625" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1371,1851 +1388,1810 @@
       <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="20">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="20">
+        <v>0.59375</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="20">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="20">
+        <v>0.40625</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0.46875</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="20">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="20">
+        <v>0.8125</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="20">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0.6875</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="20">
+        <v>0.8125</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="20">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="20">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="20">
+        <v>0.8125</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="20">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="20">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="20">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="20">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D29" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="20">
+        <v>0.71875</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="20">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="20">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="20">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="20">
+        <v>0.6875</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="20">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="E39" s="20">
+        <v>0.625</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="20">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G40" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="H3" s="19"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="13">
-        <v>0.59375</v>
-      </c>
-      <c r="F4" t="s">
-        <v>292</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="E41" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="G41" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="H4" s="19"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="13">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G5" t="s">
-        <v>268</v>
-      </c>
-      <c r="H5" s="19"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="E42" s="20">
+        <v>0.375</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0.40625</v>
-      </c>
-      <c r="F6" t="s">
-        <v>293</v>
-      </c>
-      <c r="G6" t="s">
-        <v>268</v>
-      </c>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="E43" s="20"/>
+      <c r="F43" s="19" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="20">
+        <v>0.8125</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="20">
+        <v>0.65625</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="13">
-        <v>0.46875</v>
-      </c>
-      <c r="F7" t="s">
-        <v>270</v>
-      </c>
-      <c r="G7" t="s">
-        <v>268</v>
-      </c>
-      <c r="H7" s="19"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="13">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="F8" t="s">
-        <v>271</v>
-      </c>
-      <c r="G8" t="s">
-        <v>268</v>
-      </c>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G9" t="s">
-        <v>268</v>
-      </c>
-      <c r="H9" s="19"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>221</v>
-      </c>
-      <c r="B10" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F10" t="s">
-        <v>274</v>
-      </c>
-      <c r="G10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H10" s="19"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F11" t="s">
-        <v>262</v>
-      </c>
-      <c r="H11" s="19"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="F12" t="s">
-        <v>305</v>
-      </c>
-      <c r="G12" t="s">
-        <v>306</v>
-      </c>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>223</v>
-      </c>
-      <c r="B13" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="13">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F13" t="s">
-        <v>275</v>
-      </c>
-      <c r="G13" t="s">
-        <v>276</v>
-      </c>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="13">
-        <v>0.6875</v>
-      </c>
-      <c r="F14" t="s">
-        <v>294</v>
-      </c>
-      <c r="G14" t="s">
-        <v>276</v>
-      </c>
-      <c r="H14" s="19"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>225</v>
-      </c>
-      <c r="B15" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F15" t="s">
-        <v>285</v>
-      </c>
-      <c r="G15" t="s">
-        <v>286</v>
-      </c>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>226</v>
-      </c>
-      <c r="B16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D46" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="13">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F16" t="s">
-        <v>295</v>
-      </c>
-      <c r="G16" t="s">
-        <v>276</v>
-      </c>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>227</v>
-      </c>
-      <c r="B17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="13">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F17" t="s">
-        <v>296</v>
-      </c>
-      <c r="G17" t="s">
-        <v>277</v>
-      </c>
-      <c r="H17" s="19"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>228</v>
-      </c>
-      <c r="B18" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F18" t="s">
-        <v>307</v>
-      </c>
-      <c r="G18" t="s">
-        <v>308</v>
-      </c>
-      <c r="H18" s="19"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F19" t="s">
-        <v>278</v>
-      </c>
-      <c r="G19" t="s">
-        <v>277</v>
-      </c>
-      <c r="H19" s="19"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F20" t="s">
-        <v>317</v>
-      </c>
-      <c r="G20" t="s">
-        <v>277</v>
-      </c>
-      <c r="H20" s="19"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F21" t="s">
-        <v>263</v>
-      </c>
-      <c r="H21" s="19"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="F22" t="s">
-        <v>264</v>
-      </c>
-      <c r="H22" s="19"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>232</v>
-      </c>
-      <c r="B23" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D23" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F23" t="s">
-        <v>297</v>
-      </c>
-      <c r="G23" t="s">
-        <v>276</v>
-      </c>
-      <c r="H23" s="19"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="13">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F24" t="s">
-        <v>298</v>
-      </c>
-      <c r="G24" t="s">
-        <v>276</v>
-      </c>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>234</v>
-      </c>
-      <c r="B25" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="F25" t="s">
-        <v>299</v>
-      </c>
-      <c r="G25" t="s">
-        <v>276</v>
-      </c>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>235</v>
-      </c>
-      <c r="B26" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="13">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="F26" t="s">
-        <v>300</v>
-      </c>
-      <c r="G26" t="s">
-        <v>276</v>
-      </c>
-      <c r="H26" s="19"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F27" t="s">
-        <v>301</v>
-      </c>
-      <c r="G27" t="s">
-        <v>277</v>
-      </c>
-      <c r="H27" s="19"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="13">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F28" t="s">
-        <v>287</v>
-      </c>
-      <c r="G28" t="s">
-        <v>288</v>
-      </c>
-      <c r="H28" s="19"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="13">
-        <v>0.71875</v>
-      </c>
-      <c r="F29" t="s">
-        <v>259</v>
-      </c>
-      <c r="H29" s="19"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="13">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="F30" t="s">
-        <v>302</v>
-      </c>
-      <c r="G30" t="s">
-        <v>279</v>
-      </c>
-      <c r="H30" s="19"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>236</v>
-      </c>
-      <c r="B31" t="s">
-        <v>193</v>
-      </c>
-      <c r="D31" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="13">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F31" t="s">
-        <v>303</v>
-      </c>
-      <c r="G31" t="s">
-        <v>281</v>
-      </c>
-      <c r="H31" s="19"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>237</v>
-      </c>
-      <c r="B32" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F32" t="s">
-        <v>280</v>
-      </c>
-      <c r="G32" t="s">
-        <v>281</v>
-      </c>
-      <c r="H32" s="19"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="13">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="E46" s="20">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F46" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="H33" s="19"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D34" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="F34" t="s">
-        <v>309</v>
-      </c>
-      <c r="G34" t="s">
-        <v>310</v>
-      </c>
-      <c r="H34" s="19"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="13">
-        <v>0.6875</v>
-      </c>
-      <c r="F35" t="s">
-        <v>315</v>
-      </c>
-      <c r="G35" t="s">
-        <v>316</v>
-      </c>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F36" t="s">
-        <v>261</v>
-      </c>
-      <c r="H36" s="19"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="F37" t="s">
-        <v>284</v>
-      </c>
-      <c r="G37" t="s">
-        <v>268</v>
-      </c>
-      <c r="H37" s="19"/>
-    </row>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>238</v>
-      </c>
-      <c r="B38" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="13">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F38" t="s">
-        <v>283</v>
-      </c>
-      <c r="G38" t="s">
-        <v>282</v>
-      </c>
-      <c r="H38" s="19"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>239</v>
-      </c>
-      <c r="B39" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="13">
-        <v>0.625</v>
-      </c>
-      <c r="F39" t="s">
-        <v>289</v>
-      </c>
-      <c r="G39" t="s">
-        <v>282</v>
-      </c>
-      <c r="H39" s="19"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" t="s">
-        <v>187</v>
-      </c>
-      <c r="D40" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="13">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F40" t="s">
-        <v>283</v>
-      </c>
-      <c r="G40" t="s">
-        <v>268</v>
-      </c>
-      <c r="H40" s="19"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" t="s">
-        <v>194</v>
-      </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F41" t="s">
-        <v>259</v>
-      </c>
-      <c r="G41" t="s">
-        <v>268</v>
-      </c>
-      <c r="H41" s="19"/>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C42" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="F42" t="s">
-        <v>313</v>
-      </c>
-      <c r="G42" t="s">
-        <v>314</v>
-      </c>
-      <c r="H42" s="19"/>
-    </row>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" t="s">
-        <v>265</v>
-      </c>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>240</v>
-      </c>
-      <c r="B44" t="s">
-        <v>193</v>
-      </c>
-      <c r="C44" t="s">
-        <v>202</v>
-      </c>
-      <c r="D44" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F44" t="s">
-        <v>311</v>
-      </c>
-      <c r="G44" t="s">
-        <v>312</v>
-      </c>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F45" t="s">
-        <v>304</v>
-      </c>
-      <c r="G45" t="s">
-        <v>281</v>
-      </c>
-      <c r="H45" s="19"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="13">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F46" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="16" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" s="19" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -31624,7 +31600,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F2" s="13">
         <v>0.41666666666666669</v>
@@ -31656,7 +31632,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F3" s="13">
         <v>0.41666666666666669</v>
@@ -31688,7 +31664,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F4" s="13">
         <v>0.41666666666666669</v>
@@ -31720,7 +31696,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F5" s="16">
         <v>0.43055555555555558</v>
@@ -31752,7 +31728,7 @@
         <v>73</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F6" s="16">
         <v>0.4375</v>
@@ -31784,7 +31760,7 @@
         <v>206</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F7" s="16">
         <v>0.4513888888888889</v>
@@ -31816,7 +31792,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F8" s="16">
         <v>0.46180555555555558</v>
@@ -31848,7 +31824,7 @@
         <v>238</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F9" s="16">
         <v>0.47569444444444442</v>
@@ -31880,7 +31856,7 @@
         <v>185</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F10" s="16">
         <v>0.47569444444444442</v>
@@ -31912,7 +31888,7 @@
         <v>17</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F11" s="16">
         <v>0.4861111111111111</v>
@@ -31944,7 +31920,7 @@
         <v>18</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F12" s="16">
         <v>0.4861111111111111</v>
@@ -31976,7 +31952,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F13" s="16">
         <v>0.4861111111111111</v>
@@ -32008,7 +31984,7 @@
         <v>73</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F14" s="16">
         <v>0.4861111111111111</v>
@@ -32040,7 +32016,7 @@
         <v>206</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F15" s="16">
         <v>0.4861111111111111</v>
@@ -32072,7 +32048,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F16" s="16">
         <v>0.4861111111111111</v>
@@ -32104,7 +32080,7 @@
         <v>238</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F17" s="16">
         <v>0.4861111111111111</v>
@@ -32136,7 +32112,7 @@
         <v>185</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F18" s="16">
         <v>0.4861111111111111</v>
@@ -32168,7 +32144,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F19" s="13">
         <v>0.5</v>
@@ -32200,7 +32176,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F20" s="13">
         <v>0.54166666666666663</v>
@@ -32232,7 +32208,7 @@
         <v>17</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F21" s="13">
         <v>0.55555555555555558</v>
@@ -32264,7 +32240,7 @@
         <v>15</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F22" s="13">
         <v>0.56597222222222221</v>
@@ -32296,7 +32272,7 @@
         <v>239</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F23" s="13">
         <v>0.57986111111111105</v>
@@ -32328,7 +32304,7 @@
         <v>18</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F24" s="13">
         <v>0.58680555555555558</v>
@@ -32360,7 +32336,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F25" s="13">
         <v>0.59722222222222221</v>
@@ -32392,7 +32368,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F26" s="13">
         <v>0.59722222222222221</v>
@@ -32424,7 +32400,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F27" s="13">
         <v>0.59722222222222221</v>
@@ -32456,7 +32432,7 @@
         <v>239</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F28" s="13">
         <v>0.59722222222222221</v>
@@ -32488,7 +32464,7 @@
         <v>18</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F29" s="13">
         <v>0.59722222222222221</v>
@@ -32520,7 +32496,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F30" s="13">
         <v>0.61458333333333337</v>
@@ -32552,7 +32528,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F31" s="13">
         <v>0.61458333333333337</v>
@@ -32584,7 +32560,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F32" s="13">
         <v>0.61458333333333337</v>
@@ -32616,7 +32592,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F33" s="13">
         <v>0.61458333333333337</v>
@@ -32648,7 +32624,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F34" s="13">
         <v>0.61458333333333337</v>
@@ -32680,7 +32656,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F35" s="13">
         <v>0.61458333333333337</v>
@@ -32712,7 +32688,7 @@
         <v>206</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F36" s="13">
         <v>0.61458333333333337</v>
@@ -32744,7 +32720,7 @@
         <v>73</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F37" s="13">
         <v>0.61458333333333337</v>
@@ -32776,7 +32752,7 @@
         <v>238</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F38" s="13">
         <v>0.61458333333333337</v>
@@ -32808,7 +32784,7 @@
         <v>239</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F39" s="13">
         <v>0.61458333333333337</v>
@@ -32840,7 +32816,7 @@
         <v>185</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F40" s="13">
         <v>0.61458333333333337</v>
@@ -32872,7 +32848,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F41" s="13">
         <v>0.3611111111111111</v>
@@ -32904,7 +32880,7 @@
         <v>18</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F42" s="13">
         <v>0.3611111111111111</v>
@@ -32936,7 +32912,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F43" s="13">
         <v>0.3611111111111111</v>
@@ -32968,7 +32944,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F44" s="13">
         <v>0.39583333333333331</v>
@@ -33000,7 +32976,7 @@
         <v>73</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F45" s="13">
         <v>0.40625</v>
@@ -33032,7 +33008,7 @@
         <v>206</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F46" s="13">
         <v>0.42708333333333331</v>
@@ -33064,7 +33040,7 @@
         <v>12</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F47" s="13">
         <v>0.44791666666666669</v>
@@ -33096,7 +33072,7 @@
         <v>238</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F48" s="13">
         <v>0.46875</v>
@@ -33128,7 +33104,7 @@
         <v>185</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F49" s="13">
         <v>0.46875</v>
@@ -33160,7 +33136,7 @@
         <v>17</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F50" s="13">
         <v>0.5</v>
@@ -33192,7 +33168,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F51" s="13">
         <v>0.5</v>
@@ -33224,7 +33200,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F52" s="13">
         <v>0.5</v>
@@ -33256,7 +33232,7 @@
         <v>73</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F53" s="13">
         <v>0.5</v>
@@ -33288,7 +33264,7 @@
         <v>206</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F54" s="13">
         <v>0.5</v>
@@ -33320,7 +33296,7 @@
         <v>12</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F55" s="13">
         <v>0.5</v>
@@ -33352,7 +33328,7 @@
         <v>238</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F56" s="13">
         <v>0.5</v>
@@ -33384,7 +33360,7 @@
         <v>185</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F57" s="13">
         <v>0.5</v>
@@ -33416,7 +33392,7 @@
         <v>9</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F58" s="13">
         <v>0.51041666666666663</v>
@@ -33448,7 +33424,7 @@
         <v>12</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F59" s="13">
         <v>0.51041666666666663</v>
@@ -33480,7 +33456,7 @@
         <v>15</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F60" s="13">
         <v>0.51041666666666663</v>
@@ -33512,7 +33488,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F61" s="13">
         <v>0.51041666666666663</v>
@@ -33544,7 +33520,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F62" s="13">
         <v>0.51041666666666663</v>
@@ -33576,7 +33552,7 @@
         <v>20</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F63" s="13">
         <v>0.51041666666666663</v>
@@ -33608,7 +33584,7 @@
         <v>206</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F64" s="13">
         <v>0.51041666666666663</v>
@@ -33640,7 +33616,7 @@
         <v>73</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F65" s="13">
         <v>0.51041666666666663</v>
@@ -33672,7 +33648,7 @@
         <v>238</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F66" s="13">
         <v>0.51041666666666663</v>
@@ -33704,7 +33680,7 @@
         <v>239</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F67" s="13">
         <v>0.51041666666666663</v>
@@ -33736,7 +33712,7 @@
         <v>185</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F68" s="13">
         <v>0.51041666666666663</v>
@@ -33768,7 +33744,7 @@
         <v>9</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F69" s="13">
         <v>0.55208333333333337</v>
@@ -33800,7 +33776,7 @@
         <v>17</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F70" s="13">
         <v>0.57291666666666663</v>
@@ -33832,7 +33808,7 @@
         <v>15</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F71" s="13">
         <v>0.59375</v>
@@ -33864,7 +33840,7 @@
         <v>239</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F72" s="13">
         <v>0.61458333333333337</v>
@@ -33896,7 +33872,7 @@
         <v>18</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F73" s="13">
         <v>0.63541666666666663</v>
@@ -33928,7 +33904,7 @@
         <v>9</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F74" s="13">
         <v>0.65625</v>
@@ -33960,7 +33936,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F75" s="13">
         <v>0.65625</v>
@@ -33992,7 +33968,7 @@
         <v>15</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F76" s="13">
         <v>0.65625</v>
@@ -34024,7 +34000,7 @@
         <v>239</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F77" s="13">
         <v>0.65625</v>
@@ -34056,7 +34032,7 @@
         <v>18</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F78" s="13">
         <v>0.65625</v>
@@ -34088,7 +34064,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F79" s="13">
         <v>0.67708333333333337</v>
@@ -34120,7 +34096,7 @@
         <v>58</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F80" s="13">
         <v>0.73958333333333337</v>
@@ -34152,7 +34128,7 @@
         <v>55</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F81" s="13">
         <v>0.76041666666666663</v>
@@ -34184,7 +34160,7 @@
         <v>80</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F82" s="13">
         <v>0.78125</v>
@@ -34216,7 +34192,7 @@
         <v>66</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F83" s="13">
         <v>0.80208333333333337</v>
@@ -34248,7 +34224,7 @@
         <v>66</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F84" s="13">
         <v>0.83333333333333337</v>
@@ -34280,7 +34256,7 @@
         <v>66</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F85" s="13">
         <v>0.85416666666666663</v>
@@ -34312,7 +34288,7 @@
         <v>85</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F86" s="13">
         <v>0.85416666666666663</v>
@@ -34344,7 +34320,7 @@
         <v>85</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F87" s="13">
         <v>0.875</v>
@@ -34376,7 +34352,7 @@
         <v>85</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F88" s="13">
         <v>0.88888888888888884</v>
@@ -34408,7 +34384,7 @@
         <v>85</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F89" s="13">
         <v>0.90277777777777779</v>
@@ -34440,7 +34416,7 @@
         <v>228</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F90" s="13">
         <v>0.65625</v>
@@ -34472,7 +34448,7 @@
         <v>44</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F91" s="13">
         <v>0.67708333333333337</v>
@@ -34504,7 +34480,7 @@
         <v>236</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F92" s="13">
         <v>0.69791666666666663</v>
@@ -34536,7 +34512,7 @@
         <v>226</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F93" s="13">
         <v>0.71875</v>
@@ -34568,7 +34544,7 @@
         <v>237</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F94" s="13">
         <v>0.73958333333333337</v>
@@ -34600,7 +34576,7 @@
         <v>59</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F95" s="13">
         <v>0.76041666666666663</v>
@@ -34632,7 +34608,7 @@
         <v>62</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F96" s="13">
         <v>0.78125</v>
@@ -34664,7 +34640,7 @@
         <v>227</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F97" s="13">
         <v>0.80208333333333337</v>
@@ -34696,7 +34672,7 @@
         <v>67</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F98" s="13">
         <v>0.84375</v>
@@ -34728,7 +34704,7 @@
         <v>240</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F99" s="13">
         <v>0.86458333333333337</v>
@@ -34760,7 +34736,7 @@
         <v>85</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F100" s="13">
         <v>0.88541666666666663</v>
@@ -34792,7 +34768,7 @@
         <v>71</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F101" s="13">
         <v>0.65625</v>
@@ -34824,7 +34800,7 @@
         <v>68</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F102" s="13">
         <v>0.67708333333333337</v>
@@ -34856,7 +34832,7 @@
         <v>66</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F103" s="13">
         <v>0.69791666666666663</v>
@@ -34888,7 +34864,7 @@
         <v>66</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F104" s="13">
         <v>0.71875</v>
@@ -34920,7 +34896,7 @@
         <v>66</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F105" s="13">
         <v>0.73958333333333337</v>
@@ -34952,7 +34928,7 @@
         <v>221</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F106" s="13">
         <v>0.76041666666666663</v>
@@ -34984,7 +34960,7 @@
         <v>222</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F107" s="13">
         <v>0.78125</v>
@@ -35016,7 +34992,7 @@
         <v>85</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F108" s="13">
         <v>0.82291666666666663</v>
@@ -35048,7 +35024,7 @@
         <v>229</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F109" s="13">
         <v>0.84375</v>
@@ -35080,7 +35056,7 @@
         <v>85</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F110" s="13">
         <v>0.86458333333333337</v>
@@ -35112,7 +35088,7 @@
         <v>85</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F111" s="13">
         <v>0.89583333333333337</v>
@@ -35144,7 +35120,7 @@
         <v>230</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F112" s="13">
         <v>0.65625</v>
@@ -35176,7 +35152,7 @@
         <v>220</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F113" s="13">
         <v>0.67708333333333337</v>
@@ -35208,7 +35184,7 @@
         <v>231</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F114" s="13">
         <v>0.69791666666666663</v>
@@ -35240,7 +35216,7 @@
         <v>82</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F115" s="13">
         <v>0.71875</v>
@@ -35272,7 +35248,7 @@
         <v>232</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F116" s="13">
         <v>0.73958333333333337</v>
@@ -35304,7 +35280,7 @@
         <v>233</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F117" s="13">
         <v>0.76041666666666663</v>
@@ -35336,7 +35312,7 @@
         <v>234</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F118" s="13">
         <v>0.78125</v>
@@ -35368,7 +35344,7 @@
         <v>235</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F119" s="13">
         <v>0.80208333333333337</v>
@@ -35400,7 +35376,7 @@
         <v>223</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F120" s="13">
         <v>0.84375</v>
@@ -35432,7 +35408,7 @@
         <v>224</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F121" s="13">
         <v>0.86458333333333337</v>
@@ -35464,7 +35440,7 @@
         <v>225</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F122" s="13">
         <v>0.89583333333333337</v>
@@ -35496,7 +35472,7 @@
         <v>17</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F123" s="13">
         <v>0.65625</v>
@@ -35528,7 +35504,7 @@
         <v>18</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F124" s="13">
         <v>0.65625</v>
@@ -35560,7 +35536,7 @@
         <v>20</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F125" s="13">
         <v>0.65625</v>
@@ -35592,7 +35568,7 @@
         <v>73</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F126" s="13">
         <v>0.65625</v>
@@ -35624,7 +35600,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F127" s="13">
         <v>0.69791666666666663</v>
@@ -35656,7 +35632,7 @@
         <v>12</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F128" s="13">
         <v>0.69791666666666663</v>
@@ -35688,7 +35664,7 @@
         <v>15</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F129" s="13">
         <v>0.69791666666666663</v>
@@ -35720,7 +35696,7 @@
         <v>17</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F130" s="13">
         <v>0.69791666666666663</v>
@@ -35752,7 +35728,7 @@
         <v>18</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F131" s="13">
         <v>0.69791666666666663</v>
@@ -35784,7 +35760,7 @@
         <v>20</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F132" s="13">
         <v>0.69791666666666663</v>
@@ -35816,7 +35792,7 @@
         <v>206</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F133" s="13">
         <v>0.69791666666666663</v>
@@ -35848,7 +35824,7 @@
         <v>73</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F134" s="13">
         <v>0.69791666666666663</v>
@@ -35880,7 +35856,7 @@
         <v>185</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F135" s="13">
         <v>0.69791666666666663</v>
@@ -35912,7 +35888,7 @@
         <v>238</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F136" s="13">
         <v>0.69791666666666663</v>
@@ -35944,7 +35920,7 @@
         <v>239</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F137" s="13">
         <v>0.69791666666666663</v>
@@ -35976,7 +35952,7 @@
         <v>220</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F138" s="13">
         <v>0.75</v>
@@ -36008,7 +35984,7 @@
         <v>226</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F139" s="13">
         <v>0.75</v>
@@ -36040,7 +36016,7 @@
         <v>44</v>
       </c>
       <c r="E140" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F140" s="13">
         <v>0.75</v>
@@ -36072,7 +36048,7 @@
         <v>230</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F141" s="13">
         <v>0.75</v>
@@ -36104,7 +36080,7 @@
         <v>231</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F142" s="13">
         <v>0.75</v>
@@ -36136,7 +36112,7 @@
         <v>232</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F143" s="13">
         <v>0.75</v>
@@ -36168,7 +36144,7 @@
         <v>233</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F144" s="13">
         <v>0.75</v>
@@ -36200,7 +36176,7 @@
         <v>234</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F145" s="13">
         <v>0.75</v>
@@ -36232,7 +36208,7 @@
         <v>55</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F146" s="13">
         <v>0.75</v>
@@ -36264,7 +36240,7 @@
         <v>59</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F147" s="13">
         <v>0.75</v>
@@ -36296,7 +36272,7 @@
         <v>236</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F148" s="13">
         <v>0.75</v>
@@ -36328,7 +36304,7 @@
         <v>237</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F149" s="13">
         <v>0.75</v>
@@ -36360,7 +36336,7 @@
         <v>66</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F150" s="13">
         <v>0.75</v>
@@ -36392,7 +36368,7 @@
         <v>71</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F151" s="13">
         <v>0.75</v>
@@ -36424,7 +36400,7 @@
         <v>82</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F152" s="13">
         <v>0.75</v>
@@ -36456,7 +36432,7 @@
         <v>85</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F153" s="13">
         <v>0.75</v>
@@ -36488,7 +36464,7 @@
         <v>221</v>
       </c>
       <c r="E154" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F154" s="13">
         <v>0.84375</v>
@@ -36520,7 +36496,7 @@
         <v>222</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F155" s="13">
         <v>0.84375</v>
@@ -36552,7 +36528,7 @@
         <v>223</v>
       </c>
       <c r="E156" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F156" s="13">
         <v>0.84375</v>
@@ -36584,7 +36560,7 @@
         <v>224</v>
       </c>
       <c r="E157" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F157" s="13">
         <v>0.84375</v>
@@ -36616,7 +36592,7 @@
         <v>225</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F158" s="13">
         <v>0.84375</v>
@@ -36648,7 +36624,7 @@
         <v>227</v>
       </c>
       <c r="E159" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F159" s="13">
         <v>0.84375</v>
@@ -36680,7 +36656,7 @@
         <v>228</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F160" s="13">
         <v>0.84375</v>
@@ -36712,7 +36688,7 @@
         <v>229</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F161" s="13">
         <v>0.84375</v>
@@ -36744,7 +36720,7 @@
         <v>235</v>
       </c>
       <c r="E162" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F162" s="13">
         <v>0.84375</v>
@@ -36776,7 +36752,7 @@
         <v>58</v>
       </c>
       <c r="E163" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F163" s="13">
         <v>0.84375</v>
@@ -36808,7 +36784,7 @@
         <v>62</v>
       </c>
       <c r="E164" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F164" s="13">
         <v>0.84375</v>
@@ -36840,7 +36816,7 @@
         <v>66</v>
       </c>
       <c r="E165" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F165" s="13">
         <v>0.84375</v>
@@ -36872,7 +36848,7 @@
         <v>67</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F166" s="13">
         <v>0.84375</v>
@@ -36904,7 +36880,7 @@
         <v>68</v>
       </c>
       <c r="E167" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F167" s="13">
         <v>0.84375</v>
@@ -36936,7 +36912,7 @@
         <v>80</v>
       </c>
       <c r="E168" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F168" s="13">
         <v>0.84375</v>
@@ -36968,7 +36944,7 @@
         <v>240</v>
       </c>
       <c r="E169" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F169" s="13">
         <v>0.84375</v>
@@ -37000,7 +36976,7 @@
         <v>85</v>
       </c>
       <c r="E170" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F170" s="13">
         <v>0.84375</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Isadora/Documents/GitHub/rehearsal-schedule/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wsp/Documents/GitHub/rehearsal-schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F056CD-31E9-3C44-A812-97EA6E8AF61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D22DDBF-DA5D-CA40-90CC-E81AB9127B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4120" yWindow="780" windowWidth="27240" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3320" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3320" uniqueCount="323">
   <si>
     <t>class_name</t>
   </si>
@@ -778,18 +778,6 @@
     <t>Onstage warmup for Ballet 4, 5, and 6. Open Ballet may arrive at this time to join the warmup.</t>
   </si>
   <si>
-    <t>Stone and Veil: Ballet Half Dress Rehearsal. 1st Half Saturday &amp; 1st Half Sunday Performances. Dancers arrive with hair and make-up done. Dancers must clean their dressing room and have it approved by a staff member before being allowed to leave the theater. They will remain backstage until the end of their dress rehearsal and will only be released to the lobby once the cleaning has been completed and approved. All students must check in at arrival, and students under 12 must be checked out by an adult on departure.</t>
-  </si>
-  <si>
-    <t>Kids Half Dress Rehearsal. 1st Half Friday &amp; 2nd Half Saturday Performances. Dancers arrive with hair and make-up done. Dancers must clean their dressing room and have it approved by a staff member before being allowed to leave the theater. They will remain backstage until the end of their dress rehearsal and will only be released to the lobby once the cleaning has been completed and approved. All students must check in at arrival, and students under 12 must be checked out by an adult on departure.</t>
-  </si>
-  <si>
-    <t>Teen/Adult Half Dress Rehearsal. 2nd Half Friday &amp; 2nd Half Sunday Performances. Dancers arrive with hair and make-up done. Dancers must clean their dressing room and have it approved by a staff member before being allowed to leave the theater. They will remain backstage until the end of their dress rehearsal and will only be released to the lobby once the cleaning has been completed and approved. All students must check in at arrival, and students under 12 must be checked out by an adult on departure.</t>
-  </si>
-  <si>
-    <t>Kids Half and Teen/Adult Half performance. Dancers arrive with hair and make-up done. Dancers must clean their dressing room and have it approved by a staff member before being allowed to leave the theater. All dancers will remain backstage or in the balcony until the end of the show. No intermission pickups. All students must check in at arrival, and students under 12 must be checked out by an adult on departure.</t>
-  </si>
-  <si>
     <t>Pre-Primary Ballet, Primary Ballet, &amp; Creative Movement arrive in costume with hair and make-up done. After receiving instructions in the lobby, they will be escorted backstage. You may reserve your seat with a jacket or bag at this time.</t>
   </si>
   <si>
@@ -803,12 +791,6 @@
   </si>
   <si>
     <t>Ballet &amp; Kids Performance</t>
-  </si>
-  <si>
-    <t>Ballet Half and Kids Half performance. Dancers arrive with hair and make-up done. Dancers must clean their dressing room and have it approved by a staff member before being allowed to leave the theater. All dancers will remain backstage or in the balcony until the end of the show. No intermission pickups. All students must check in at arrival, and students under 12 must be checked out by an adult on departure.</t>
-  </si>
-  <si>
-    <t>Ballet Half and Teen/Adult Half performance. Dancers arrive with hair and make-up done. Dancers must clean their dressing room and have it approved by a staff member before being allowed to leave the theater. All dancers will remain backstage or in the balcony until the end of the show. No intermission pickups. All students must check in at arrival, and students under 12 must be checked out by an adult on departure.</t>
   </si>
   <si>
     <t>Ballet &amp; Teen/Adult Performance</t>
@@ -1014,12 +996,24 @@
   <si>
     <t>Dark blue jeans and a black or brown belt. Black socks and tap shoes.</t>
   </si>
+  <si>
+    <t>All dancers check in upon arrival​. Arrive with hair and makeup done​. ​Dancers remain backstage or in the balcony until the end​ of the show (no intermission pickups). Dressing rooms must be cleaned and staff-approved before leaving. ​​Dancers under 12 must be checked out by an adult.</t>
+  </si>
+  <si>
+    <t>Ballet Half</t>
+  </si>
+  <si>
+    <t>Kids Half</t>
+  </si>
+  <si>
+    <t>All dancers check in upon arrival​. Arrive with hair and makeup done​. ​Dancers remain backstage or in the balcony until the end​ of the rehearsal. Dressing rooms must be cleaned and staff-approved before leaving. ​​Dancers under 12 must be checked out by an adult.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1081,6 +1075,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1103,7 +1103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1131,8 +1131,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1352,15 +1351,14 @@
   <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" style="19" customWidth="1"/>
-    <col min="4" max="5" width="15.83203125" style="19" customWidth="1"/>
-    <col min="6" max="6" width="107.33203125" style="19" customWidth="1"/>
-    <col min="7" max="7" width="51" style="19" customWidth="1"/>
-    <col min="8" max="8" width="94" style="19" customWidth="1"/>
-    <col min="9" max="23" width="10.5" style="19" customWidth="1"/>
-    <col min="24" max="16384" width="11.1640625" style="19"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="107.33203125" customWidth="1"/>
+    <col min="7" max="7" width="51" customWidth="1"/>
+    <col min="8" max="8" width="94" customWidth="1"/>
+    <col min="9" max="23" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1380,1818 +1378,1818 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F3" t="s">
+        <v>284</v>
+      </c>
+      <c r="G3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="13">
+        <v>0.59375</v>
+      </c>
+      <c r="F4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="13">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F5" t="s">
+        <v>263</v>
+      </c>
+      <c r="G5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0.40625</v>
+      </c>
+      <c r="F6" t="s">
+        <v>305</v>
+      </c>
+      <c r="G6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="13">
+        <v>0.46875</v>
+      </c>
+      <c r="F7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="13">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F8" t="s">
+        <v>265</v>
+      </c>
+      <c r="G8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" t="s">
         <v>266</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F10" t="s">
+        <v>268</v>
+      </c>
+      <c r="G10" t="s">
         <v>267</v>
       </c>
-      <c r="H1" s="19"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="19" t="s">
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F11" t="s">
+        <v>256</v>
+      </c>
+      <c r="G11" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="F12" t="s">
+        <v>297</v>
+      </c>
+      <c r="G12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F13" t="s">
+        <v>269</v>
+      </c>
+      <c r="G13" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0.6875</v>
+      </c>
+      <c r="F14" t="s">
+        <v>286</v>
+      </c>
+      <c r="G14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F15" t="s">
+        <v>278</v>
+      </c>
+      <c r="G15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F16" t="s">
+        <v>287</v>
+      </c>
+      <c r="G16" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>227</v>
+      </c>
+      <c r="B17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="13">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F17" t="s">
+        <v>288</v>
+      </c>
+      <c r="G17" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F18" t="s">
+        <v>299</v>
+      </c>
+      <c r="G18" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F19" t="s">
+        <v>272</v>
+      </c>
+      <c r="G19" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F20" t="s">
+        <v>304</v>
+      </c>
+      <c r="G20" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C21" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D21" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E21" s="13">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>231</v>
+      </c>
+      <c r="B22" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="F22" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F23" t="s">
+        <v>289</v>
+      </c>
+      <c r="G23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="13">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="F24" t="s">
+        <v>290</v>
+      </c>
+      <c r="G24" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>234</v>
+      </c>
+      <c r="B25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F25" t="s">
+        <v>291</v>
+      </c>
+      <c r="G25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>235</v>
+      </c>
+      <c r="B26" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="13">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="F26" t="s">
+        <v>292</v>
+      </c>
+      <c r="G26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C27" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F27" t="s">
+        <v>293</v>
+      </c>
+      <c r="G27" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G28" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0.71875</v>
+      </c>
+      <c r="F29" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="13">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F30" t="s">
+        <v>294</v>
+      </c>
+      <c r="G30" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F31" t="s">
+        <v>295</v>
+      </c>
+      <c r="G31" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G32" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="13">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F33" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F34" t="s">
+        <v>315</v>
+      </c>
+      <c r="G34" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="13">
+        <v>0.6875</v>
+      </c>
+      <c r="F35" t="s">
+        <v>317</v>
+      </c>
+      <c r="G35" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F36" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F37" t="s">
+        <v>277</v>
+      </c>
+      <c r="G37" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="13">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F38" t="s">
+        <v>276</v>
+      </c>
+      <c r="G38" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="E39" s="13">
+        <v>0.625</v>
+      </c>
+      <c r="F39" t="s">
+        <v>282</v>
+      </c>
+      <c r="G39" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="13">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F40" t="s">
+        <v>276</v>
+      </c>
+      <c r="G40" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="20">
-        <v>0.59375</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="E41" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F41" t="s">
+        <v>253</v>
+      </c>
+      <c r="G41" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="20">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="E42" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="F42" t="s">
+        <v>301</v>
+      </c>
+      <c r="G42" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="20">
-        <v>0.40625</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="19" t="s">
+      <c r="E43" s="13"/>
+      <c r="F43" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>240</v>
+      </c>
+      <c r="B44" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F44" t="s">
+        <v>300</v>
+      </c>
+      <c r="G44" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
+        <v>196</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F45" t="s">
+        <v>296</v>
+      </c>
+      <c r="G45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
         <v>187</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="20">
-        <v>0.46875</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="20">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="20">
-        <v>0.8125</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="20">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="20">
-        <v>0.375</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="20">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="20">
-        <v>0.6875</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="20">
-        <v>0.8125</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="D16" s="19" t="s">
+      <c r="D46" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="20">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="20">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="20">
-        <v>0.65625</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="20">
-        <v>0.8125</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="20">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="20">
-        <v>0.375</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="20">
-        <v>0.65625</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="20">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="20">
-        <v>0.75</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="20">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="20">
-        <v>0.65625</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="20">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="20">
-        <v>0.71875</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="20">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="20">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="20">
-        <v>0.65625</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>319</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="20">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="20">
-        <v>0.75</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="20">
-        <v>0.6875</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="20">
-        <v>0.65625</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="20">
-        <v>0.75</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="20">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="20">
-        <v>0.625</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="20">
+      <c r="E46" s="13">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F40" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="D41" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="20">
-        <v>0.375</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43" s="20"/>
-      <c r="F43" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="20">
-        <v>0.8125</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="20">
-        <v>0.65625</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>302</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="20">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>260</v>
+      <c r="F46" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" s="19" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -31600,7 +31598,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F2" s="13">
         <v>0.41666666666666669</v>
@@ -31632,7 +31630,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F3" s="13">
         <v>0.41666666666666669</v>
@@ -31664,7 +31662,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F4" s="13">
         <v>0.41666666666666669</v>
@@ -31696,7 +31694,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F5" s="16">
         <v>0.43055555555555558</v>
@@ -31728,7 +31726,7 @@
         <v>73</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F6" s="16">
         <v>0.4375</v>
@@ -31760,7 +31758,7 @@
         <v>206</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F7" s="16">
         <v>0.4513888888888889</v>
@@ -31792,7 +31790,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F8" s="16">
         <v>0.46180555555555558</v>
@@ -31824,7 +31822,7 @@
         <v>238</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F9" s="16">
         <v>0.47569444444444442</v>
@@ -31856,7 +31854,7 @@
         <v>185</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F10" s="16">
         <v>0.47569444444444442</v>
@@ -31888,7 +31886,7 @@
         <v>17</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F11" s="16">
         <v>0.4861111111111111</v>
@@ -31920,7 +31918,7 @@
         <v>18</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F12" s="16">
         <v>0.4861111111111111</v>
@@ -31952,7 +31950,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F13" s="16">
         <v>0.4861111111111111</v>
@@ -31984,7 +31982,7 @@
         <v>73</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F14" s="16">
         <v>0.4861111111111111</v>
@@ -32016,7 +32014,7 @@
         <v>206</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F15" s="16">
         <v>0.4861111111111111</v>
@@ -32048,7 +32046,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F16" s="16">
         <v>0.4861111111111111</v>
@@ -32080,7 +32078,7 @@
         <v>238</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F17" s="16">
         <v>0.4861111111111111</v>
@@ -32112,7 +32110,7 @@
         <v>185</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F18" s="16">
         <v>0.4861111111111111</v>
@@ -32144,7 +32142,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F19" s="13">
         <v>0.5</v>
@@ -32176,7 +32174,7 @@
         <v>9</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F20" s="13">
         <v>0.54166666666666663</v>
@@ -32208,7 +32206,7 @@
         <v>17</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F21" s="13">
         <v>0.55555555555555558</v>
@@ -32240,7 +32238,7 @@
         <v>15</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F22" s="13">
         <v>0.56597222222222221</v>
@@ -32272,7 +32270,7 @@
         <v>239</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F23" s="13">
         <v>0.57986111111111105</v>
@@ -32304,7 +32302,7 @@
         <v>18</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F24" s="13">
         <v>0.58680555555555558</v>
@@ -32336,7 +32334,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F25" s="13">
         <v>0.59722222222222221</v>
@@ -32368,7 +32366,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F26" s="13">
         <v>0.59722222222222221</v>
@@ -32400,7 +32398,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F27" s="13">
         <v>0.59722222222222221</v>
@@ -32432,7 +32430,7 @@
         <v>239</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F28" s="13">
         <v>0.59722222222222221</v>
@@ -32464,7 +32462,7 @@
         <v>18</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F29" s="13">
         <v>0.59722222222222221</v>
@@ -32496,7 +32494,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F30" s="13">
         <v>0.61458333333333337</v>
@@ -32528,7 +32526,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F31" s="13">
         <v>0.61458333333333337</v>
@@ -32560,7 +32558,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F32" s="13">
         <v>0.61458333333333337</v>
@@ -32592,7 +32590,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F33" s="13">
         <v>0.61458333333333337</v>
@@ -32624,7 +32622,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F34" s="13">
         <v>0.61458333333333337</v>
@@ -32656,7 +32654,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F35" s="13">
         <v>0.61458333333333337</v>
@@ -32688,7 +32686,7 @@
         <v>206</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F36" s="13">
         <v>0.61458333333333337</v>
@@ -32720,7 +32718,7 @@
         <v>73</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F37" s="13">
         <v>0.61458333333333337</v>
@@ -32752,7 +32750,7 @@
         <v>238</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F38" s="13">
         <v>0.61458333333333337</v>
@@ -32784,7 +32782,7 @@
         <v>239</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F39" s="13">
         <v>0.61458333333333337</v>
@@ -32816,7 +32814,7 @@
         <v>185</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F40" s="13">
         <v>0.61458333333333337</v>
@@ -32848,7 +32846,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F41" s="13">
         <v>0.3611111111111111</v>
@@ -32880,7 +32878,7 @@
         <v>18</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F42" s="13">
         <v>0.3611111111111111</v>
@@ -32912,7 +32910,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F43" s="13">
         <v>0.3611111111111111</v>
@@ -32944,7 +32942,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F44" s="13">
         <v>0.39583333333333331</v>
@@ -32976,7 +32974,7 @@
         <v>73</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F45" s="13">
         <v>0.40625</v>
@@ -33008,7 +33006,7 @@
         <v>206</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F46" s="13">
         <v>0.42708333333333331</v>
@@ -33040,7 +33038,7 @@
         <v>12</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F47" s="13">
         <v>0.44791666666666669</v>
@@ -33072,7 +33070,7 @@
         <v>238</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F48" s="13">
         <v>0.46875</v>
@@ -33104,7 +33102,7 @@
         <v>185</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F49" s="13">
         <v>0.46875</v>
@@ -33136,7 +33134,7 @@
         <v>17</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F50" s="13">
         <v>0.5</v>
@@ -33168,7 +33166,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F51" s="13">
         <v>0.5</v>
@@ -33200,7 +33198,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F52" s="13">
         <v>0.5</v>
@@ -33232,7 +33230,7 @@
         <v>73</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F53" s="13">
         <v>0.5</v>
@@ -33264,7 +33262,7 @@
         <v>206</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F54" s="13">
         <v>0.5</v>
@@ -33296,7 +33294,7 @@
         <v>12</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F55" s="13">
         <v>0.5</v>
@@ -33328,7 +33326,7 @@
         <v>238</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F56" s="13">
         <v>0.5</v>
@@ -33360,7 +33358,7 @@
         <v>185</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F57" s="13">
         <v>0.5</v>
@@ -33392,7 +33390,7 @@
         <v>9</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F58" s="13">
         <v>0.51041666666666663</v>
@@ -33424,7 +33422,7 @@
         <v>12</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F59" s="13">
         <v>0.51041666666666663</v>
@@ -33456,7 +33454,7 @@
         <v>15</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F60" s="13">
         <v>0.51041666666666663</v>
@@ -33488,7 +33486,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F61" s="13">
         <v>0.51041666666666663</v>
@@ -33520,7 +33518,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F62" s="13">
         <v>0.51041666666666663</v>
@@ -33552,7 +33550,7 @@
         <v>20</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F63" s="13">
         <v>0.51041666666666663</v>
@@ -33584,7 +33582,7 @@
         <v>206</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F64" s="13">
         <v>0.51041666666666663</v>
@@ -33616,7 +33614,7 @@
         <v>73</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F65" s="13">
         <v>0.51041666666666663</v>
@@ -33648,7 +33646,7 @@
         <v>238</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F66" s="13">
         <v>0.51041666666666663</v>
@@ -33680,7 +33678,7 @@
         <v>239</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F67" s="13">
         <v>0.51041666666666663</v>
@@ -33712,7 +33710,7 @@
         <v>185</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F68" s="13">
         <v>0.51041666666666663</v>
@@ -33744,7 +33742,7 @@
         <v>9</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F69" s="13">
         <v>0.55208333333333337</v>
@@ -33776,7 +33774,7 @@
         <v>17</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F70" s="13">
         <v>0.57291666666666663</v>
@@ -33808,7 +33806,7 @@
         <v>15</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F71" s="13">
         <v>0.59375</v>
@@ -33840,7 +33838,7 @@
         <v>239</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F72" s="13">
         <v>0.61458333333333337</v>
@@ -33872,7 +33870,7 @@
         <v>18</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F73" s="13">
         <v>0.63541666666666663</v>
@@ -33904,7 +33902,7 @@
         <v>9</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F74" s="13">
         <v>0.65625</v>
@@ -33936,7 +33934,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F75" s="13">
         <v>0.65625</v>
@@ -33968,7 +33966,7 @@
         <v>15</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F76" s="13">
         <v>0.65625</v>
@@ -34000,7 +33998,7 @@
         <v>239</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F77" s="13">
         <v>0.65625</v>
@@ -34032,7 +34030,7 @@
         <v>18</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F78" s="13">
         <v>0.65625</v>
@@ -34064,7 +34062,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F79" s="13">
         <v>0.67708333333333337</v>
@@ -34096,7 +34094,7 @@
         <v>58</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F80" s="13">
         <v>0.73958333333333337</v>
@@ -34128,7 +34126,7 @@
         <v>55</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F81" s="13">
         <v>0.76041666666666663</v>
@@ -34160,7 +34158,7 @@
         <v>80</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F82" s="13">
         <v>0.78125</v>
@@ -34192,7 +34190,7 @@
         <v>66</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F83" s="13">
         <v>0.80208333333333337</v>
@@ -34224,7 +34222,7 @@
         <v>66</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F84" s="13">
         <v>0.83333333333333337</v>
@@ -34256,7 +34254,7 @@
         <v>66</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F85" s="13">
         <v>0.85416666666666663</v>
@@ -34288,7 +34286,7 @@
         <v>85</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F86" s="13">
         <v>0.85416666666666663</v>
@@ -34320,7 +34318,7 @@
         <v>85</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F87" s="13">
         <v>0.875</v>
@@ -34352,7 +34350,7 @@
         <v>85</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F88" s="13">
         <v>0.88888888888888884</v>
@@ -34384,7 +34382,7 @@
         <v>85</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F89" s="13">
         <v>0.90277777777777779</v>
@@ -34416,7 +34414,7 @@
         <v>228</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F90" s="13">
         <v>0.65625</v>
@@ -34448,7 +34446,7 @@
         <v>44</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F91" s="13">
         <v>0.67708333333333337</v>
@@ -34480,7 +34478,7 @@
         <v>236</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F92" s="13">
         <v>0.69791666666666663</v>
@@ -34512,7 +34510,7 @@
         <v>226</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F93" s="13">
         <v>0.71875</v>
@@ -34544,7 +34542,7 @@
         <v>237</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F94" s="13">
         <v>0.73958333333333337</v>
@@ -34576,7 +34574,7 @@
         <v>59</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F95" s="13">
         <v>0.76041666666666663</v>
@@ -34608,7 +34606,7 @@
         <v>62</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F96" s="13">
         <v>0.78125</v>
@@ -34640,7 +34638,7 @@
         <v>227</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F97" s="13">
         <v>0.80208333333333337</v>
@@ -34672,7 +34670,7 @@
         <v>67</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F98" s="13">
         <v>0.84375</v>
@@ -34704,7 +34702,7 @@
         <v>240</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F99" s="13">
         <v>0.86458333333333337</v>
@@ -34736,7 +34734,7 @@
         <v>85</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F100" s="13">
         <v>0.88541666666666663</v>
@@ -34768,7 +34766,7 @@
         <v>71</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F101" s="13">
         <v>0.65625</v>
@@ -34800,7 +34798,7 @@
         <v>68</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F102" s="13">
         <v>0.67708333333333337</v>
@@ -34832,7 +34830,7 @@
         <v>66</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F103" s="13">
         <v>0.69791666666666663</v>
@@ -34864,7 +34862,7 @@
         <v>66</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F104" s="13">
         <v>0.71875</v>
@@ -34896,7 +34894,7 @@
         <v>66</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F105" s="13">
         <v>0.73958333333333337</v>
@@ -34928,7 +34926,7 @@
         <v>221</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F106" s="13">
         <v>0.76041666666666663</v>
@@ -34960,7 +34958,7 @@
         <v>222</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F107" s="13">
         <v>0.78125</v>
@@ -34992,7 +34990,7 @@
         <v>85</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F108" s="13">
         <v>0.82291666666666663</v>
@@ -35024,7 +35022,7 @@
         <v>229</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F109" s="13">
         <v>0.84375</v>
@@ -35056,7 +35054,7 @@
         <v>85</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F110" s="13">
         <v>0.86458333333333337</v>
@@ -35088,7 +35086,7 @@
         <v>85</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F111" s="13">
         <v>0.89583333333333337</v>
@@ -35120,7 +35118,7 @@
         <v>230</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F112" s="13">
         <v>0.65625</v>
@@ -35152,7 +35150,7 @@
         <v>220</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F113" s="13">
         <v>0.67708333333333337</v>
@@ -35184,7 +35182,7 @@
         <v>231</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F114" s="13">
         <v>0.69791666666666663</v>
@@ -35216,7 +35214,7 @@
         <v>82</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F115" s="13">
         <v>0.71875</v>
@@ -35248,7 +35246,7 @@
         <v>232</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F116" s="13">
         <v>0.73958333333333337</v>
@@ -35280,7 +35278,7 @@
         <v>233</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F117" s="13">
         <v>0.76041666666666663</v>
@@ -35312,7 +35310,7 @@
         <v>234</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F118" s="13">
         <v>0.78125</v>
@@ -35344,7 +35342,7 @@
         <v>235</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F119" s="13">
         <v>0.80208333333333337</v>
@@ -35376,7 +35374,7 @@
         <v>223</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F120" s="13">
         <v>0.84375</v>
@@ -35408,7 +35406,7 @@
         <v>224</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F121" s="13">
         <v>0.86458333333333337</v>
@@ -35440,7 +35438,7 @@
         <v>225</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F122" s="13">
         <v>0.89583333333333337</v>
@@ -35472,7 +35470,7 @@
         <v>17</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F123" s="13">
         <v>0.65625</v>
@@ -35504,7 +35502,7 @@
         <v>18</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F124" s="13">
         <v>0.65625</v>
@@ -35536,7 +35534,7 @@
         <v>20</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F125" s="13">
         <v>0.65625</v>
@@ -35568,7 +35566,7 @@
         <v>73</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F126" s="13">
         <v>0.65625</v>
@@ -35600,7 +35598,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F127" s="13">
         <v>0.69791666666666663</v>
@@ -35611,8 +35609,8 @@
       <c r="H127" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I127" t="s">
-        <v>246</v>
+      <c r="I127" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J127" s="18" t="s">
         <v>167</v>
@@ -35632,7 +35630,7 @@
         <v>12</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F128" s="13">
         <v>0.69791666666666663</v>
@@ -35643,8 +35641,8 @@
       <c r="H128" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I128" t="s">
-        <v>246</v>
+      <c r="I128" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J128" s="18" t="s">
         <v>167</v>
@@ -35664,7 +35662,7 @@
         <v>15</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F129" s="13">
         <v>0.69791666666666663</v>
@@ -35675,8 +35673,8 @@
       <c r="H129" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I129" t="s">
-        <v>246</v>
+      <c r="I129" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J129" s="18" t="s">
         <v>167</v>
@@ -35696,7 +35694,7 @@
         <v>17</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F130" s="13">
         <v>0.69791666666666663</v>
@@ -35707,8 +35705,8 @@
       <c r="H130" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I130" t="s">
-        <v>246</v>
+      <c r="I130" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J130" s="18" t="s">
         <v>167</v>
@@ -35728,7 +35726,7 @@
         <v>18</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F131" s="13">
         <v>0.69791666666666663</v>
@@ -35739,8 +35737,8 @@
       <c r="H131" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I131" t="s">
-        <v>246</v>
+      <c r="I131" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J131" s="18" t="s">
         <v>167</v>
@@ -35760,7 +35758,7 @@
         <v>20</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F132" s="13">
         <v>0.69791666666666663</v>
@@ -35771,8 +35769,8 @@
       <c r="H132" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I132" t="s">
-        <v>246</v>
+      <c r="I132" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J132" s="18" t="s">
         <v>167</v>
@@ -35792,7 +35790,7 @@
         <v>206</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F133" s="13">
         <v>0.69791666666666663</v>
@@ -35803,8 +35801,8 @@
       <c r="H133" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I133" t="s">
-        <v>246</v>
+      <c r="I133" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J133" s="18" t="s">
         <v>167</v>
@@ -35824,7 +35822,7 @@
         <v>73</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F134" s="13">
         <v>0.69791666666666663</v>
@@ -35835,8 +35833,8 @@
       <c r="H134" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I134" t="s">
-        <v>246</v>
+      <c r="I134" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J134" s="18" t="s">
         <v>167</v>
@@ -35856,7 +35854,7 @@
         <v>185</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F135" s="13">
         <v>0.69791666666666663</v>
@@ -35867,8 +35865,8 @@
       <c r="H135" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I135" t="s">
-        <v>246</v>
+      <c r="I135" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J135" s="18" t="s">
         <v>167</v>
@@ -35888,7 +35886,7 @@
         <v>238</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F136" s="13">
         <v>0.69791666666666663</v>
@@ -35899,8 +35897,8 @@
       <c r="H136" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I136" t="s">
-        <v>246</v>
+      <c r="I136" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J136" s="18" t="s">
         <v>167</v>
@@ -35920,7 +35918,7 @@
         <v>239</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F137" s="13">
         <v>0.69791666666666663</v>
@@ -35931,8 +35929,8 @@
       <c r="H137" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I137" t="s">
-        <v>246</v>
+      <c r="I137" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J137" s="18" t="s">
         <v>167</v>
@@ -35952,7 +35950,7 @@
         <v>220</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F138" s="13">
         <v>0.75</v>
@@ -35963,8 +35961,8 @@
       <c r="H138" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I138" t="s">
-        <v>247</v>
+      <c r="I138" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J138" s="18" t="s">
         <v>167</v>
@@ -35984,7 +35982,7 @@
         <v>226</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F139" s="13">
         <v>0.75</v>
@@ -35995,8 +35993,8 @@
       <c r="H139" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I139" t="s">
-        <v>247</v>
+      <c r="I139" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J139" s="18" t="s">
         <v>167</v>
@@ -36016,7 +36014,7 @@
         <v>44</v>
       </c>
       <c r="E140" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F140" s="13">
         <v>0.75</v>
@@ -36027,8 +36025,8 @@
       <c r="H140" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I140" t="s">
-        <v>247</v>
+      <c r="I140" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J140" s="18" t="s">
         <v>167</v>
@@ -36048,7 +36046,7 @@
         <v>230</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F141" s="13">
         <v>0.75</v>
@@ -36059,8 +36057,8 @@
       <c r="H141" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I141" t="s">
-        <v>247</v>
+      <c r="I141" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J141" s="18" t="s">
         <v>167</v>
@@ -36080,7 +36078,7 @@
         <v>231</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F142" s="13">
         <v>0.75</v>
@@ -36091,8 +36089,8 @@
       <c r="H142" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I142" t="s">
-        <v>247</v>
+      <c r="I142" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J142" s="18" t="s">
         <v>167</v>
@@ -36112,7 +36110,7 @@
         <v>232</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F143" s="13">
         <v>0.75</v>
@@ -36123,8 +36121,8 @@
       <c r="H143" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I143" t="s">
-        <v>247</v>
+      <c r="I143" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J143" s="18" t="s">
         <v>167</v>
@@ -36144,7 +36142,7 @@
         <v>233</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F144" s="13">
         <v>0.75</v>
@@ -36155,8 +36153,8 @@
       <c r="H144" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I144" t="s">
-        <v>247</v>
+      <c r="I144" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J144" s="18" t="s">
         <v>167</v>
@@ -36176,7 +36174,7 @@
         <v>234</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F145" s="13">
         <v>0.75</v>
@@ -36187,8 +36185,8 @@
       <c r="H145" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I145" t="s">
-        <v>247</v>
+      <c r="I145" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J145" s="18" t="s">
         <v>167</v>
@@ -36208,7 +36206,7 @@
         <v>55</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F146" s="13">
         <v>0.75</v>
@@ -36219,8 +36217,8 @@
       <c r="H146" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I146" t="s">
-        <v>247</v>
+      <c r="I146" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J146" s="18" t="s">
         <v>167</v>
@@ -36240,7 +36238,7 @@
         <v>59</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F147" s="13">
         <v>0.75</v>
@@ -36251,8 +36249,8 @@
       <c r="H147" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I147" t="s">
-        <v>247</v>
+      <c r="I147" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J147" s="18" t="s">
         <v>167</v>
@@ -36272,7 +36270,7 @@
         <v>236</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F148" s="13">
         <v>0.75</v>
@@ -36283,8 +36281,8 @@
       <c r="H148" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I148" t="s">
-        <v>247</v>
+      <c r="I148" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J148" s="18" t="s">
         <v>167</v>
@@ -36304,7 +36302,7 @@
         <v>237</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F149" s="13">
         <v>0.75</v>
@@ -36315,8 +36313,8 @@
       <c r="H149" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I149" t="s">
-        <v>247</v>
+      <c r="I149" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J149" s="18" t="s">
         <v>167</v>
@@ -36336,7 +36334,7 @@
         <v>66</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F150" s="13">
         <v>0.75</v>
@@ -36347,8 +36345,8 @@
       <c r="H150" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I150" t="s">
-        <v>247</v>
+      <c r="I150" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J150" s="18" t="s">
         <v>167</v>
@@ -36368,7 +36366,7 @@
         <v>71</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F151" s="13">
         <v>0.75</v>
@@ -36379,8 +36377,8 @@
       <c r="H151" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I151" t="s">
-        <v>247</v>
+      <c r="I151" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J151" s="18" t="s">
         <v>167</v>
@@ -36400,7 +36398,7 @@
         <v>82</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F152" s="13">
         <v>0.75</v>
@@ -36411,8 +36409,8 @@
       <c r="H152" s="13">
         <v>0.72916666666666663</v>
       </c>
-      <c r="I152" t="s">
-        <v>247</v>
+      <c r="I152" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J152" s="18" t="s">
         <v>167</v>
@@ -36432,7 +36430,7 @@
         <v>85</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="F153" s="13">
         <v>0.75</v>
@@ -36443,8 +36441,8 @@
       <c r="H153" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I153" t="s">
-        <v>247</v>
+      <c r="I153" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J153" s="18" t="s">
         <v>167</v>
@@ -36464,7 +36462,7 @@
         <v>221</v>
       </c>
       <c r="E154" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F154" s="13">
         <v>0.84375</v>
@@ -36475,8 +36473,8 @@
       <c r="H154" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I154" t="s">
-        <v>248</v>
+      <c r="I154" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J154" s="18" t="s">
         <v>167</v>
@@ -36496,7 +36494,7 @@
         <v>222</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F155" s="13">
         <v>0.84375</v>
@@ -36507,8 +36505,8 @@
       <c r="H155" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I155" t="s">
-        <v>248</v>
+      <c r="I155" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J155" s="18" t="s">
         <v>167</v>
@@ -36528,7 +36526,7 @@
         <v>223</v>
       </c>
       <c r="E156" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F156" s="13">
         <v>0.84375</v>
@@ -36539,8 +36537,8 @@
       <c r="H156" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I156" t="s">
-        <v>248</v>
+      <c r="I156" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J156" s="18" t="s">
         <v>167</v>
@@ -36560,7 +36558,7 @@
         <v>224</v>
       </c>
       <c r="E157" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F157" s="13">
         <v>0.84375</v>
@@ -36571,8 +36569,8 @@
       <c r="H157" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I157" t="s">
-        <v>248</v>
+      <c r="I157" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J157" s="18" t="s">
         <v>167</v>
@@ -36592,7 +36590,7 @@
         <v>225</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F158" s="13">
         <v>0.84375</v>
@@ -36603,8 +36601,8 @@
       <c r="H158" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I158" t="s">
-        <v>248</v>
+      <c r="I158" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J158" s="18" t="s">
         <v>167</v>
@@ -36624,7 +36622,7 @@
         <v>227</v>
       </c>
       <c r="E159" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F159" s="13">
         <v>0.84375</v>
@@ -36635,8 +36633,8 @@
       <c r="H159" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I159" t="s">
-        <v>248</v>
+      <c r="I159" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J159" s="18" t="s">
         <v>167</v>
@@ -36656,7 +36654,7 @@
         <v>228</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F160" s="13">
         <v>0.84375</v>
@@ -36667,8 +36665,8 @@
       <c r="H160" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I160" t="s">
-        <v>248</v>
+      <c r="I160" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J160" s="18" t="s">
         <v>167</v>
@@ -36688,7 +36686,7 @@
         <v>229</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F161" s="13">
         <v>0.84375</v>
@@ -36699,8 +36697,8 @@
       <c r="H161" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I161" t="s">
-        <v>248</v>
+      <c r="I161" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J161" s="18" t="s">
         <v>167</v>
@@ -36720,7 +36718,7 @@
         <v>235</v>
       </c>
       <c r="E162" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F162" s="13">
         <v>0.84375</v>
@@ -36731,8 +36729,8 @@
       <c r="H162" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I162" t="s">
-        <v>248</v>
+      <c r="I162" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J162" s="18" t="s">
         <v>167</v>
@@ -36752,7 +36750,7 @@
         <v>58</v>
       </c>
       <c r="E163" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F163" s="13">
         <v>0.84375</v>
@@ -36763,8 +36761,8 @@
       <c r="H163" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I163" t="s">
-        <v>248</v>
+      <c r="I163" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J163" s="18" t="s">
         <v>167</v>
@@ -36784,7 +36782,7 @@
         <v>62</v>
       </c>
       <c r="E164" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F164" s="13">
         <v>0.84375</v>
@@ -36795,8 +36793,8 @@
       <c r="H164" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I164" t="s">
-        <v>248</v>
+      <c r="I164" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J164" s="18" t="s">
         <v>167</v>
@@ -36816,7 +36814,7 @@
         <v>66</v>
       </c>
       <c r="E165" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F165" s="13">
         <v>0.84375</v>
@@ -36827,8 +36825,8 @@
       <c r="H165" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I165" t="s">
-        <v>248</v>
+      <c r="I165" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J165" s="18" t="s">
         <v>167</v>
@@ -36848,7 +36846,7 @@
         <v>67</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F166" s="13">
         <v>0.84375</v>
@@ -36859,8 +36857,8 @@
       <c r="H166" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I166" t="s">
-        <v>248</v>
+      <c r="I166" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J166" s="18" t="s">
         <v>167</v>
@@ -36880,7 +36878,7 @@
         <v>68</v>
       </c>
       <c r="E167" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F167" s="13">
         <v>0.84375</v>
@@ -36891,8 +36889,8 @@
       <c r="H167" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I167" t="s">
-        <v>248</v>
+      <c r="I167" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J167" s="18" t="s">
         <v>167</v>
@@ -36912,7 +36910,7 @@
         <v>80</v>
       </c>
       <c r="E168" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F168" s="13">
         <v>0.84375</v>
@@ -36923,8 +36921,8 @@
       <c r="H168" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I168" t="s">
-        <v>248</v>
+      <c r="I168" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J168" s="18" t="s">
         <v>167</v>
@@ -36944,7 +36942,7 @@
         <v>240</v>
       </c>
       <c r="E169" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F169" s="13">
         <v>0.84375</v>
@@ -36955,8 +36953,8 @@
       <c r="H169" s="13">
         <v>0.82291666666666663</v>
       </c>
-      <c r="I169" t="s">
-        <v>248</v>
+      <c r="I169" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J169" s="18" t="s">
         <v>167</v>
@@ -36976,7 +36974,7 @@
         <v>85</v>
       </c>
       <c r="E170" s="15" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
       <c r="F170" s="13">
         <v>0.84375</v>
@@ -36987,8 +36985,8 @@
       <c r="H170" s="13">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I170" t="s">
-        <v>248</v>
+      <c r="I170" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="J170" s="18" t="s">
         <v>167</v>
@@ -37008,7 +37006,7 @@
         <v>220</v>
       </c>
       <c r="E171" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F171" s="13">
         <v>0.75</v>
@@ -37019,8 +37017,8 @@
       <c r="H171" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I171" t="s">
-        <v>249</v>
+      <c r="I171" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J171" s="18" t="s">
         <v>175</v>
@@ -37040,7 +37038,7 @@
         <v>226</v>
       </c>
       <c r="E172" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F172" s="13">
         <v>0.75</v>
@@ -37051,8 +37049,8 @@
       <c r="H172" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I172" t="s">
-        <v>249</v>
+      <c r="I172" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J172" s="18" t="s">
         <v>175</v>
@@ -37072,7 +37070,7 @@
         <v>44</v>
       </c>
       <c r="E173" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F173" s="13">
         <v>0.75</v>
@@ -37083,8 +37081,8 @@
       <c r="H173" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I173" t="s">
-        <v>249</v>
+      <c r="I173" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J173" s="18" t="s">
         <v>175</v>
@@ -37104,7 +37102,7 @@
         <v>230</v>
       </c>
       <c r="E174" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F174" s="13">
         <v>0.75</v>
@@ -37115,8 +37113,8 @@
       <c r="H174" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I174" t="s">
-        <v>249</v>
+      <c r="I174" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J174" s="18" t="s">
         <v>175</v>
@@ -37136,7 +37134,7 @@
         <v>231</v>
       </c>
       <c r="E175" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F175" s="13">
         <v>0.75</v>
@@ -37147,8 +37145,8 @@
       <c r="H175" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I175" t="s">
-        <v>249</v>
+      <c r="I175" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J175" s="18" t="s">
         <v>175</v>
@@ -37168,7 +37166,7 @@
         <v>232</v>
       </c>
       <c r="E176" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F176" s="13">
         <v>0.75</v>
@@ -37179,8 +37177,8 @@
       <c r="H176" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I176" t="s">
-        <v>249</v>
+      <c r="I176" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J176" s="18" t="s">
         <v>175</v>
@@ -37200,7 +37198,7 @@
         <v>233</v>
       </c>
       <c r="E177" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F177" s="13">
         <v>0.75</v>
@@ -37211,8 +37209,8 @@
       <c r="H177" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I177" t="s">
-        <v>249</v>
+      <c r="I177" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J177" s="18" t="s">
         <v>175</v>
@@ -37232,7 +37230,7 @@
         <v>234</v>
       </c>
       <c r="E178" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F178" s="13">
         <v>0.75</v>
@@ -37243,8 +37241,8 @@
       <c r="H178" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I178" t="s">
-        <v>249</v>
+      <c r="I178" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J178" s="18" t="s">
         <v>175</v>
@@ -37264,7 +37262,7 @@
         <v>55</v>
       </c>
       <c r="E179" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F179" s="13">
         <v>0.75</v>
@@ -37275,8 +37273,8 @@
       <c r="H179" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I179" t="s">
-        <v>249</v>
+      <c r="I179" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J179" s="18" t="s">
         <v>175</v>
@@ -37296,7 +37294,7 @@
         <v>59</v>
       </c>
       <c r="E180" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F180" s="13">
         <v>0.75</v>
@@ -37307,8 +37305,8 @@
       <c r="H180" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I180" t="s">
-        <v>249</v>
+      <c r="I180" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J180" s="18" t="s">
         <v>175</v>
@@ -37328,7 +37326,7 @@
         <v>236</v>
       </c>
       <c r="E181" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F181" s="13">
         <v>0.75</v>
@@ -37339,8 +37337,8 @@
       <c r="H181" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I181" t="s">
-        <v>249</v>
+      <c r="I181" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J181" s="18" t="s">
         <v>175</v>
@@ -37360,7 +37358,7 @@
         <v>237</v>
       </c>
       <c r="E182" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F182" s="13">
         <v>0.75</v>
@@ -37371,8 +37369,8 @@
       <c r="H182" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I182" t="s">
-        <v>249</v>
+      <c r="I182" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J182" s="18" t="s">
         <v>175</v>
@@ -37392,7 +37390,7 @@
         <v>66</v>
       </c>
       <c r="E183" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F183" s="13">
         <v>0.75</v>
@@ -37403,8 +37401,8 @@
       <c r="H183" s="13">
         <v>0.69791666666666663</v>
       </c>
-      <c r="I183" t="s">
-        <v>249</v>
+      <c r="I183" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J183" s="18" t="s">
         <v>175</v>
@@ -37424,7 +37422,7 @@
         <v>71</v>
       </c>
       <c r="E184" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F184" s="13">
         <v>0.75</v>
@@ -37435,8 +37433,8 @@
       <c r="H184" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I184" t="s">
-        <v>249</v>
+      <c r="I184" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J184" s="18" t="s">
         <v>175</v>
@@ -37456,7 +37454,7 @@
         <v>82</v>
       </c>
       <c r="E185" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F185" s="13">
         <v>0.75</v>
@@ -37467,8 +37465,8 @@
       <c r="H185" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="I185" t="s">
-        <v>249</v>
+      <c r="I185" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J185" s="18" t="s">
         <v>175</v>
@@ -37488,7 +37486,7 @@
         <v>85</v>
       </c>
       <c r="E186" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F186" s="13">
         <v>0.75</v>
@@ -37499,8 +37497,8 @@
       <c r="H186" s="13">
         <v>0.69791666666666663</v>
       </c>
-      <c r="I186" t="s">
-        <v>249</v>
+      <c r="I186" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J186" s="18" t="s">
         <v>175</v>
@@ -37520,7 +37518,7 @@
         <v>221</v>
       </c>
       <c r="E187" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F187" s="13">
         <v>0.75</v>
@@ -37531,8 +37529,8 @@
       <c r="H187" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I187" t="s">
-        <v>249</v>
+      <c r="I187" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J187" s="18" t="s">
         <v>175</v>
@@ -37552,7 +37550,7 @@
         <v>222</v>
       </c>
       <c r="E188" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F188" s="13">
         <v>0.75</v>
@@ -37563,8 +37561,8 @@
       <c r="H188" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I188" t="s">
-        <v>249</v>
+      <c r="I188" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J188" s="18" t="s">
         <v>175</v>
@@ -37584,7 +37582,7 @@
         <v>223</v>
       </c>
       <c r="E189" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F189" s="13">
         <v>0.75</v>
@@ -37595,8 +37593,8 @@
       <c r="H189" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I189" t="s">
-        <v>249</v>
+      <c r="I189" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J189" s="18" t="s">
         <v>175</v>
@@ -37616,7 +37614,7 @@
         <v>224</v>
       </c>
       <c r="E190" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F190" s="13">
         <v>0.75</v>
@@ -37627,8 +37625,8 @@
       <c r="H190" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I190" t="s">
-        <v>249</v>
+      <c r="I190" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J190" s="18" t="s">
         <v>175</v>
@@ -37648,7 +37646,7 @@
         <v>225</v>
       </c>
       <c r="E191" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F191" s="13">
         <v>0.75</v>
@@ -37659,8 +37657,8 @@
       <c r="H191" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I191" t="s">
-        <v>249</v>
+      <c r="I191" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J191" s="18" t="s">
         <v>175</v>
@@ -37680,7 +37678,7 @@
         <v>227</v>
       </c>
       <c r="E192" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F192" s="13">
         <v>0.75</v>
@@ -37691,8 +37689,8 @@
       <c r="H192" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I192" t="s">
-        <v>249</v>
+      <c r="I192" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J192" s="18" t="s">
         <v>175</v>
@@ -37712,7 +37710,7 @@
         <v>228</v>
       </c>
       <c r="E193" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F193" s="13">
         <v>0.75</v>
@@ -37723,8 +37721,8 @@
       <c r="H193" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I193" t="s">
-        <v>249</v>
+      <c r="I193" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J193" s="18" t="s">
         <v>175</v>
@@ -37744,7 +37742,7 @@
         <v>229</v>
       </c>
       <c r="E194" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F194" s="13">
         <v>0.75</v>
@@ -37755,8 +37753,8 @@
       <c r="H194" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I194" t="s">
-        <v>249</v>
+      <c r="I194" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J194" s="18" t="s">
         <v>175</v>
@@ -37776,7 +37774,7 @@
         <v>235</v>
       </c>
       <c r="E195" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F195" s="13">
         <v>0.75</v>
@@ -37787,8 +37785,8 @@
       <c r="H195" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I195" t="s">
-        <v>249</v>
+      <c r="I195" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J195" s="18" t="s">
         <v>175</v>
@@ -37808,7 +37806,7 @@
         <v>58</v>
       </c>
       <c r="E196" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F196" s="13">
         <v>0.75</v>
@@ -37819,8 +37817,8 @@
       <c r="H196" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I196" t="s">
-        <v>249</v>
+      <c r="I196" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J196" s="18" t="s">
         <v>175</v>
@@ -37840,7 +37838,7 @@
         <v>62</v>
       </c>
       <c r="E197" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F197" s="13">
         <v>0.75</v>
@@ -37851,8 +37849,8 @@
       <c r="H197" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I197" t="s">
-        <v>249</v>
+      <c r="I197" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J197" s="18" t="s">
         <v>175</v>
@@ -37872,7 +37870,7 @@
         <v>67</v>
       </c>
       <c r="E198" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F198" s="13">
         <v>0.75</v>
@@ -37883,8 +37881,8 @@
       <c r="H198" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I198" t="s">
-        <v>249</v>
+      <c r="I198" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J198" s="18" t="s">
         <v>175</v>
@@ -37904,7 +37902,7 @@
         <v>68</v>
       </c>
       <c r="E199" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F199" s="13">
         <v>0.75</v>
@@ -37915,8 +37913,8 @@
       <c r="H199" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I199" t="s">
-        <v>249</v>
+      <c r="I199" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J199" s="18" t="s">
         <v>175</v>
@@ -37936,7 +37934,7 @@
         <v>80</v>
       </c>
       <c r="E200" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F200" s="13">
         <v>0.75</v>
@@ -37947,8 +37945,8 @@
       <c r="H200" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I200" t="s">
-        <v>249</v>
+      <c r="I200" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J200" s="18" t="s">
         <v>175</v>
@@ -37968,7 +37966,7 @@
         <v>240</v>
       </c>
       <c r="E201" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F201" s="13">
         <v>0.75</v>
@@ -37979,8 +37977,8 @@
       <c r="H201" s="13">
         <v>0.71875</v>
       </c>
-      <c r="I201" t="s">
-        <v>249</v>
+      <c r="I201" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J201" s="18" t="s">
         <v>175</v>
@@ -38000,7 +37998,7 @@
         <v>30</v>
       </c>
       <c r="E202" s="15" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F202" s="13">
         <v>0.51041666666666663</v>
@@ -38012,7 +38010,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I202" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J202" s="18" t="s">
         <v>179</v>
@@ -38032,7 +38030,7 @@
         <v>76</v>
       </c>
       <c r="E203" s="15" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F203" s="13">
         <v>0.51041666666666663</v>
@@ -38044,7 +38042,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I203" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J203" s="18" t="s">
         <v>179</v>
@@ -38064,7 +38062,7 @@
         <v>78</v>
       </c>
       <c r="E204" s="15" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F204" s="13">
         <v>0.51041666666666663</v>
@@ -38076,7 +38074,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I204" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J204" s="18" t="s">
         <v>179</v>
@@ -38096,7 +38094,7 @@
         <v>30</v>
       </c>
       <c r="E205" s="15" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F205" s="13">
         <v>0.54166666666666663</v>
@@ -38108,7 +38106,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I205" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J205" s="18" t="s">
         <v>179</v>
@@ -38128,7 +38126,7 @@
         <v>76</v>
       </c>
       <c r="E206" s="15" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F206" s="13">
         <v>0.54166666666666663</v>
@@ -38140,7 +38138,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I206" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J206" s="18" t="s">
         <v>179</v>
@@ -38160,7 +38158,7 @@
         <v>78</v>
       </c>
       <c r="E207" s="15" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F207" s="13">
         <v>0.54166666666666663</v>
@@ -38172,7 +38170,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I207" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="J207" s="18" t="s">
         <v>179</v>
@@ -38192,7 +38190,7 @@
         <v>17</v>
       </c>
       <c r="E208" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F208" s="13">
         <v>0.64583333333333337</v>
@@ -38224,7 +38222,7 @@
         <v>18</v>
       </c>
       <c r="E209" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F209" s="13">
         <v>0.64583333333333337</v>
@@ -38256,7 +38254,7 @@
         <v>20</v>
       </c>
       <c r="E210" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F210" s="13">
         <v>0.64583333333333337</v>
@@ -38288,7 +38286,7 @@
         <v>73</v>
       </c>
       <c r="E211" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F211" s="13">
         <v>0.64583333333333337</v>
@@ -38320,7 +38318,7 @@
         <v>9</v>
       </c>
       <c r="E212" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F212" s="13">
         <v>0.70833333333333337</v>
@@ -38331,8 +38329,8 @@
       <c r="H212" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I212" t="s">
-        <v>255</v>
+      <c r="I212" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J212" s="18" t="s">
         <v>175</v>
@@ -38352,7 +38350,7 @@
         <v>12</v>
       </c>
       <c r="E213" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F213" s="13">
         <v>0.70833333333333337</v>
@@ -38363,8 +38361,8 @@
       <c r="H213" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I213" t="s">
-        <v>255</v>
+      <c r="I213" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J213" s="18" t="s">
         <v>175</v>
@@ -38384,7 +38382,7 @@
         <v>15</v>
       </c>
       <c r="E214" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F214" s="13">
         <v>0.70833333333333337</v>
@@ -38395,8 +38393,8 @@
       <c r="H214" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I214" t="s">
-        <v>255</v>
+      <c r="I214" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J214" s="18" t="s">
         <v>175</v>
@@ -38416,7 +38414,7 @@
         <v>17</v>
       </c>
       <c r="E215" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F215" s="13">
         <v>0.70833333333333337</v>
@@ -38427,8 +38425,8 @@
       <c r="H215" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I215" t="s">
-        <v>255</v>
+      <c r="I215" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J215" s="18" t="s">
         <v>175</v>
@@ -38448,7 +38446,7 @@
         <v>18</v>
       </c>
       <c r="E216" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F216" s="13">
         <v>0.70833333333333337</v>
@@ -38459,8 +38457,8 @@
       <c r="H216" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I216" t="s">
-        <v>255</v>
+      <c r="I216" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J216" s="18" t="s">
         <v>175</v>
@@ -38480,7 +38478,7 @@
         <v>20</v>
       </c>
       <c r="E217" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F217" s="13">
         <v>0.70833333333333337</v>
@@ -38491,8 +38489,8 @@
       <c r="H217" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I217" t="s">
-        <v>255</v>
+      <c r="I217" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J217" s="18" t="s">
         <v>175</v>
@@ -38512,7 +38510,7 @@
         <v>206</v>
       </c>
       <c r="E218" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F218" s="13">
         <v>0.70833333333333337</v>
@@ -38523,8 +38521,8 @@
       <c r="H218" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I218" t="s">
-        <v>255</v>
+      <c r="I218" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J218" s="18" t="s">
         <v>175</v>
@@ -38544,7 +38542,7 @@
         <v>73</v>
       </c>
       <c r="E219" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F219" s="13">
         <v>0.70833333333333337</v>
@@ -38555,8 +38553,8 @@
       <c r="H219" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I219" t="s">
-        <v>255</v>
+      <c r="I219" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J219" s="18" t="s">
         <v>175</v>
@@ -38576,7 +38574,7 @@
         <v>238</v>
       </c>
       <c r="E220" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F220" s="13">
         <v>0.70833333333333337</v>
@@ -38587,8 +38585,8 @@
       <c r="H220" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I220" t="s">
-        <v>255</v>
+      <c r="I220" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J220" s="18" t="s">
         <v>175</v>
@@ -38608,7 +38606,7 @@
         <v>239</v>
       </c>
       <c r="E221" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F221" s="13">
         <v>0.70833333333333337</v>
@@ -38619,8 +38617,8 @@
       <c r="H221" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I221" t="s">
-        <v>255</v>
+      <c r="I221" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J221" s="18" t="s">
         <v>175</v>
@@ -38640,7 +38638,7 @@
         <v>185</v>
       </c>
       <c r="E222" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F222" s="13">
         <v>0.70833333333333337</v>
@@ -38651,8 +38649,8 @@
       <c r="H222" s="13">
         <v>0.66666666666666663</v>
       </c>
-      <c r="I222" t="s">
-        <v>255</v>
+      <c r="I222" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J222" s="18" t="s">
         <v>175</v>
@@ -38672,7 +38670,7 @@
         <v>220</v>
       </c>
       <c r="E223" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F223" s="13">
         <v>0.70833333333333337</v>
@@ -38683,8 +38681,8 @@
       <c r="H223" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I223" t="s">
-        <v>255</v>
+      <c r="I223" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J223" s="18" t="s">
         <v>175</v>
@@ -38704,7 +38702,7 @@
         <v>226</v>
       </c>
       <c r="E224" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F224" s="13">
         <v>0.70833333333333337</v>
@@ -38715,8 +38713,8 @@
       <c r="H224" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I224" t="s">
-        <v>255</v>
+      <c r="I224" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J224" s="18" t="s">
         <v>175</v>
@@ -38736,7 +38734,7 @@
         <v>44</v>
       </c>
       <c r="E225" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F225" s="13">
         <v>0.70833333333333337</v>
@@ -38747,8 +38745,8 @@
       <c r="H225" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I225" t="s">
-        <v>255</v>
+      <c r="I225" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J225" s="18" t="s">
         <v>175</v>
@@ -38768,7 +38766,7 @@
         <v>230</v>
       </c>
       <c r="E226" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F226" s="13">
         <v>0.70833333333333337</v>
@@ -38779,8 +38777,8 @@
       <c r="H226" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I226" t="s">
-        <v>255</v>
+      <c r="I226" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J226" s="18" t="s">
         <v>175</v>
@@ -38800,7 +38798,7 @@
         <v>231</v>
       </c>
       <c r="E227" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F227" s="13">
         <v>0.70833333333333337</v>
@@ -38811,8 +38809,8 @@
       <c r="H227" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I227" t="s">
-        <v>255</v>
+      <c r="I227" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J227" s="18" t="s">
         <v>175</v>
@@ -38832,7 +38830,7 @@
         <v>232</v>
       </c>
       <c r="E228" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F228" s="13">
         <v>0.70833333333333337</v>
@@ -38843,8 +38841,8 @@
       <c r="H228" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I228" t="s">
-        <v>255</v>
+      <c r="I228" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J228" s="18" t="s">
         <v>175</v>
@@ -38864,7 +38862,7 @@
         <v>233</v>
       </c>
       <c r="E229" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F229" s="13">
         <v>0.70833333333333337</v>
@@ -38875,8 +38873,8 @@
       <c r="H229" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I229" t="s">
-        <v>255</v>
+      <c r="I229" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J229" s="18" t="s">
         <v>175</v>
@@ -38896,7 +38894,7 @@
         <v>234</v>
       </c>
       <c r="E230" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F230" s="13">
         <v>0.70833333333333337</v>
@@ -38907,8 +38905,8 @@
       <c r="H230" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I230" t="s">
-        <v>255</v>
+      <c r="I230" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J230" s="18" t="s">
         <v>175</v>
@@ -38928,7 +38926,7 @@
         <v>55</v>
       </c>
       <c r="E231" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F231" s="13">
         <v>0.70833333333333337</v>
@@ -38939,8 +38937,8 @@
       <c r="H231" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I231" t="s">
-        <v>255</v>
+      <c r="I231" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J231" s="18" t="s">
         <v>175</v>
@@ -38960,7 +38958,7 @@
         <v>59</v>
       </c>
       <c r="E232" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F232" s="13">
         <v>0.70833333333333337</v>
@@ -38971,8 +38969,8 @@
       <c r="H232" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I232" t="s">
-        <v>255</v>
+      <c r="I232" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J232" s="18" t="s">
         <v>175</v>
@@ -38992,7 +38990,7 @@
         <v>236</v>
       </c>
       <c r="E233" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F233" s="13">
         <v>0.70833333333333337</v>
@@ -39003,8 +39001,8 @@
       <c r="H233" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I233" t="s">
-        <v>255</v>
+      <c r="I233" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J233" s="18" t="s">
         <v>175</v>
@@ -39024,7 +39022,7 @@
         <v>237</v>
       </c>
       <c r="E234" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F234" s="13">
         <v>0.70833333333333337</v>
@@ -39035,8 +39033,8 @@
       <c r="H234" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I234" t="s">
-        <v>255</v>
+      <c r="I234" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J234" s="18" t="s">
         <v>175</v>
@@ -39056,7 +39054,7 @@
         <v>66</v>
       </c>
       <c r="E235" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F235" s="13">
         <v>0.70833333333333337</v>
@@ -39067,8 +39065,8 @@
       <c r="H235" s="13">
         <v>0.625</v>
       </c>
-      <c r="I235" t="s">
-        <v>255</v>
+      <c r="I235" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J235" s="18" t="s">
         <v>175</v>
@@ -39088,7 +39086,7 @@
         <v>71</v>
       </c>
       <c r="E236" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F236" s="13">
         <v>0.70833333333333337</v>
@@ -39099,8 +39097,8 @@
       <c r="H236" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I236" t="s">
-        <v>255</v>
+      <c r="I236" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J236" s="18" t="s">
         <v>175</v>
@@ -39120,7 +39118,7 @@
         <v>82</v>
       </c>
       <c r="E237" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F237" s="13">
         <v>0.70833333333333337</v>
@@ -39131,8 +39129,8 @@
       <c r="H237" s="13">
         <v>0.67708333333333337</v>
       </c>
-      <c r="I237" t="s">
-        <v>255</v>
+      <c r="I237" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J237" s="18" t="s">
         <v>175</v>
@@ -39152,7 +39150,7 @@
         <v>85</v>
       </c>
       <c r="E238" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F238" s="13">
         <v>0.70833333333333337</v>
@@ -39163,8 +39161,8 @@
       <c r="H238" s="13">
         <v>0.625</v>
       </c>
-      <c r="I238" t="s">
-        <v>255</v>
+      <c r="I238" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J238" s="18" t="s">
         <v>175</v>
@@ -39184,7 +39182,7 @@
         <v>17</v>
       </c>
       <c r="E239" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F239" s="13">
         <v>0.52083333333333337</v>
@@ -39195,8 +39193,8 @@
       <c r="H239" s="13">
         <v>0.5</v>
       </c>
-      <c r="I239" t="s">
-        <v>245</v>
+      <c r="I239" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J239" s="18" t="s">
         <v>175</v>
@@ -39216,7 +39214,7 @@
         <v>18</v>
       </c>
       <c r="E240" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F240" s="13">
         <v>0.52083333333333337</v>
@@ -39227,8 +39225,8 @@
       <c r="H240" s="13">
         <v>0.5</v>
       </c>
-      <c r="I240" t="s">
-        <v>245</v>
+      <c r="I240" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J240" s="18" t="s">
         <v>175</v>
@@ -39248,7 +39246,7 @@
         <v>20</v>
       </c>
       <c r="E241" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F241" s="13">
         <v>0.52083333333333337</v>
@@ -39259,8 +39257,8 @@
       <c r="H241" s="13">
         <v>0.5</v>
       </c>
-      <c r="I241" t="s">
-        <v>245</v>
+      <c r="I241" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J241" s="18" t="s">
         <v>175</v>
@@ -39280,7 +39278,7 @@
         <v>73</v>
       </c>
       <c r="E242" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F242" s="13">
         <v>0.52083333333333337</v>
@@ -39291,8 +39289,8 @@
       <c r="H242" s="13">
         <v>0.5</v>
       </c>
-      <c r="I242" t="s">
-        <v>245</v>
+      <c r="I242" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J242" s="18" t="s">
         <v>175</v>
@@ -39312,7 +39310,7 @@
         <v>9</v>
       </c>
       <c r="E243" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F243" s="13">
         <v>0.58333333333333337</v>
@@ -39323,8 +39321,8 @@
       <c r="H243" s="13">
         <v>0.54166666666666663</v>
       </c>
-      <c r="I243" t="s">
-        <v>256</v>
+      <c r="I243" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J243" s="18" t="s">
         <v>175</v>
@@ -39344,7 +39342,7 @@
         <v>12</v>
       </c>
       <c r="E244" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F244" s="13">
         <v>0.58333333333333337</v>
@@ -39355,8 +39353,8 @@
       <c r="H244" s="13">
         <v>0.54166666666666663</v>
       </c>
-      <c r="I244" t="s">
-        <v>256</v>
+      <c r="I244" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J244" s="18" t="s">
         <v>175</v>
@@ -39376,7 +39374,7 @@
         <v>15</v>
       </c>
       <c r="E245" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F245" s="13">
         <v>0.58333333333333337</v>
@@ -39387,8 +39385,8 @@
       <c r="H245" s="13">
         <v>0.54166666666666663</v>
       </c>
-      <c r="I245" t="s">
-        <v>256</v>
+      <c r="I245" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J245" s="18" t="s">
         <v>175</v>
@@ -39408,7 +39406,7 @@
         <v>17</v>
       </c>
       <c r="E246" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F246" s="13">
         <v>0.58333333333333337</v>
@@ -39419,8 +39417,8 @@
       <c r="H246" s="13">
         <v>0.5</v>
       </c>
-      <c r="I246" t="s">
-        <v>256</v>
+      <c r="I246" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J246" s="18" t="s">
         <v>175</v>
@@ -39440,7 +39438,7 @@
         <v>18</v>
       </c>
       <c r="E247" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F247" s="13">
         <v>0.58333333333333337</v>
@@ -39451,8 +39449,8 @@
       <c r="H247" s="13">
         <v>0.5</v>
       </c>
-      <c r="I247" t="s">
-        <v>256</v>
+      <c r="I247" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J247" s="18" t="s">
         <v>175</v>
@@ -39472,7 +39470,7 @@
         <v>20</v>
       </c>
       <c r="E248" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F248" s="13">
         <v>0.58333333333333337</v>
@@ -39483,8 +39481,8 @@
       <c r="H248" s="13">
         <v>0.5</v>
       </c>
-      <c r="I248" t="s">
-        <v>256</v>
+      <c r="I248" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J248" s="18" t="s">
         <v>175</v>
@@ -39504,7 +39502,7 @@
         <v>206</v>
       </c>
       <c r="E249" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F249" s="13">
         <v>0.58333333333333337</v>
@@ -39515,8 +39513,8 @@
       <c r="H249" s="13">
         <v>0.54166666666666663</v>
       </c>
-      <c r="I249" t="s">
-        <v>256</v>
+      <c r="I249" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J249" s="18" t="s">
         <v>175</v>
@@ -39536,7 +39534,7 @@
         <v>73</v>
       </c>
       <c r="E250" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F250" s="13">
         <v>0.58333333333333337</v>
@@ -39547,8 +39545,8 @@
       <c r="H250" s="13">
         <v>0.54166666666666663</v>
       </c>
-      <c r="I250" t="s">
-        <v>256</v>
+      <c r="I250" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J250" s="18" t="s">
         <v>175</v>
@@ -39568,7 +39566,7 @@
         <v>238</v>
       </c>
       <c r="E251" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F251" s="13">
         <v>0.58333333333333337</v>
@@ -39579,8 +39577,8 @@
       <c r="H251" s="13">
         <v>0.54166666666666663</v>
       </c>
-      <c r="I251" t="s">
-        <v>256</v>
+      <c r="I251" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J251" s="18" t="s">
         <v>175</v>
@@ -39600,7 +39598,7 @@
         <v>239</v>
       </c>
       <c r="E252" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F252" s="13">
         <v>0.58333333333333337</v>
@@ -39611,8 +39609,8 @@
       <c r="H252" s="13">
         <v>0.54166666666666663</v>
       </c>
-      <c r="I252" t="s">
-        <v>256</v>
+      <c r="I252" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J252" s="18" t="s">
         <v>175</v>
@@ -39632,7 +39630,7 @@
         <v>185</v>
       </c>
       <c r="E253" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F253" s="13">
         <v>0.58333333333333337</v>
@@ -39643,8 +39641,8 @@
       <c r="H253" s="13">
         <v>0.54166666666666663</v>
       </c>
-      <c r="I253" t="s">
-        <v>256</v>
+      <c r="I253" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J253" s="18" t="s">
         <v>175</v>
@@ -39664,7 +39662,7 @@
         <v>221</v>
       </c>
       <c r="E254" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F254" s="13">
         <v>0.58333333333333337</v>
@@ -39675,8 +39673,8 @@
       <c r="H254" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I254" t="s">
-        <v>256</v>
+      <c r="I254" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J254" s="18" t="s">
         <v>175</v>
@@ -39696,7 +39694,7 @@
         <v>222</v>
       </c>
       <c r="E255" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F255" s="13">
         <v>0.58333333333333337</v>
@@ -39707,8 +39705,8 @@
       <c r="H255" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I255" t="s">
-        <v>256</v>
+      <c r="I255" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J255" s="18" t="s">
         <v>175</v>
@@ -39728,7 +39726,7 @@
         <v>223</v>
       </c>
       <c r="E256" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F256" s="13">
         <v>0.58333333333333337</v>
@@ -39739,8 +39737,8 @@
       <c r="H256" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I256" t="s">
-        <v>256</v>
+      <c r="I256" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J256" s="18" t="s">
         <v>175</v>
@@ -39760,7 +39758,7 @@
         <v>224</v>
       </c>
       <c r="E257" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F257" s="13">
         <v>0.58333333333333337</v>
@@ -39771,8 +39769,8 @@
       <c r="H257" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I257" t="s">
-        <v>256</v>
+      <c r="I257" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J257" s="18" t="s">
         <v>175</v>
@@ -39792,7 +39790,7 @@
         <v>225</v>
       </c>
       <c r="E258" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F258" s="13">
         <v>0.58333333333333337</v>
@@ -39803,8 +39801,8 @@
       <c r="H258" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I258" t="s">
-        <v>256</v>
+      <c r="I258" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J258" s="18" t="s">
         <v>175</v>
@@ -39824,7 +39822,7 @@
         <v>227</v>
       </c>
       <c r="E259" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F259" s="13">
         <v>0.58333333333333337</v>
@@ -39835,8 +39833,8 @@
       <c r="H259" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I259" t="s">
-        <v>256</v>
+      <c r="I259" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J259" s="18" t="s">
         <v>175</v>
@@ -39856,7 +39854,7 @@
         <v>228</v>
       </c>
       <c r="E260" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F260" s="13">
         <v>0.58333333333333337</v>
@@ -39867,8 +39865,8 @@
       <c r="H260" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I260" t="s">
-        <v>256</v>
+      <c r="I260" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J260" s="18" t="s">
         <v>175</v>
@@ -39888,7 +39886,7 @@
         <v>229</v>
       </c>
       <c r="E261" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F261" s="13">
         <v>0.58333333333333337</v>
@@ -39899,8 +39897,8 @@
       <c r="H261" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I261" t="s">
-        <v>256</v>
+      <c r="I261" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J261" s="18" t="s">
         <v>175</v>
@@ -39920,7 +39918,7 @@
         <v>235</v>
       </c>
       <c r="E262" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F262" s="13">
         <v>0.58333333333333337</v>
@@ -39931,8 +39929,8 @@
       <c r="H262" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I262" t="s">
-        <v>256</v>
+      <c r="I262" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J262" s="18" t="s">
         <v>175</v>
@@ -39952,7 +39950,7 @@
         <v>58</v>
       </c>
       <c r="E263" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F263" s="13">
         <v>0.58333333333333337</v>
@@ -39963,8 +39961,8 @@
       <c r="H263" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I263" t="s">
-        <v>256</v>
+      <c r="I263" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J263" s="18" t="s">
         <v>175</v>
@@ -39984,7 +39982,7 @@
         <v>62</v>
       </c>
       <c r="E264" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F264" s="13">
         <v>0.58333333333333337</v>
@@ -39995,8 +39993,8 @@
       <c r="H264" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I264" t="s">
-        <v>256</v>
+      <c r="I264" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J264" s="18" t="s">
         <v>175</v>
@@ -40016,7 +40014,7 @@
         <v>67</v>
       </c>
       <c r="E265" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F265" s="13">
         <v>0.58333333333333337</v>
@@ -40027,8 +40025,8 @@
       <c r="H265" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I265" t="s">
-        <v>256</v>
+      <c r="I265" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J265" s="18" t="s">
         <v>175</v>
@@ -40048,7 +40046,7 @@
         <v>68</v>
       </c>
       <c r="E266" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F266" s="13">
         <v>0.58333333333333337</v>
@@ -40059,8 +40057,8 @@
       <c r="H266" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I266" t="s">
-        <v>256</v>
+      <c r="I266" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J266" s="18" t="s">
         <v>175</v>
@@ -40080,7 +40078,7 @@
         <v>80</v>
       </c>
       <c r="E267" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F267" s="13">
         <v>0.58333333333333337</v>
@@ -40091,8 +40089,8 @@
       <c r="H267" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I267" t="s">
-        <v>256</v>
+      <c r="I267" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J267" s="18" t="s">
         <v>175</v>
@@ -40112,7 +40110,7 @@
         <v>240</v>
       </c>
       <c r="E268" s="15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F268" s="13">
         <v>0.58333333333333337</v>
@@ -40123,8 +40121,8 @@
       <c r="H268" s="13">
         <v>0.55208333333333337</v>
       </c>
-      <c r="I268" t="s">
-        <v>256</v>
+      <c r="I268" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="J268" s="18" t="s">
         <v>175</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wsp/Documents/GitHub/rehearsal-schedule/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Isadora/Documents/GitHub/rehearsal-schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D22DDBF-DA5D-CA40-90CC-E81AB9127B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8C93B9-4BAC-5D48-B0A8-128F0185E5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4120" yWindow="780" windowWidth="27240" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3320" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3319" uniqueCount="323">
   <si>
     <t>class_name</t>
   </si>
@@ -646,9 +646,6 @@
     <t>Willoughby</t>
   </si>
   <si>
-    <t>Izzy &amp; Bella</t>
-  </si>
-  <si>
     <t>Studio Rehearsal</t>
   </si>
   <si>
@@ -826,9 +823,6 @@
     <t>student_costume</t>
   </si>
   <si>
-    <t>Ballet tights and ballet shoes.</t>
-  </si>
-  <si>
     <t>Dark rose and pale pink gradient dress.</t>
   </si>
   <si>
@@ -863,9 +857,6 @@
   </si>
   <si>
     <t>Tap shoes.</t>
-  </si>
-  <si>
-    <t>Ballet tights and pointe shoes.</t>
   </si>
   <si>
     <t>Pale blue dress with gold trim.</t>
@@ -931,9 +922,6 @@
     <t>Blue sequin dress and tights OR blue sequin shirt and black pants.</t>
   </si>
   <si>
-    <t>Multicolor floral and tulle dress with flower hair clip OR blue short sleeve shirt and green pants.</t>
-  </si>
-  <si>
     <t>Footless skin color tights.</t>
   </si>
   <si>
@@ -946,22 +934,13 @@
     <t>Pale green dress and ballet tights OR pale green sequin vest.</t>
   </si>
   <si>
-    <t>For vest: black pants. Ballet tights and ballet shoes.</t>
-  </si>
-  <si>
     <t>Black leotard and shorts.</t>
-  </si>
-  <si>
-    <t>Yellow sequin dress and black tights OR white button down with a silver sequin vest and black pants.</t>
   </si>
   <si>
     <t>Dark rose dress baby doll dress OR rose button down with white pants. White leotard with mesh skirt OR white button down and white pants.</t>
   </si>
   <si>
     <t>Beige/skin-toned leotard or fitted tank.</t>
-  </si>
-  <si>
-    <t>Black/white/gray Accessories, tank top/leo if applicable. Hip hop sneakers.</t>
   </si>
   <si>
     <t>Blakc socks and hip hop sneakers.</t>
@@ -1007,6 +986,27 @@
   </si>
   <si>
     <t>All dancers check in upon arrival​. Arrive with hair and makeup done​. ​Dancers remain backstage or in the balcony until the end​ of the rehearsal. Dressing rooms must be cleaned and staff-approved before leaving. ​​Dancers under 12 must be checked out by an adult.</t>
+  </si>
+  <si>
+    <t>Pink or skin tone ballet tights and ballet shoes.</t>
+  </si>
+  <si>
+    <t>Multicolor floral and tulle dress with flower hair clip OR blue short sleeve shirt with floral accessory and green pants.</t>
+  </si>
+  <si>
+    <t>Black, white, or grey accessories. Black tank top or leo if needed. Hip hop sneakers.</t>
+  </si>
+  <si>
+    <t>Yellow sequin dress OR white button down with a silver sequin vest and black pants.</t>
+  </si>
+  <si>
+    <t>Black footed tights. Black jazz shoes.</t>
+  </si>
+  <si>
+    <t>Pink or skin tone ballet tights and pointe shoes.</t>
+  </si>
+  <si>
+    <t>For vest: black pants. Pink or skin tone ballet tights and ballet shoes.</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1103,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1132,6 +1132,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1351,14 +1353,15 @@
   <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" customWidth="1"/>
-    <col min="4" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="107.33203125" customWidth="1"/>
-    <col min="7" max="7" width="51" customWidth="1"/>
-    <col min="8" max="8" width="94" customWidth="1"/>
-    <col min="9" max="23" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" style="20" customWidth="1"/>
+    <col min="4" max="5" width="15.83203125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="107.33203125" style="20" customWidth="1"/>
+    <col min="7" max="7" width="51" style="20" customWidth="1"/>
+    <col min="8" max="8" width="94" style="20" customWidth="1"/>
+    <col min="9" max="23" width="10.5" style="20" customWidth="1"/>
+    <col min="24" max="16384" width="11.1640625" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1378,1818 +1381,1814 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="G1" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="21">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="21">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="21">
+        <v>0.59375</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="21">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="H1"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="G5" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="21">
+        <v>0.40625</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="21">
+        <v>0.46875</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="21">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B10" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D10" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="21">
+        <v>0.8125</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="21">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="21">
+        <v>0.375</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="21">
+        <v>0.6875</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="21">
+        <v>0.8125</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="21">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="21">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="21">
+        <v>0.65625</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="21">
+        <v>0.8125</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="21">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D21" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E21" s="21">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="21">
+        <v>0.375</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="21">
+        <v>0.65625</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="21">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F24" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="21">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="21">
+        <v>0.65625</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="21">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="21">
+        <v>0.71875</v>
+      </c>
+      <c r="F29" s="20" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="21">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="21">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="21">
+        <v>0.65625</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="21">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="21">
+        <v>0.6875</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="21">
+        <v>0.65625</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D37" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="21">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F3" t="s">
-        <v>284</v>
-      </c>
-      <c r="G3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E39" s="21">
+        <v>0.625</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="21">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="13">
-        <v>0.59375</v>
-      </c>
-      <c r="F4" t="s">
-        <v>285</v>
-      </c>
-      <c r="G4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E41" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="13">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="E42" s="21">
+        <v>0.375</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0.40625</v>
-      </c>
-      <c r="F6" t="s">
-        <v>305</v>
-      </c>
-      <c r="G6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="F43" s="20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="21">
+        <v>0.8125</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="21">
+        <v>0.65625</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="13">
-        <v>0.46875</v>
-      </c>
-      <c r="F7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="13">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="F8" t="s">
-        <v>265</v>
-      </c>
-      <c r="G8" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" t="s">
-        <v>266</v>
-      </c>
-      <c r="G9" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>221</v>
-      </c>
-      <c r="B10" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F10" t="s">
-        <v>268</v>
-      </c>
-      <c r="G10" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F11" t="s">
-        <v>256</v>
-      </c>
-      <c r="G11" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="F12" t="s">
-        <v>297</v>
-      </c>
-      <c r="G12" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>223</v>
-      </c>
-      <c r="B13" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="13">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F13" t="s">
-        <v>269</v>
-      </c>
-      <c r="G13" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="13">
-        <v>0.6875</v>
-      </c>
-      <c r="F14" t="s">
-        <v>286</v>
-      </c>
-      <c r="G14" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>225</v>
-      </c>
-      <c r="B15" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F15" t="s">
-        <v>278</v>
-      </c>
-      <c r="G15" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>226</v>
-      </c>
-      <c r="B16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D46" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="13">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F16" t="s">
-        <v>287</v>
-      </c>
-      <c r="G16" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>227</v>
-      </c>
-      <c r="B17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="13">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F17" t="s">
-        <v>288</v>
-      </c>
-      <c r="G17" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>228</v>
-      </c>
-      <c r="B18" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F18" t="s">
-        <v>299</v>
-      </c>
-      <c r="G18" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F19" t="s">
-        <v>272</v>
-      </c>
-      <c r="G19" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F20" t="s">
-        <v>304</v>
-      </c>
-      <c r="G20" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F21" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="F22" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>232</v>
-      </c>
-      <c r="B23" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D23" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F23" t="s">
-        <v>289</v>
-      </c>
-      <c r="G23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="13">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F24" t="s">
-        <v>290</v>
-      </c>
-      <c r="G24" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>234</v>
-      </c>
-      <c r="B25" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="F25" t="s">
-        <v>291</v>
-      </c>
-      <c r="G25" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>235</v>
-      </c>
-      <c r="B26" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="13">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="F26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F27" t="s">
-        <v>293</v>
-      </c>
-      <c r="G27" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="13">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F28" t="s">
-        <v>280</v>
-      </c>
-      <c r="G28" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="13">
-        <v>0.71875</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E46" s="21">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F46" s="20" t="s">
         <v>253</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="13">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="F30" t="s">
-        <v>294</v>
-      </c>
-      <c r="G30" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>236</v>
-      </c>
-      <c r="B31" t="s">
-        <v>193</v>
-      </c>
-      <c r="D31" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="13">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F31" t="s">
-        <v>295</v>
-      </c>
-      <c r="G31" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>237</v>
-      </c>
-      <c r="B32" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F32" t="s">
-        <v>313</v>
-      </c>
-      <c r="G32" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="13">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F33" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D34" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="F34" t="s">
-        <v>315</v>
-      </c>
-      <c r="G34" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="13">
-        <v>0.6875</v>
-      </c>
-      <c r="F35" t="s">
-        <v>317</v>
-      </c>
-      <c r="G35" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F36" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="F37" t="s">
-        <v>277</v>
-      </c>
-      <c r="G37" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>238</v>
-      </c>
-      <c r="B38" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="13">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F38" t="s">
-        <v>276</v>
-      </c>
-      <c r="G38" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>239</v>
-      </c>
-      <c r="B39" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="13">
-        <v>0.625</v>
-      </c>
-      <c r="F39" t="s">
-        <v>282</v>
-      </c>
-      <c r="G39" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" t="s">
-        <v>187</v>
-      </c>
-      <c r="D40" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="13">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F40" t="s">
-        <v>276</v>
-      </c>
-      <c r="G40" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" t="s">
-        <v>194</v>
-      </c>
-      <c r="C41" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F41" t="s">
-        <v>253</v>
-      </c>
-      <c r="G41" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C42" t="s">
-        <v>202</v>
-      </c>
-      <c r="D42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="13">
-        <v>0.375</v>
-      </c>
-      <c r="F42" t="s">
-        <v>301</v>
-      </c>
-      <c r="G42" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>240</v>
-      </c>
-      <c r="B44" t="s">
-        <v>193</v>
-      </c>
-      <c r="D44" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="13">
-        <v>0.8125</v>
-      </c>
-      <c r="F44" t="s">
-        <v>300</v>
-      </c>
-      <c r="G44" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="13">
-        <v>0.65625</v>
-      </c>
-      <c r="F45" t="s">
-        <v>296</v>
-      </c>
-      <c r="G45" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="13">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F46" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="49" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" s="20" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -31586,19 +31585,19 @@
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B2" s="14">
         <v>46144</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F2" s="13">
         <v>0.41666666666666669</v>
@@ -31610,27 +31609,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B3" s="14">
         <v>46144</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F3" s="13">
         <v>0.41666666666666669</v>
@@ -31642,27 +31641,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B4" s="14">
         <v>46144</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F4" s="13">
         <v>0.41666666666666669</v>
@@ -31674,27 +31673,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B5" s="14">
         <v>46144</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F5" s="16">
         <v>0.43055555555555558</v>
@@ -31706,27 +31705,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B6" s="14">
         <v>46144</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D6" t="s">
         <v>73</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F6" s="16">
         <v>0.4375</v>
@@ -31738,27 +31737,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B7" s="14">
         <v>46144</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F7" s="16">
         <v>0.4513888888888889</v>
@@ -31770,27 +31769,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="14">
         <v>46144</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F8" s="16">
         <v>0.46180555555555558</v>
@@ -31802,27 +31801,27 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="I8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B9" s="14">
         <v>46144</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F9" s="16">
         <v>0.47569444444444442</v>
@@ -31834,27 +31833,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B10" s="14">
         <v>46144</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D10" t="s">
         <v>185</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F10" s="16">
         <v>0.47569444444444442</v>
@@ -31866,27 +31865,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B11" s="14">
         <v>46144</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F11" s="16">
         <v>0.4861111111111111</v>
@@ -31898,27 +31897,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B12" s="14">
         <v>46144</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F12" s="16">
         <v>0.4861111111111111</v>
@@ -31930,27 +31929,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B13" s="14">
         <v>46144</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F13" s="16">
         <v>0.4861111111111111</v>
@@ -31962,27 +31961,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B14" s="14">
         <v>46144</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D14" t="s">
         <v>73</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F14" s="16">
         <v>0.4861111111111111</v>
@@ -31994,27 +31993,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B15" s="14">
         <v>46144</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F15" s="16">
         <v>0.4861111111111111</v>
@@ -32026,27 +32025,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J15" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B16" s="14">
         <v>46144</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F16" s="16">
         <v>0.4861111111111111</v>
@@ -32058,27 +32057,27 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="I16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" s="14">
         <v>46144</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F17" s="16">
         <v>0.4861111111111111</v>
@@ -32090,27 +32089,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I17" t="s">
+        <v>214</v>
+      </c>
+      <c r="J17" s="17" t="s">
         <v>215</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B18" s="14">
         <v>46144</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D18" t="s">
         <v>185</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F18" s="16">
         <v>0.4861111111111111</v>
@@ -32122,27 +32121,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B19" s="14">
         <v>46144</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D19" t="s">
         <v>20</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F19" s="13">
         <v>0.5</v>
@@ -32154,27 +32153,27 @@
         <v>0.39930555555555558</v>
       </c>
       <c r="I19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B20" s="14">
         <v>46144</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F20" s="13">
         <v>0.54166666666666663</v>
@@ -32186,27 +32185,27 @@
         <v>0.53125</v>
       </c>
       <c r="I20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B21" s="14">
         <v>46144</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D21" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F21" s="13">
         <v>0.55555555555555558</v>
@@ -32218,27 +32217,27 @@
         <v>0.53125</v>
       </c>
       <c r="I21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B22" s="14">
         <v>46144</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F22" s="13">
         <v>0.56597222222222221</v>
@@ -32250,27 +32249,27 @@
         <v>0.53125</v>
       </c>
       <c r="I22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B23" s="14">
         <v>46144</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F23" s="13">
         <v>0.57986111111111105</v>
@@ -32282,27 +32281,27 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="I23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B24" s="14">
         <v>46144</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F24" s="13">
         <v>0.58680555555555558</v>
@@ -32314,27 +32313,27 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="I24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B25" s="14">
         <v>46144</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F25" s="13">
         <v>0.59722222222222221</v>
@@ -32346,27 +32345,27 @@
         <v>0.53125</v>
       </c>
       <c r="I25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B26" s="14">
         <v>46144</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F26" s="13">
         <v>0.59722222222222221</v>
@@ -32378,27 +32377,27 @@
         <v>0.53125</v>
       </c>
       <c r="I26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B27" s="14">
         <v>46144</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D27" t="s">
         <v>15</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F27" s="13">
         <v>0.59722222222222221</v>
@@ -32410,27 +32409,27 @@
         <v>0.53125</v>
       </c>
       <c r="I27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B28" s="14">
         <v>46144</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F28" s="13">
         <v>0.59722222222222221</v>
@@ -32442,27 +32441,27 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="I28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B29" s="14">
         <v>46144</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F29" s="13">
         <v>0.59722222222222221</v>
@@ -32474,27 +32473,27 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="I29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B30" s="14">
         <v>46144</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F30" s="13">
         <v>0.61458333333333337</v>
@@ -32506,27 +32505,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B31" s="14">
         <v>46144</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F31" s="13">
         <v>0.61458333333333337</v>
@@ -32538,27 +32537,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I31" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B32" s="14">
         <v>46144</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F32" s="13">
         <v>0.61458333333333337</v>
@@ -32570,27 +32569,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B33" s="14">
         <v>46144</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F33" s="13">
         <v>0.61458333333333337</v>
@@ -32602,27 +32601,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B34" s="14">
         <v>46144</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F34" s="13">
         <v>0.61458333333333337</v>
@@ -32634,27 +32633,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B35" s="14">
         <v>46144</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D35" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F35" s="13">
         <v>0.61458333333333337</v>
@@ -32666,27 +32665,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I35" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B36" s="14">
         <v>46144</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D36" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F36" s="13">
         <v>0.61458333333333337</v>
@@ -32698,27 +32697,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B37" s="14">
         <v>46144</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D37" t="s">
         <v>73</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F37" s="13">
         <v>0.61458333333333337</v>
@@ -32730,27 +32729,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B38" s="14">
         <v>46144</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F38" s="13">
         <v>0.61458333333333337</v>
@@ -32762,27 +32761,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B39" s="14">
         <v>46144</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D39" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F39" s="13">
         <v>0.61458333333333337</v>
@@ -32794,27 +32793,27 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B40" s="14">
         <v>46144</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D40" t="s">
         <v>185</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F40" s="13">
         <v>0.61458333333333337</v>
@@ -32826,10 +32825,10 @@
         <v>0.60763888888888895</v>
       </c>
       <c r="I40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -32846,7 +32845,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F41" s="13">
         <v>0.3611111111111111</v>
@@ -32858,7 +32857,7 @@
         <v>0.3611111111111111</v>
       </c>
       <c r="I41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J41" s="18" t="s">
         <v>100</v>
@@ -32878,7 +32877,7 @@
         <v>18</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F42" s="13">
         <v>0.3611111111111111</v>
@@ -32890,7 +32889,7 @@
         <v>0.3611111111111111</v>
       </c>
       <c r="I42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J42" s="18" t="s">
         <v>100</v>
@@ -32910,7 +32909,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F43" s="13">
         <v>0.3611111111111111</v>
@@ -32922,7 +32921,7 @@
         <v>0.3611111111111111</v>
       </c>
       <c r="I43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J43" s="18" t="s">
         <v>100</v>
@@ -32942,7 +32941,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F44" s="13">
         <v>0.39583333333333331</v>
@@ -32974,7 +32973,7 @@
         <v>73</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F45" s="13">
         <v>0.40625</v>
@@ -33003,10 +33002,10 @@
         <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F46" s="13">
         <v>0.42708333333333331</v>
@@ -33038,7 +33037,7 @@
         <v>12</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F47" s="13">
         <v>0.44791666666666669</v>
@@ -33067,10 +33066,10 @@
         <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F48" s="13">
         <v>0.46875</v>
@@ -33102,7 +33101,7 @@
         <v>185</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F49" s="13">
         <v>0.46875</v>
@@ -33134,7 +33133,7 @@
         <v>17</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F50" s="13">
         <v>0.5</v>
@@ -33146,7 +33145,7 @@
         <v>0.5</v>
       </c>
       <c r="I50" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J50" s="18" t="s">
         <v>100</v>
@@ -33166,7 +33165,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F51" s="13">
         <v>0.5</v>
@@ -33178,7 +33177,7 @@
         <v>0.5</v>
       </c>
       <c r="I51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J51" s="18" t="s">
         <v>100</v>
@@ -33198,7 +33197,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F52" s="13">
         <v>0.5</v>
@@ -33210,7 +33209,7 @@
         <v>0.5</v>
       </c>
       <c r="I52" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J52" s="18" t="s">
         <v>100</v>
@@ -33230,7 +33229,7 @@
         <v>73</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F53" s="13">
         <v>0.5</v>
@@ -33242,7 +33241,7 @@
         <v>0.5</v>
       </c>
       <c r="I53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J53" s="18" t="s">
         <v>100</v>
@@ -33259,10 +33258,10 @@
         <v>97</v>
       </c>
       <c r="D54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F54" s="13">
         <v>0.5</v>
@@ -33274,7 +33273,7 @@
         <v>0.5</v>
       </c>
       <c r="I54" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J54" s="18" t="s">
         <v>100</v>
@@ -33294,7 +33293,7 @@
         <v>12</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F55" s="13">
         <v>0.5</v>
@@ -33306,7 +33305,7 @@
         <v>0.5</v>
       </c>
       <c r="I55" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J55" s="18" t="s">
         <v>100</v>
@@ -33323,10 +33322,10 @@
         <v>97</v>
       </c>
       <c r="D56" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F56" s="13">
         <v>0.5</v>
@@ -33338,7 +33337,7 @@
         <v>0.5</v>
       </c>
       <c r="I56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J56" s="18" t="s">
         <v>100</v>
@@ -33358,7 +33357,7 @@
         <v>185</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F57" s="13">
         <v>0.5</v>
@@ -33370,7 +33369,7 @@
         <v>0.5</v>
       </c>
       <c r="I57" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J57" s="18" t="s">
         <v>100</v>
@@ -33390,7 +33389,7 @@
         <v>9</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F58" s="13">
         <v>0.51041666666666663</v>
@@ -33402,7 +33401,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I58" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J58" s="18" t="s">
         <v>100</v>
@@ -33422,7 +33421,7 @@
         <v>12</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F59" s="13">
         <v>0.51041666666666663</v>
@@ -33434,7 +33433,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I59" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J59" s="18" t="s">
         <v>100</v>
@@ -33454,7 +33453,7 @@
         <v>15</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F60" s="13">
         <v>0.51041666666666663</v>
@@ -33466,7 +33465,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I60" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J60" s="18" t="s">
         <v>100</v>
@@ -33486,7 +33485,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F61" s="13">
         <v>0.51041666666666663</v>
@@ -33498,7 +33497,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J61" s="18" t="s">
         <v>100</v>
@@ -33518,7 +33517,7 @@
         <v>18</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F62" s="13">
         <v>0.51041666666666663</v>
@@ -33530,7 +33529,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J62" s="18" t="s">
         <v>100</v>
@@ -33550,7 +33549,7 @@
         <v>20</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F63" s="13">
         <v>0.51041666666666663</v>
@@ -33562,7 +33561,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J63" s="18" t="s">
         <v>100</v>
@@ -33579,10 +33578,10 @@
         <v>97</v>
       </c>
       <c r="D64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F64" s="13">
         <v>0.51041666666666663</v>
@@ -33594,7 +33593,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I64" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J64" s="18" t="s">
         <v>100</v>
@@ -33614,7 +33613,7 @@
         <v>73</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F65" s="13">
         <v>0.51041666666666663</v>
@@ -33626,7 +33625,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I65" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J65" s="18" t="s">
         <v>100</v>
@@ -33643,10 +33642,10 @@
         <v>97</v>
       </c>
       <c r="D66" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F66" s="13">
         <v>0.51041666666666663</v>
@@ -33658,7 +33657,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I66" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J66" s="18" t="s">
         <v>100</v>
@@ -33675,10 +33674,10 @@
         <v>97</v>
       </c>
       <c r="D67" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F67" s="13">
         <v>0.51041666666666663</v>
@@ -33690,7 +33689,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I67" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J67" s="18" t="s">
         <v>100</v>
@@ -33710,7 +33709,7 @@
         <v>185</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F68" s="13">
         <v>0.51041666666666663</v>
@@ -33722,7 +33721,7 @@
         <v>0.51041666666666663</v>
       </c>
       <c r="I68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J68" s="18" t="s">
         <v>100</v>
@@ -33742,7 +33741,7 @@
         <v>9</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F69" s="13">
         <v>0.55208333333333337</v>
@@ -33774,7 +33773,7 @@
         <v>17</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F70" s="13">
         <v>0.57291666666666663</v>
@@ -33806,7 +33805,7 @@
         <v>15</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F71" s="13">
         <v>0.59375</v>
@@ -33835,10 +33834,10 @@
         <v>97</v>
       </c>
       <c r="D72" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F72" s="13">
         <v>0.61458333333333337</v>
@@ -33870,7 +33869,7 @@
         <v>18</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F73" s="13">
         <v>0.63541666666666663</v>
@@ -33902,7 +33901,7 @@
         <v>9</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F74" s="13">
         <v>0.65625</v>
@@ -33914,7 +33913,7 @@
         <v>0.65625</v>
       </c>
       <c r="I74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J74" s="18" t="s">
         <v>100</v>
@@ -33934,7 +33933,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F75" s="13">
         <v>0.65625</v>
@@ -33946,7 +33945,7 @@
         <v>0.65625</v>
       </c>
       <c r="I75" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J75" s="18" t="s">
         <v>100</v>
@@ -33966,7 +33965,7 @@
         <v>15</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F76" s="13">
         <v>0.65625</v>
@@ -33978,7 +33977,7 @@
         <v>0.65625</v>
       </c>
       <c r="I76" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J76" s="18" t="s">
         <v>100</v>
@@ -33995,10 +33994,10 @@
         <v>97</v>
       </c>
       <c r="D77" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F77" s="13">
         <v>0.65625</v>
@@ -34010,7 +34009,7 @@
         <v>0.65625</v>
       </c>
       <c r="I77" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J77" s="18" t="s">
         <v>100</v>
@@ -34030,7 +34029,7 @@
         <v>18</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F78" s="13">
         <v>0.65625</v>
@@ -34042,7 +34041,7 @@
         <v>0.65625</v>
       </c>
       <c r="I78" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J78" s="18" t="s">
         <v>100</v>
@@ -34062,7 +34061,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F79" s="13">
         <v>0.67708333333333337</v>
@@ -34074,7 +34073,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I79" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J79" s="18" t="s">
         <v>100</v>
@@ -34094,7 +34093,7 @@
         <v>58</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F80" s="13">
         <v>0.73958333333333337</v>
@@ -34126,7 +34125,7 @@
         <v>55</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F81" s="13">
         <v>0.76041666666666663</v>
@@ -34158,7 +34157,7 @@
         <v>80</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F82" s="13">
         <v>0.78125</v>
@@ -34190,7 +34189,7 @@
         <v>66</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F83" s="13">
         <v>0.80208333333333337</v>
@@ -34222,7 +34221,7 @@
         <v>66</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F84" s="13">
         <v>0.83333333333333337</v>
@@ -34254,7 +34253,7 @@
         <v>66</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F85" s="13">
         <v>0.85416666666666663</v>
@@ -34286,7 +34285,7 @@
         <v>85</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F86" s="13">
         <v>0.85416666666666663</v>
@@ -34318,7 +34317,7 @@
         <v>85</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F87" s="13">
         <v>0.875</v>
@@ -34350,7 +34349,7 @@
         <v>85</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F88" s="13">
         <v>0.88888888888888884</v>
@@ -34382,7 +34381,7 @@
         <v>85</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F89" s="13">
         <v>0.90277777777777779</v>
@@ -34411,10 +34410,10 @@
         <v>97</v>
       </c>
       <c r="D90" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F90" s="13">
         <v>0.65625</v>
@@ -34446,7 +34445,7 @@
         <v>44</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F91" s="13">
         <v>0.67708333333333337</v>
@@ -34475,10 +34474,10 @@
         <v>97</v>
       </c>
       <c r="D92" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F92" s="13">
         <v>0.69791666666666663</v>
@@ -34507,10 +34506,10 @@
         <v>97</v>
       </c>
       <c r="D93" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F93" s="13">
         <v>0.71875</v>
@@ -34539,10 +34538,10 @@
         <v>97</v>
       </c>
       <c r="D94" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F94" s="13">
         <v>0.73958333333333337</v>
@@ -34574,7 +34573,7 @@
         <v>59</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F95" s="13">
         <v>0.76041666666666663</v>
@@ -34606,7 +34605,7 @@
         <v>62</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F96" s="13">
         <v>0.78125</v>
@@ -34635,10 +34634,10 @@
         <v>97</v>
       </c>
       <c r="D97" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F97" s="13">
         <v>0.80208333333333337</v>
@@ -34670,7 +34669,7 @@
         <v>67</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F98" s="13">
         <v>0.84375</v>
@@ -34699,10 +34698,10 @@
         <v>97</v>
       </c>
       <c r="D99" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F99" s="13">
         <v>0.86458333333333337</v>
@@ -34734,7 +34733,7 @@
         <v>85</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F100" s="13">
         <v>0.88541666666666663</v>
@@ -34766,7 +34765,7 @@
         <v>71</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F101" s="13">
         <v>0.65625</v>
@@ -34798,7 +34797,7 @@
         <v>68</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F102" s="13">
         <v>0.67708333333333337</v>
@@ -34830,7 +34829,7 @@
         <v>66</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F103" s="13">
         <v>0.69791666666666663</v>
@@ -34862,7 +34861,7 @@
         <v>66</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F104" s="13">
         <v>0.71875</v>
@@ -34894,7 +34893,7 @@
         <v>66</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F105" s="13">
         <v>0.73958333333333337</v>
@@ -34923,10 +34922,10 @@
         <v>97</v>
       </c>
       <c r="D106" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F106" s="13">
         <v>0.76041666666666663</v>
@@ -34955,10 +34954,10 @@
         <v>97</v>
       </c>
       <c r="D107" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F107" s="13">
         <v>0.78125</v>
@@ -34990,7 +34989,7 @@
         <v>85</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F108" s="13">
         <v>0.82291666666666663</v>
@@ -35019,10 +35018,10 @@
         <v>97</v>
       </c>
       <c r="D109" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F109" s="13">
         <v>0.84375</v>
@@ -35054,7 +35053,7 @@
         <v>85</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F110" s="13">
         <v>0.86458333333333337</v>
@@ -35086,7 +35085,7 @@
         <v>85</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F111" s="13">
         <v>0.89583333333333337</v>
@@ -35115,10 +35114,10 @@
         <v>97</v>
       </c>
       <c r="D112" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F112" s="13">
         <v>0.65625</v>
@@ -35147,10 +35146,10 @@
         <v>97</v>
       </c>
       <c r="D113" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F113" s="13">
         <v>0.67708333333333337</v>
@@ -35179,10 +35178,10 @@
         <v>97</v>
       </c>
       <c r="D114" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F114" s="13">
         <v>0.69791666666666663</v>
@@ -35214,7 +35213,7 @@
         <v>82</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F115" s="13">
         <v>0.71875</v>
@@ -35243,10 +35242,10 @@
         <v>97</v>
       </c>
       <c r="D116" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F116" s="13">
         <v>0.73958333333333337</v>
@@ -35275,10 +35274,10 @@
         <v>97</v>
       </c>
       <c r="D117" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F117" s="13">
         <v>0.76041666666666663</v>
@@ -35307,10 +35306,10 @@
         <v>97</v>
       </c>
       <c r="D118" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F118" s="13">
         <v>0.78125</v>
@@ -35339,10 +35338,10 @@
         <v>97</v>
       </c>
       <c r="D119" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F119" s="13">
         <v>0.80208333333333337</v>
@@ -35371,10 +35370,10 @@
         <v>97</v>
       </c>
       <c r="D120" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F120" s="13">
         <v>0.84375</v>
@@ -35403,10 +35402,10 @@
         <v>97</v>
       </c>
       <c r="D121" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F121" s="13">
         <v>0.86458333333333337</v>
@@ -35435,10 +35434,10 @@
         <v>97</v>
       </c>
       <c r="D122" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F122" s="13">
         <v>0.89583333333333337</v>
@@ -35470,7 +35469,7 @@
         <v>17</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F123" s="13">
         <v>0.65625</v>
@@ -35482,7 +35481,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I123" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J123" s="18" t="s">
         <v>167</v>
@@ -35502,7 +35501,7 @@
         <v>18</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F124" s="13">
         <v>0.65625</v>
@@ -35514,7 +35513,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I124" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J124" s="18" t="s">
         <v>167</v>
@@ -35534,7 +35533,7 @@
         <v>20</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F125" s="13">
         <v>0.65625</v>
@@ -35546,7 +35545,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I125" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J125" s="18" t="s">
         <v>167</v>
@@ -35566,7 +35565,7 @@
         <v>73</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F126" s="13">
         <v>0.65625</v>
@@ -35578,7 +35577,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I126" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J126" s="18" t="s">
         <v>167</v>
@@ -35598,7 +35597,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F127" s="13">
         <v>0.69791666666666663</v>
@@ -35610,7 +35609,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I127" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J127" s="18" t="s">
         <v>167</v>
@@ -35630,7 +35629,7 @@
         <v>12</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F128" s="13">
         <v>0.69791666666666663</v>
@@ -35642,7 +35641,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I128" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J128" s="18" t="s">
         <v>167</v>
@@ -35662,7 +35661,7 @@
         <v>15</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F129" s="13">
         <v>0.69791666666666663</v>
@@ -35674,7 +35673,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I129" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J129" s="18" t="s">
         <v>167</v>
@@ -35694,7 +35693,7 @@
         <v>17</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F130" s="13">
         <v>0.69791666666666663</v>
@@ -35706,7 +35705,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I130" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J130" s="18" t="s">
         <v>167</v>
@@ -35726,7 +35725,7 @@
         <v>18</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F131" s="13">
         <v>0.69791666666666663</v>
@@ -35738,7 +35737,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I131" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J131" s="18" t="s">
         <v>167</v>
@@ -35758,7 +35757,7 @@
         <v>20</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F132" s="13">
         <v>0.69791666666666663</v>
@@ -35770,7 +35769,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I132" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J132" s="18" t="s">
         <v>167</v>
@@ -35787,10 +35786,10 @@
         <v>97</v>
       </c>
       <c r="D133" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F133" s="13">
         <v>0.69791666666666663</v>
@@ -35802,7 +35801,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I133" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J133" s="18" t="s">
         <v>167</v>
@@ -35822,7 +35821,7 @@
         <v>73</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F134" s="13">
         <v>0.69791666666666663</v>
@@ -35834,7 +35833,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I134" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J134" s="18" t="s">
         <v>167</v>
@@ -35854,7 +35853,7 @@
         <v>185</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F135" s="13">
         <v>0.69791666666666663</v>
@@ -35866,7 +35865,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I135" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J135" s="18" t="s">
         <v>167</v>
@@ -35883,10 +35882,10 @@
         <v>97</v>
       </c>
       <c r="D136" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F136" s="13">
         <v>0.69791666666666663</v>
@@ -35898,7 +35897,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I136" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J136" s="18" t="s">
         <v>167</v>
@@ -35915,10 +35914,10 @@
         <v>97</v>
       </c>
       <c r="D137" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F137" s="13">
         <v>0.69791666666666663</v>
@@ -35930,7 +35929,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I137" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J137" s="18" t="s">
         <v>167</v>
@@ -35947,10 +35946,10 @@
         <v>97</v>
       </c>
       <c r="D138" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F138" s="13">
         <v>0.75</v>
@@ -35962,7 +35961,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I138" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J138" s="18" t="s">
         <v>167</v>
@@ -35979,10 +35978,10 @@
         <v>97</v>
       </c>
       <c r="D139" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F139" s="13">
         <v>0.75</v>
@@ -35994,7 +35993,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I139" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J139" s="18" t="s">
         <v>167</v>
@@ -36014,7 +36013,7 @@
         <v>44</v>
       </c>
       <c r="E140" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F140" s="13">
         <v>0.75</v>
@@ -36026,7 +36025,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I140" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J140" s="18" t="s">
         <v>167</v>
@@ -36043,10 +36042,10 @@
         <v>97</v>
       </c>
       <c r="D141" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F141" s="13">
         <v>0.75</v>
@@ -36058,7 +36057,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I141" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J141" s="18" t="s">
         <v>167</v>
@@ -36075,10 +36074,10 @@
         <v>97</v>
       </c>
       <c r="D142" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F142" s="13">
         <v>0.75</v>
@@ -36090,7 +36089,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I142" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J142" s="18" t="s">
         <v>167</v>
@@ -36107,10 +36106,10 @@
         <v>97</v>
       </c>
       <c r="D143" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F143" s="13">
         <v>0.75</v>
@@ -36122,7 +36121,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I143" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J143" s="18" t="s">
         <v>167</v>
@@ -36139,10 +36138,10 @@
         <v>97</v>
       </c>
       <c r="D144" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F144" s="13">
         <v>0.75</v>
@@ -36154,7 +36153,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I144" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J144" s="18" t="s">
         <v>167</v>
@@ -36171,10 +36170,10 @@
         <v>97</v>
       </c>
       <c r="D145" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F145" s="13">
         <v>0.75</v>
@@ -36186,7 +36185,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I145" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J145" s="18" t="s">
         <v>167</v>
@@ -36206,7 +36205,7 @@
         <v>55</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F146" s="13">
         <v>0.75</v>
@@ -36218,7 +36217,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I146" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J146" s="18" t="s">
         <v>167</v>
@@ -36238,7 +36237,7 @@
         <v>59</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F147" s="13">
         <v>0.75</v>
@@ -36250,7 +36249,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I147" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J147" s="18" t="s">
         <v>167</v>
@@ -36267,10 +36266,10 @@
         <v>97</v>
       </c>
       <c r="D148" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F148" s="13">
         <v>0.75</v>
@@ -36282,7 +36281,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I148" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J148" s="18" t="s">
         <v>167</v>
@@ -36299,10 +36298,10 @@
         <v>97</v>
       </c>
       <c r="D149" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F149" s="13">
         <v>0.75</v>
@@ -36314,7 +36313,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I149" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J149" s="18" t="s">
         <v>167</v>
@@ -36334,7 +36333,7 @@
         <v>66</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F150" s="13">
         <v>0.75</v>
@@ -36346,7 +36345,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I150" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J150" s="18" t="s">
         <v>167</v>
@@ -36366,7 +36365,7 @@
         <v>71</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F151" s="13">
         <v>0.75</v>
@@ -36378,7 +36377,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I151" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J151" s="18" t="s">
         <v>167</v>
@@ -36398,7 +36397,7 @@
         <v>82</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F152" s="13">
         <v>0.75</v>
@@ -36410,7 +36409,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I152" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J152" s="18" t="s">
         <v>167</v>
@@ -36430,7 +36429,7 @@
         <v>85</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F153" s="13">
         <v>0.75</v>
@@ -36442,7 +36441,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I153" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J153" s="18" t="s">
         <v>167</v>
@@ -36459,7 +36458,7 @@
         <v>97</v>
       </c>
       <c r="D154" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E154" s="15" t="s">
         <v>171</v>
@@ -36474,7 +36473,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I154" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J154" s="18" t="s">
         <v>167</v>
@@ -36491,7 +36490,7 @@
         <v>97</v>
       </c>
       <c r="D155" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E155" s="15" t="s">
         <v>171</v>
@@ -36506,7 +36505,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I155" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J155" s="18" t="s">
         <v>167</v>
@@ -36523,7 +36522,7 @@
         <v>97</v>
       </c>
       <c r="D156" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E156" s="15" t="s">
         <v>171</v>
@@ -36538,7 +36537,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I156" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J156" s="18" t="s">
         <v>167</v>
@@ -36555,7 +36554,7 @@
         <v>97</v>
       </c>
       <c r="D157" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E157" s="15" t="s">
         <v>171</v>
@@ -36570,7 +36569,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I157" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J157" s="18" t="s">
         <v>167</v>
@@ -36587,7 +36586,7 @@
         <v>97</v>
       </c>
       <c r="D158" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E158" s="15" t="s">
         <v>171</v>
@@ -36602,7 +36601,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I158" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J158" s="18" t="s">
         <v>167</v>
@@ -36619,7 +36618,7 @@
         <v>97</v>
       </c>
       <c r="D159" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E159" s="15" t="s">
         <v>171</v>
@@ -36634,7 +36633,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I159" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J159" s="18" t="s">
         <v>167</v>
@@ -36651,7 +36650,7 @@
         <v>97</v>
       </c>
       <c r="D160" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E160" s="15" t="s">
         <v>171</v>
@@ -36666,7 +36665,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I160" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J160" s="18" t="s">
         <v>167</v>
@@ -36683,7 +36682,7 @@
         <v>97</v>
       </c>
       <c r="D161" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E161" s="15" t="s">
         <v>171</v>
@@ -36698,7 +36697,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I161" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J161" s="18" t="s">
         <v>167</v>
@@ -36715,7 +36714,7 @@
         <v>97</v>
       </c>
       <c r="D162" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E162" s="15" t="s">
         <v>171</v>
@@ -36730,7 +36729,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I162" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J162" s="18" t="s">
         <v>167</v>
@@ -36762,7 +36761,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I163" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J163" s="18" t="s">
         <v>167</v>
@@ -36794,7 +36793,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I164" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J164" s="18" t="s">
         <v>167</v>
@@ -36826,7 +36825,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I165" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J165" s="18" t="s">
         <v>167</v>
@@ -36858,7 +36857,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I166" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J166" s="18" t="s">
         <v>167</v>
@@ -36890,7 +36889,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I167" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J167" s="18" t="s">
         <v>167</v>
@@ -36922,7 +36921,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I168" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J168" s="18" t="s">
         <v>167</v>
@@ -36939,7 +36938,7 @@
         <v>97</v>
       </c>
       <c r="D169" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E169" s="15" t="s">
         <v>171</v>
@@ -36954,7 +36953,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I169" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J169" s="18" t="s">
         <v>167</v>
@@ -36986,7 +36985,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I170" s="19" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J170" s="18" t="s">
         <v>167</v>
@@ -37003,10 +37002,10 @@
         <v>97</v>
       </c>
       <c r="D171" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E171" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F171" s="13">
         <v>0.75</v>
@@ -37018,7 +37017,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I171" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J171" s="18" t="s">
         <v>175</v>
@@ -37035,10 +37034,10 @@
         <v>97</v>
       </c>
       <c r="D172" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E172" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F172" s="13">
         <v>0.75</v>
@@ -37050,7 +37049,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I172" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J172" s="18" t="s">
         <v>175</v>
@@ -37070,7 +37069,7 @@
         <v>44</v>
       </c>
       <c r="E173" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F173" s="13">
         <v>0.75</v>
@@ -37082,7 +37081,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I173" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J173" s="18" t="s">
         <v>175</v>
@@ -37099,10 +37098,10 @@
         <v>97</v>
       </c>
       <c r="D174" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E174" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F174" s="13">
         <v>0.75</v>
@@ -37114,7 +37113,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I174" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J174" s="18" t="s">
         <v>175</v>
@@ -37131,10 +37130,10 @@
         <v>97</v>
       </c>
       <c r="D175" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E175" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F175" s="13">
         <v>0.75</v>
@@ -37146,7 +37145,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I175" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J175" s="18" t="s">
         <v>175</v>
@@ -37163,10 +37162,10 @@
         <v>97</v>
       </c>
       <c r="D176" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E176" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F176" s="13">
         <v>0.75</v>
@@ -37178,7 +37177,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I176" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J176" s="18" t="s">
         <v>175</v>
@@ -37195,10 +37194,10 @@
         <v>97</v>
       </c>
       <c r="D177" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E177" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F177" s="13">
         <v>0.75</v>
@@ -37210,7 +37209,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I177" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J177" s="18" t="s">
         <v>175</v>
@@ -37227,10 +37226,10 @@
         <v>97</v>
       </c>
       <c r="D178" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E178" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F178" s="13">
         <v>0.75</v>
@@ -37242,7 +37241,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I178" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J178" s="18" t="s">
         <v>175</v>
@@ -37262,7 +37261,7 @@
         <v>55</v>
       </c>
       <c r="E179" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F179" s="13">
         <v>0.75</v>
@@ -37274,7 +37273,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I179" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J179" s="18" t="s">
         <v>175</v>
@@ -37294,7 +37293,7 @@
         <v>59</v>
       </c>
       <c r="E180" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F180" s="13">
         <v>0.75</v>
@@ -37306,7 +37305,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I180" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J180" s="18" t="s">
         <v>175</v>
@@ -37323,10 +37322,10 @@
         <v>97</v>
       </c>
       <c r="D181" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E181" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F181" s="13">
         <v>0.75</v>
@@ -37338,7 +37337,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I181" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J181" s="18" t="s">
         <v>175</v>
@@ -37355,10 +37354,10 @@
         <v>97</v>
       </c>
       <c r="D182" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E182" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F182" s="13">
         <v>0.75</v>
@@ -37370,7 +37369,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I182" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J182" s="18" t="s">
         <v>175</v>
@@ -37390,7 +37389,7 @@
         <v>66</v>
       </c>
       <c r="E183" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F183" s="13">
         <v>0.75</v>
@@ -37402,7 +37401,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="I183" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J183" s="18" t="s">
         <v>175</v>
@@ -37422,7 +37421,7 @@
         <v>71</v>
       </c>
       <c r="E184" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F184" s="13">
         <v>0.75</v>
@@ -37434,7 +37433,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I184" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J184" s="18" t="s">
         <v>175</v>
@@ -37454,7 +37453,7 @@
         <v>82</v>
       </c>
       <c r="E185" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F185" s="13">
         <v>0.75</v>
@@ -37466,7 +37465,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I185" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J185" s="18" t="s">
         <v>175</v>
@@ -37486,7 +37485,7 @@
         <v>85</v>
       </c>
       <c r="E186" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F186" s="13">
         <v>0.75</v>
@@ -37498,7 +37497,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="I186" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J186" s="18" t="s">
         <v>175</v>
@@ -37515,10 +37514,10 @@
         <v>97</v>
       </c>
       <c r="D187" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E187" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F187" s="13">
         <v>0.75</v>
@@ -37530,7 +37529,7 @@
         <v>0.71875</v>
       </c>
       <c r="I187" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J187" s="18" t="s">
         <v>175</v>
@@ -37547,10 +37546,10 @@
         <v>97</v>
       </c>
       <c r="D188" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E188" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F188" s="13">
         <v>0.75</v>
@@ -37562,7 +37561,7 @@
         <v>0.71875</v>
       </c>
       <c r="I188" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J188" s="18" t="s">
         <v>175</v>
@@ -37579,10 +37578,10 @@
         <v>97</v>
       </c>
       <c r="D189" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E189" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F189" s="13">
         <v>0.75</v>
@@ -37594,7 +37593,7 @@
         <v>0.71875</v>
       </c>
       <c r="I189" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J189" s="18" t="s">
         <v>175</v>
@@ -37611,10 +37610,10 @@
         <v>97</v>
       </c>
       <c r="D190" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E190" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F190" s="13">
         <v>0.75</v>
@@ -37626,7 +37625,7 @@
         <v>0.71875</v>
       </c>
       <c r="I190" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J190" s="18" t="s">
         <v>175</v>
@@ -37643,10 +37642,10 @@
         <v>97</v>
       </c>
       <c r="D191" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E191" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F191" s="13">
         <v>0.75</v>
@@ -37658,7 +37657,7 @@
         <v>0.71875</v>
       </c>
       <c r="I191" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J191" s="18" t="s">
         <v>175</v>
@@ -37675,10 +37674,10 @@
         <v>97</v>
       </c>
       <c r="D192" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E192" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F192" s="13">
         <v>0.75</v>
@@ -37690,7 +37689,7 @@
         <v>0.71875</v>
       </c>
       <c r="I192" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J192" s="18" t="s">
         <v>175</v>
@@ -37707,10 +37706,10 @@
         <v>97</v>
       </c>
       <c r="D193" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E193" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F193" s="13">
         <v>0.75</v>
@@ -37722,7 +37721,7 @@
         <v>0.71875</v>
       </c>
       <c r="I193" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J193" s="18" t="s">
         <v>175</v>
@@ -37739,10 +37738,10 @@
         <v>97</v>
       </c>
       <c r="D194" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E194" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F194" s="13">
         <v>0.75</v>
@@ -37754,7 +37753,7 @@
         <v>0.71875</v>
       </c>
       <c r="I194" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J194" s="18" t="s">
         <v>175</v>
@@ -37771,10 +37770,10 @@
         <v>97</v>
       </c>
       <c r="D195" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E195" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F195" s="13">
         <v>0.75</v>
@@ -37786,7 +37785,7 @@
         <v>0.71875</v>
       </c>
       <c r="I195" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J195" s="18" t="s">
         <v>175</v>
@@ -37806,7 +37805,7 @@
         <v>58</v>
       </c>
       <c r="E196" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F196" s="13">
         <v>0.75</v>
@@ -37818,7 +37817,7 @@
         <v>0.71875</v>
       </c>
       <c r="I196" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J196" s="18" t="s">
         <v>175</v>
@@ -37838,7 +37837,7 @@
         <v>62</v>
       </c>
       <c r="E197" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F197" s="13">
         <v>0.75</v>
@@ -37850,7 +37849,7 @@
         <v>0.71875</v>
       </c>
       <c r="I197" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J197" s="18" t="s">
         <v>175</v>
@@ -37870,7 +37869,7 @@
         <v>67</v>
       </c>
       <c r="E198" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F198" s="13">
         <v>0.75</v>
@@ -37882,7 +37881,7 @@
         <v>0.71875</v>
       </c>
       <c r="I198" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J198" s="18" t="s">
         <v>175</v>
@@ -37902,7 +37901,7 @@
         <v>68</v>
       </c>
       <c r="E199" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F199" s="13">
         <v>0.75</v>
@@ -37914,7 +37913,7 @@
         <v>0.71875</v>
       </c>
       <c r="I199" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J199" s="18" t="s">
         <v>175</v>
@@ -37934,7 +37933,7 @@
         <v>80</v>
       </c>
       <c r="E200" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F200" s="13">
         <v>0.75</v>
@@ -37946,7 +37945,7 @@
         <v>0.71875</v>
       </c>
       <c r="I200" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J200" s="18" t="s">
         <v>175</v>
@@ -37963,10 +37962,10 @@
         <v>97</v>
       </c>
       <c r="D201" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E201" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F201" s="13">
         <v>0.75</v>
@@ -37978,7 +37977,7 @@
         <v>0.71875</v>
       </c>
       <c r="I201" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J201" s="18" t="s">
         <v>175</v>
@@ -37998,7 +37997,7 @@
         <v>30</v>
       </c>
       <c r="E202" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F202" s="13">
         <v>0.51041666666666663</v>
@@ -38010,7 +38009,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I202" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J202" s="18" t="s">
         <v>179</v>
@@ -38030,7 +38029,7 @@
         <v>76</v>
       </c>
       <c r="E203" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F203" s="13">
         <v>0.51041666666666663</v>
@@ -38042,7 +38041,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I203" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J203" s="18" t="s">
         <v>179</v>
@@ -38062,7 +38061,7 @@
         <v>78</v>
       </c>
       <c r="E204" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F204" s="13">
         <v>0.51041666666666663</v>
@@ -38074,7 +38073,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I204" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J204" s="18" t="s">
         <v>179</v>
@@ -38094,7 +38093,7 @@
         <v>30</v>
       </c>
       <c r="E205" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F205" s="13">
         <v>0.54166666666666663</v>
@@ -38106,7 +38105,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I205" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J205" s="18" t="s">
         <v>179</v>
@@ -38126,7 +38125,7 @@
         <v>76</v>
       </c>
       <c r="E206" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F206" s="13">
         <v>0.54166666666666663</v>
@@ -38138,7 +38137,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I206" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J206" s="18" t="s">
         <v>179</v>
@@ -38158,7 +38157,7 @@
         <v>78</v>
       </c>
       <c r="E207" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F207" s="13">
         <v>0.54166666666666663</v>
@@ -38170,7 +38169,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="I207" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J207" s="18" t="s">
         <v>179</v>
@@ -38190,7 +38189,7 @@
         <v>17</v>
       </c>
       <c r="E208" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F208" s="13">
         <v>0.64583333333333337</v>
@@ -38202,7 +38201,7 @@
         <v>0.625</v>
       </c>
       <c r="I208" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J208" s="18" t="s">
         <v>175</v>
@@ -38222,7 +38221,7 @@
         <v>18</v>
       </c>
       <c r="E209" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F209" s="13">
         <v>0.64583333333333337</v>
@@ -38234,7 +38233,7 @@
         <v>0.625</v>
       </c>
       <c r="I209" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J209" s="18" t="s">
         <v>175</v>
@@ -38254,7 +38253,7 @@
         <v>20</v>
       </c>
       <c r="E210" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F210" s="13">
         <v>0.64583333333333337</v>
@@ -38266,7 +38265,7 @@
         <v>0.625</v>
       </c>
       <c r="I210" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J210" s="18" t="s">
         <v>175</v>
@@ -38286,7 +38285,7 @@
         <v>73</v>
       </c>
       <c r="E211" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F211" s="13">
         <v>0.64583333333333337</v>
@@ -38298,7 +38297,7 @@
         <v>0.625</v>
       </c>
       <c r="I211" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J211" s="18" t="s">
         <v>175</v>
@@ -38318,7 +38317,7 @@
         <v>9</v>
       </c>
       <c r="E212" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F212" s="13">
         <v>0.70833333333333337</v>
@@ -38330,7 +38329,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I212" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J212" s="18" t="s">
         <v>175</v>
@@ -38350,7 +38349,7 @@
         <v>12</v>
       </c>
       <c r="E213" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F213" s="13">
         <v>0.70833333333333337</v>
@@ -38362,7 +38361,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I213" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J213" s="18" t="s">
         <v>175</v>
@@ -38382,7 +38381,7 @@
         <v>15</v>
       </c>
       <c r="E214" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F214" s="13">
         <v>0.70833333333333337</v>
@@ -38394,7 +38393,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I214" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J214" s="18" t="s">
         <v>175</v>
@@ -38414,7 +38413,7 @@
         <v>17</v>
       </c>
       <c r="E215" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F215" s="13">
         <v>0.70833333333333337</v>
@@ -38426,7 +38425,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I215" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J215" s="18" t="s">
         <v>175</v>
@@ -38446,7 +38445,7 @@
         <v>18</v>
       </c>
       <c r="E216" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F216" s="13">
         <v>0.70833333333333337</v>
@@ -38458,7 +38457,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I216" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J216" s="18" t="s">
         <v>175</v>
@@ -38478,7 +38477,7 @@
         <v>20</v>
       </c>
       <c r="E217" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F217" s="13">
         <v>0.70833333333333337</v>
@@ -38490,7 +38489,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I217" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J217" s="18" t="s">
         <v>175</v>
@@ -38507,10 +38506,10 @@
         <v>97</v>
       </c>
       <c r="D218" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E218" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F218" s="13">
         <v>0.70833333333333337</v>
@@ -38522,7 +38521,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I218" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J218" s="18" t="s">
         <v>175</v>
@@ -38542,7 +38541,7 @@
         <v>73</v>
       </c>
       <c r="E219" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F219" s="13">
         <v>0.70833333333333337</v>
@@ -38554,7 +38553,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I219" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J219" s="18" t="s">
         <v>175</v>
@@ -38571,10 +38570,10 @@
         <v>97</v>
       </c>
       <c r="D220" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E220" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F220" s="13">
         <v>0.70833333333333337</v>
@@ -38586,7 +38585,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I220" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J220" s="18" t="s">
         <v>175</v>
@@ -38603,10 +38602,10 @@
         <v>97</v>
       </c>
       <c r="D221" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E221" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F221" s="13">
         <v>0.70833333333333337</v>
@@ -38618,7 +38617,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I221" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J221" s="18" t="s">
         <v>175</v>
@@ -38638,7 +38637,7 @@
         <v>185</v>
       </c>
       <c r="E222" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F222" s="13">
         <v>0.70833333333333337</v>
@@ -38650,7 +38649,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I222" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J222" s="18" t="s">
         <v>175</v>
@@ -38667,10 +38666,10 @@
         <v>97</v>
       </c>
       <c r="D223" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E223" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F223" s="13">
         <v>0.70833333333333337</v>
@@ -38682,7 +38681,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I223" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J223" s="18" t="s">
         <v>175</v>
@@ -38699,10 +38698,10 @@
         <v>97</v>
       </c>
       <c r="D224" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E224" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F224" s="13">
         <v>0.70833333333333337</v>
@@ -38714,7 +38713,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I224" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J224" s="18" t="s">
         <v>175</v>
@@ -38734,7 +38733,7 @@
         <v>44</v>
       </c>
       <c r="E225" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F225" s="13">
         <v>0.70833333333333337</v>
@@ -38746,7 +38745,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I225" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J225" s="18" t="s">
         <v>175</v>
@@ -38763,10 +38762,10 @@
         <v>97</v>
       </c>
       <c r="D226" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E226" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F226" s="13">
         <v>0.70833333333333337</v>
@@ -38778,7 +38777,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I226" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J226" s="18" t="s">
         <v>175</v>
@@ -38795,10 +38794,10 @@
         <v>97</v>
       </c>
       <c r="D227" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E227" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F227" s="13">
         <v>0.70833333333333337</v>
@@ -38810,7 +38809,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I227" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J227" s="18" t="s">
         <v>175</v>
@@ -38827,10 +38826,10 @@
         <v>97</v>
       </c>
       <c r="D228" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E228" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F228" s="13">
         <v>0.70833333333333337</v>
@@ -38842,7 +38841,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I228" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J228" s="18" t="s">
         <v>175</v>
@@ -38859,10 +38858,10 @@
         <v>97</v>
       </c>
       <c r="D229" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E229" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F229" s="13">
         <v>0.70833333333333337</v>
@@ -38874,7 +38873,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I229" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J229" s="18" t="s">
         <v>175</v>
@@ -38891,10 +38890,10 @@
         <v>97</v>
       </c>
       <c r="D230" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E230" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F230" s="13">
         <v>0.70833333333333337</v>
@@ -38906,7 +38905,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I230" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J230" s="18" t="s">
         <v>175</v>
@@ -38926,7 +38925,7 @@
         <v>55</v>
       </c>
       <c r="E231" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F231" s="13">
         <v>0.70833333333333337</v>
@@ -38938,7 +38937,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I231" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J231" s="18" t="s">
         <v>175</v>
@@ -38958,7 +38957,7 @@
         <v>59</v>
       </c>
       <c r="E232" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F232" s="13">
         <v>0.70833333333333337</v>
@@ -38970,7 +38969,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I232" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J232" s="18" t="s">
         <v>175</v>
@@ -38987,10 +38986,10 @@
         <v>97</v>
       </c>
       <c r="D233" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E233" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F233" s="13">
         <v>0.70833333333333337</v>
@@ -39002,7 +39001,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I233" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J233" s="18" t="s">
         <v>175</v>
@@ -39019,10 +39018,10 @@
         <v>97</v>
       </c>
       <c r="D234" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E234" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F234" s="13">
         <v>0.70833333333333337</v>
@@ -39034,7 +39033,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I234" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J234" s="18" t="s">
         <v>175</v>
@@ -39054,7 +39053,7 @@
         <v>66</v>
       </c>
       <c r="E235" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F235" s="13">
         <v>0.70833333333333337</v>
@@ -39066,7 +39065,7 @@
         <v>0.625</v>
       </c>
       <c r="I235" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J235" s="18" t="s">
         <v>175</v>
@@ -39086,7 +39085,7 @@
         <v>71</v>
       </c>
       <c r="E236" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F236" s="13">
         <v>0.70833333333333337</v>
@@ -39098,7 +39097,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I236" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J236" s="18" t="s">
         <v>175</v>
@@ -39118,7 +39117,7 @@
         <v>82</v>
       </c>
       <c r="E237" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F237" s="13">
         <v>0.70833333333333337</v>
@@ -39130,7 +39129,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I237" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J237" s="18" t="s">
         <v>175</v>
@@ -39150,7 +39149,7 @@
         <v>85</v>
       </c>
       <c r="E238" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F238" s="13">
         <v>0.70833333333333337</v>
@@ -39162,7 +39161,7 @@
         <v>0.625</v>
       </c>
       <c r="I238" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J238" s="18" t="s">
         <v>175</v>
@@ -39182,7 +39181,7 @@
         <v>17</v>
       </c>
       <c r="E239" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F239" s="13">
         <v>0.52083333333333337</v>
@@ -39194,7 +39193,7 @@
         <v>0.5</v>
       </c>
       <c r="I239" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J239" s="18" t="s">
         <v>175</v>
@@ -39214,7 +39213,7 @@
         <v>18</v>
       </c>
       <c r="E240" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F240" s="13">
         <v>0.52083333333333337</v>
@@ -39226,7 +39225,7 @@
         <v>0.5</v>
       </c>
       <c r="I240" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J240" s="18" t="s">
         <v>175</v>
@@ -39246,7 +39245,7 @@
         <v>20</v>
       </c>
       <c r="E241" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F241" s="13">
         <v>0.52083333333333337</v>
@@ -39258,7 +39257,7 @@
         <v>0.5</v>
       </c>
       <c r="I241" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J241" s="18" t="s">
         <v>175</v>
@@ -39278,7 +39277,7 @@
         <v>73</v>
       </c>
       <c r="E242" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F242" s="13">
         <v>0.52083333333333337</v>
@@ -39290,7 +39289,7 @@
         <v>0.5</v>
       </c>
       <c r="I242" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J242" s="18" t="s">
         <v>175</v>
@@ -39310,7 +39309,7 @@
         <v>9</v>
       </c>
       <c r="E243" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F243" s="13">
         <v>0.58333333333333337</v>
@@ -39322,7 +39321,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I243" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J243" s="18" t="s">
         <v>175</v>
@@ -39342,7 +39341,7 @@
         <v>12</v>
       </c>
       <c r="E244" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F244" s="13">
         <v>0.58333333333333337</v>
@@ -39354,7 +39353,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I244" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J244" s="18" t="s">
         <v>175</v>
@@ -39374,7 +39373,7 @@
         <v>15</v>
       </c>
       <c r="E245" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F245" s="13">
         <v>0.58333333333333337</v>
@@ -39386,7 +39385,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I245" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J245" s="18" t="s">
         <v>175</v>
@@ -39406,7 +39405,7 @@
         <v>17</v>
       </c>
       <c r="E246" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F246" s="13">
         <v>0.58333333333333337</v>
@@ -39418,7 +39417,7 @@
         <v>0.5</v>
       </c>
       <c r="I246" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J246" s="18" t="s">
         <v>175</v>
@@ -39438,7 +39437,7 @@
         <v>18</v>
       </c>
       <c r="E247" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F247" s="13">
         <v>0.58333333333333337</v>
@@ -39450,7 +39449,7 @@
         <v>0.5</v>
       </c>
       <c r="I247" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J247" s="18" t="s">
         <v>175</v>
@@ -39470,7 +39469,7 @@
         <v>20</v>
       </c>
       <c r="E248" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F248" s="13">
         <v>0.58333333333333337</v>
@@ -39482,7 +39481,7 @@
         <v>0.5</v>
       </c>
       <c r="I248" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J248" s="18" t="s">
         <v>175</v>
@@ -39499,10 +39498,10 @@
         <v>97</v>
       </c>
       <c r="D249" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E249" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F249" s="13">
         <v>0.58333333333333337</v>
@@ -39514,7 +39513,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I249" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J249" s="18" t="s">
         <v>175</v>
@@ -39534,7 +39533,7 @@
         <v>73</v>
       </c>
       <c r="E250" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F250" s="13">
         <v>0.58333333333333337</v>
@@ -39546,7 +39545,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I250" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J250" s="18" t="s">
         <v>175</v>
@@ -39563,10 +39562,10 @@
         <v>97</v>
       </c>
       <c r="D251" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E251" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F251" s="13">
         <v>0.58333333333333337</v>
@@ -39578,7 +39577,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I251" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J251" s="18" t="s">
         <v>175</v>
@@ -39595,10 +39594,10 @@
         <v>97</v>
       </c>
       <c r="D252" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E252" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F252" s="13">
         <v>0.58333333333333337</v>
@@ -39610,7 +39609,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I252" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J252" s="18" t="s">
         <v>175</v>
@@ -39630,7 +39629,7 @@
         <v>185</v>
       </c>
       <c r="E253" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F253" s="13">
         <v>0.58333333333333337</v>
@@ -39642,7 +39641,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I253" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J253" s="18" t="s">
         <v>175</v>
@@ -39659,10 +39658,10 @@
         <v>97</v>
       </c>
       <c r="D254" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E254" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F254" s="13">
         <v>0.58333333333333337</v>
@@ -39674,7 +39673,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I254" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J254" s="18" t="s">
         <v>175</v>
@@ -39691,10 +39690,10 @@
         <v>97</v>
       </c>
       <c r="D255" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E255" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F255" s="13">
         <v>0.58333333333333337</v>
@@ -39706,7 +39705,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I255" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J255" s="18" t="s">
         <v>175</v>
@@ -39723,10 +39722,10 @@
         <v>97</v>
       </c>
       <c r="D256" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E256" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F256" s="13">
         <v>0.58333333333333337</v>
@@ -39738,7 +39737,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I256" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J256" s="18" t="s">
         <v>175</v>
@@ -39755,10 +39754,10 @@
         <v>97</v>
       </c>
       <c r="D257" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E257" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F257" s="13">
         <v>0.58333333333333337</v>
@@ -39770,7 +39769,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I257" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J257" s="18" t="s">
         <v>175</v>
@@ -39787,10 +39786,10 @@
         <v>97</v>
       </c>
       <c r="D258" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E258" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F258" s="13">
         <v>0.58333333333333337</v>
@@ -39802,7 +39801,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I258" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J258" s="18" t="s">
         <v>175</v>
@@ -39819,10 +39818,10 @@
         <v>97</v>
       </c>
       <c r="D259" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E259" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F259" s="13">
         <v>0.58333333333333337</v>
@@ -39834,7 +39833,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I259" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J259" s="18" t="s">
         <v>175</v>
@@ -39851,10 +39850,10 @@
         <v>97</v>
       </c>
       <c r="D260" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E260" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F260" s="13">
         <v>0.58333333333333337</v>
@@ -39866,7 +39865,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I260" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J260" s="18" t="s">
         <v>175</v>
@@ -39883,10 +39882,10 @@
         <v>97</v>
       </c>
       <c r="D261" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E261" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F261" s="13">
         <v>0.58333333333333337</v>
@@ -39898,7 +39897,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I261" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J261" s="18" t="s">
         <v>175</v>
@@ -39915,10 +39914,10 @@
         <v>97</v>
       </c>
       <c r="D262" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E262" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F262" s="13">
         <v>0.58333333333333337</v>
@@ -39930,7 +39929,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I262" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J262" s="18" t="s">
         <v>175</v>
@@ -39950,7 +39949,7 @@
         <v>58</v>
       </c>
       <c r="E263" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F263" s="13">
         <v>0.58333333333333337</v>
@@ -39962,7 +39961,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I263" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J263" s="18" t="s">
         <v>175</v>
@@ -39982,7 +39981,7 @@
         <v>62</v>
       </c>
       <c r="E264" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F264" s="13">
         <v>0.58333333333333337</v>
@@ -39994,7 +39993,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I264" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J264" s="18" t="s">
         <v>175</v>
@@ -40014,7 +40013,7 @@
         <v>67</v>
       </c>
       <c r="E265" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F265" s="13">
         <v>0.58333333333333337</v>
@@ -40026,7 +40025,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I265" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J265" s="18" t="s">
         <v>175</v>
@@ -40046,7 +40045,7 @@
         <v>68</v>
       </c>
       <c r="E266" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F266" s="13">
         <v>0.58333333333333337</v>
@@ -40058,7 +40057,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I266" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J266" s="18" t="s">
         <v>175</v>
@@ -40078,7 +40077,7 @@
         <v>80</v>
       </c>
       <c r="E267" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F267" s="13">
         <v>0.58333333333333337</v>
@@ -40090,7 +40089,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I267" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J267" s="18" t="s">
         <v>175</v>
@@ -40107,10 +40106,10 @@
         <v>97</v>
       </c>
       <c r="D268" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E268" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F268" s="13">
         <v>0.58333333333333337</v>
@@ -40122,7 +40121,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I268" s="19" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="J268" s="18" t="s">
         <v>175</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Isadora/Documents/GitHub/rehearsal-schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8C93B9-4BAC-5D48-B0A8-128F0185E5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0A377B-7FF1-3B4B-9013-D4EA0C678E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4120" yWindow="780" windowWidth="27240" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3319" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3314" uniqueCount="318">
   <si>
     <t>class_name</t>
   </si>
@@ -892,12 +892,6 @@
     <t>Black cropped long sleeve and purple sweatpants.</t>
   </si>
   <si>
-    <t>Red t-shirt with silver jacket and black pants.</t>
-  </si>
-  <si>
-    <t>Black sequin tank top and black jazz pants.</t>
-  </si>
-  <si>
     <t>Red sleeveless hoodie and black striped track pants.</t>
   </si>
   <si>
@@ -916,16 +910,10 @@
     <t>Shirt and pants in green, gray, navy, or maroon.</t>
   </si>
   <si>
-    <t>Iridescent sequin dress and tan tights OR blue sequin top and white pants</t>
-  </si>
-  <si>
     <t>Blue sequin dress and tights OR blue sequin shirt and black pants.</t>
   </si>
   <si>
     <t>Footless skin color tights.</t>
-  </si>
-  <si>
-    <t>Bright colored blazer.</t>
   </si>
   <si>
     <t>Black country top OR red country top. Black cowboy hat.</t>
@@ -958,13 +946,7 @@
     <t>Black socks and tap shoes.</t>
   </si>
   <si>
-    <t>Red sequin flapper dress and footed tights. Headband.</t>
-  </si>
-  <si>
     <t>Tan bra or leotard if needed. Tap shoes.</t>
-  </si>
-  <si>
-    <t>Black tank top and black blazer.</t>
   </si>
   <si>
     <t>Black wide leg pants. Black socks and tap shoes.</t>
@@ -1007,6 +989,9 @@
   </si>
   <si>
     <t>For vest: black pants. Pink or skin tone ballet tights and ballet shoes.</t>
+  </si>
+  <si>
+    <t>Izzy &amp; Bella</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1088,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1132,8 +1117,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1353,15 +1336,14 @@
   <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" style="20" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" style="20" customWidth="1"/>
-    <col min="4" max="5" width="15.83203125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="107.33203125" style="20" customWidth="1"/>
-    <col min="7" max="7" width="51" style="20" customWidth="1"/>
-    <col min="8" max="8" width="94" style="20" customWidth="1"/>
-    <col min="9" max="23" width="10.5" style="20" customWidth="1"/>
-    <col min="24" max="16384" width="11.1640625" style="20"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="107.33203125" customWidth="1"/>
+    <col min="7" max="7" width="51" customWidth="1"/>
+    <col min="8" max="8" width="94" customWidth="1"/>
+    <col min="9" max="23" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1386,1809 +1368,1794 @@
       <c r="G1" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="H1" s="20"/>
+      <c r="H1"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="13">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="13">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" t="s">
         <v>281</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="13">
+        <v>0.59375</v>
+      </c>
+      <c r="F4" t="s">
+        <v>282</v>
+      </c>
+      <c r="G4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="13">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0.40625</v>
+      </c>
+      <c r="F6" t="s">
+        <v>295</v>
+      </c>
+      <c r="G6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="13">
+        <v>0.46875</v>
+      </c>
+      <c r="F7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="13">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F8" t="s">
+        <v>263</v>
+      </c>
+      <c r="G8" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F10" t="s">
+        <v>266</v>
+      </c>
+      <c r="G10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G11" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="F12" t="s">
+        <v>311</v>
+      </c>
+      <c r="G12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F13" t="s">
+        <v>267</v>
+      </c>
+      <c r="G13" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0.6875</v>
+      </c>
+      <c r="F14" t="s">
+        <v>283</v>
+      </c>
+      <c r="G14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F15" t="s">
+        <v>275</v>
+      </c>
+      <c r="G15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="13">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F17" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F18" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F19" t="s">
+        <v>270</v>
+      </c>
+      <c r="G19" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F20" t="s">
+        <v>313</v>
+      </c>
+      <c r="G20" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="F22" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F23" t="s">
+        <v>284</v>
+      </c>
+      <c r="G23" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F24" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F25" t="s">
+        <v>286</v>
+      </c>
+      <c r="G25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="13">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="F26" t="s">
+        <v>287</v>
+      </c>
+      <c r="G26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F27" t="s">
+        <v>288</v>
+      </c>
+      <c r="G27" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F28" t="s">
+        <v>277</v>
+      </c>
+      <c r="G28" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0.71875</v>
+      </c>
+      <c r="F29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="13">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F30" t="s">
+        <v>289</v>
+      </c>
+      <c r="G30" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F31" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>236</v>
+      </c>
+      <c r="B32" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F32" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="13">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F33" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F34" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="13">
+        <v>0.6875</v>
+      </c>
+      <c r="F35" t="s">
+        <v>304</v>
+      </c>
+      <c r="G35" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F36" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F37" t="s">
+        <v>274</v>
+      </c>
+      <c r="G37" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="13">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F38" t="s">
+        <v>273</v>
+      </c>
+      <c r="G38" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>238</v>
+      </c>
+      <c r="B39" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="13">
+        <v>0.625</v>
+      </c>
+      <c r="F39" t="s">
+        <v>279</v>
+      </c>
+      <c r="G39" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="13">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F40" t="s">
+        <v>273</v>
+      </c>
+      <c r="G40" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F41" t="s">
+        <v>252</v>
+      </c>
+      <c r="G41" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s">
+        <v>317</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="F42" t="s">
+        <v>293</v>
+      </c>
+      <c r="G42" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="21">
-        <v>0.59375</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="21">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="20" t="s">
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="21">
-        <v>0.40625</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="20" t="s">
+      <c r="F43" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>239</v>
+      </c>
+      <c r="B44" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F44" t="s">
+        <v>292</v>
+      </c>
+      <c r="G44" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
+        <v>196</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F45" t="s">
+        <v>290</v>
+      </c>
+      <c r="G45" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
         <v>187</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0.46875</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.8125</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0.375</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="21">
-        <v>0.6875</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="21">
-        <v>0.8125</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="C16" s="20" t="s">
+      <c r="D46" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="21">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="21">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="21">
-        <v>0.8125</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="21">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="21">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="21">
-        <v>0.375</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="21">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="21">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="21">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="21">
-        <v>0.71875</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="21">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="21">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="21">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="21">
-        <v>0.6875</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="21">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="21">
-        <v>0.625</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="21">
+      <c r="E46" s="13">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F40" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="21">
-        <v>0.375</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="G42" s="20" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="21">
-        <v>0.8125</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="G44" s="20" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="21">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" s="20" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -35469,7 +35436,7 @@
         <v>17</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F123" s="13">
         <v>0.65625</v>
@@ -35501,7 +35468,7 @@
         <v>18</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F124" s="13">
         <v>0.65625</v>
@@ -35533,7 +35500,7 @@
         <v>20</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F125" s="13">
         <v>0.65625</v>
@@ -35565,7 +35532,7 @@
         <v>73</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F126" s="13">
         <v>0.65625</v>
@@ -35597,7 +35564,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F127" s="13">
         <v>0.69791666666666663</v>
@@ -35609,7 +35576,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I127" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J127" s="18" t="s">
         <v>167</v>
@@ -35629,7 +35596,7 @@
         <v>12</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F128" s="13">
         <v>0.69791666666666663</v>
@@ -35641,7 +35608,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I128" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J128" s="18" t="s">
         <v>167</v>
@@ -35661,7 +35628,7 @@
         <v>15</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F129" s="13">
         <v>0.69791666666666663</v>
@@ -35673,7 +35640,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I129" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J129" s="18" t="s">
         <v>167</v>
@@ -35693,7 +35660,7 @@
         <v>17</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F130" s="13">
         <v>0.69791666666666663</v>
@@ -35705,7 +35672,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I130" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J130" s="18" t="s">
         <v>167</v>
@@ -35725,7 +35692,7 @@
         <v>18</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F131" s="13">
         <v>0.69791666666666663</v>
@@ -35737,7 +35704,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I131" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J131" s="18" t="s">
         <v>167</v>
@@ -35757,7 +35724,7 @@
         <v>20</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F132" s="13">
         <v>0.69791666666666663</v>
@@ -35769,7 +35736,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I132" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J132" s="18" t="s">
         <v>167</v>
@@ -35789,7 +35756,7 @@
         <v>205</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F133" s="13">
         <v>0.69791666666666663</v>
@@ -35801,7 +35768,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I133" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J133" s="18" t="s">
         <v>167</v>
@@ -35821,7 +35788,7 @@
         <v>73</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F134" s="13">
         <v>0.69791666666666663</v>
@@ -35833,7 +35800,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I134" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J134" s="18" t="s">
         <v>167</v>
@@ -35853,7 +35820,7 @@
         <v>185</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F135" s="13">
         <v>0.69791666666666663</v>
@@ -35865,7 +35832,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I135" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J135" s="18" t="s">
         <v>167</v>
@@ -35885,7 +35852,7 @@
         <v>237</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F136" s="13">
         <v>0.69791666666666663</v>
@@ -35897,7 +35864,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I136" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J136" s="18" t="s">
         <v>167</v>
@@ -35917,7 +35884,7 @@
         <v>238</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F137" s="13">
         <v>0.69791666666666663</v>
@@ -35929,7 +35896,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I137" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J137" s="18" t="s">
         <v>167</v>
@@ -35949,7 +35916,7 @@
         <v>219</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F138" s="13">
         <v>0.75</v>
@@ -35961,7 +35928,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I138" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J138" s="18" t="s">
         <v>167</v>
@@ -35981,7 +35948,7 @@
         <v>225</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F139" s="13">
         <v>0.75</v>
@@ -35993,7 +35960,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I139" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J139" s="18" t="s">
         <v>167</v>
@@ -36013,7 +35980,7 @@
         <v>44</v>
       </c>
       <c r="E140" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F140" s="13">
         <v>0.75</v>
@@ -36025,7 +35992,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I140" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J140" s="18" t="s">
         <v>167</v>
@@ -36045,7 +36012,7 @@
         <v>229</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F141" s="13">
         <v>0.75</v>
@@ -36057,7 +36024,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I141" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J141" s="18" t="s">
         <v>167</v>
@@ -36077,7 +36044,7 @@
         <v>230</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F142" s="13">
         <v>0.75</v>
@@ -36089,7 +36056,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I142" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J142" s="18" t="s">
         <v>167</v>
@@ -36109,7 +36076,7 @@
         <v>231</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F143" s="13">
         <v>0.75</v>
@@ -36121,7 +36088,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I143" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J143" s="18" t="s">
         <v>167</v>
@@ -36141,7 +36108,7 @@
         <v>232</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F144" s="13">
         <v>0.75</v>
@@ -36153,7 +36120,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I144" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J144" s="18" t="s">
         <v>167</v>
@@ -36173,7 +36140,7 @@
         <v>233</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F145" s="13">
         <v>0.75</v>
@@ -36185,7 +36152,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I145" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J145" s="18" t="s">
         <v>167</v>
@@ -36205,7 +36172,7 @@
         <v>55</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F146" s="13">
         <v>0.75</v>
@@ -36217,7 +36184,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I146" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J146" s="18" t="s">
         <v>167</v>
@@ -36237,7 +36204,7 @@
         <v>59</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F147" s="13">
         <v>0.75</v>
@@ -36249,7 +36216,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I147" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J147" s="18" t="s">
         <v>167</v>
@@ -36269,7 +36236,7 @@
         <v>235</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F148" s="13">
         <v>0.75</v>
@@ -36281,7 +36248,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I148" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J148" s="18" t="s">
         <v>167</v>
@@ -36301,7 +36268,7 @@
         <v>236</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F149" s="13">
         <v>0.75</v>
@@ -36313,7 +36280,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I149" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J149" s="18" t="s">
         <v>167</v>
@@ -36333,7 +36300,7 @@
         <v>66</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F150" s="13">
         <v>0.75</v>
@@ -36345,7 +36312,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I150" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J150" s="18" t="s">
         <v>167</v>
@@ -36365,7 +36332,7 @@
         <v>71</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F151" s="13">
         <v>0.75</v>
@@ -36377,7 +36344,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I151" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J151" s="18" t="s">
         <v>167</v>
@@ -36397,7 +36364,7 @@
         <v>82</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F152" s="13">
         <v>0.75</v>
@@ -36409,7 +36376,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I152" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J152" s="18" t="s">
         <v>167</v>
@@ -36429,7 +36396,7 @@
         <v>85</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F153" s="13">
         <v>0.75</v>
@@ -36441,7 +36408,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I153" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J153" s="18" t="s">
         <v>167</v>
@@ -36473,7 +36440,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I154" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J154" s="18" t="s">
         <v>167</v>
@@ -36505,7 +36472,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I155" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J155" s="18" t="s">
         <v>167</v>
@@ -36537,7 +36504,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I156" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J156" s="18" t="s">
         <v>167</v>
@@ -36569,7 +36536,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I157" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J157" s="18" t="s">
         <v>167</v>
@@ -36601,7 +36568,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I158" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J158" s="18" t="s">
         <v>167</v>
@@ -36633,7 +36600,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I159" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J159" s="18" t="s">
         <v>167</v>
@@ -36665,7 +36632,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I160" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J160" s="18" t="s">
         <v>167</v>
@@ -36697,7 +36664,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I161" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J161" s="18" t="s">
         <v>167</v>
@@ -36729,7 +36696,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I162" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J162" s="18" t="s">
         <v>167</v>
@@ -36761,7 +36728,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I163" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J163" s="18" t="s">
         <v>167</v>
@@ -36793,7 +36760,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I164" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J164" s="18" t="s">
         <v>167</v>
@@ -36825,7 +36792,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I165" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J165" s="18" t="s">
         <v>167</v>
@@ -36857,7 +36824,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I166" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J166" s="18" t="s">
         <v>167</v>
@@ -36889,7 +36856,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I167" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J167" s="18" t="s">
         <v>167</v>
@@ -36921,7 +36888,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I168" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J168" s="18" t="s">
         <v>167</v>
@@ -36953,7 +36920,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I169" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J169" s="18" t="s">
         <v>167</v>
@@ -36985,7 +36952,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I170" s="19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="J170" s="18" t="s">
         <v>167</v>
@@ -37017,7 +36984,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I171" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J171" s="18" t="s">
         <v>175</v>
@@ -37049,7 +37016,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I172" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J172" s="18" t="s">
         <v>175</v>
@@ -37081,7 +37048,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I173" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J173" s="18" t="s">
         <v>175</v>
@@ -37113,7 +37080,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I174" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J174" s="18" t="s">
         <v>175</v>
@@ -37145,7 +37112,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I175" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J175" s="18" t="s">
         <v>175</v>
@@ -37177,7 +37144,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I176" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J176" s="18" t="s">
         <v>175</v>
@@ -37209,7 +37176,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I177" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J177" s="18" t="s">
         <v>175</v>
@@ -37241,7 +37208,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I178" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J178" s="18" t="s">
         <v>175</v>
@@ -37273,7 +37240,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I179" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J179" s="18" t="s">
         <v>175</v>
@@ -37305,7 +37272,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I180" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J180" s="18" t="s">
         <v>175</v>
@@ -37337,7 +37304,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I181" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J181" s="18" t="s">
         <v>175</v>
@@ -37369,7 +37336,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I182" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J182" s="18" t="s">
         <v>175</v>
@@ -37401,7 +37368,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="I183" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J183" s="18" t="s">
         <v>175</v>
@@ -37433,7 +37400,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I184" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J184" s="18" t="s">
         <v>175</v>
@@ -37465,7 +37432,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I185" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J185" s="18" t="s">
         <v>175</v>
@@ -37497,7 +37464,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="I186" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J186" s="18" t="s">
         <v>175</v>
@@ -37529,7 +37496,7 @@
         <v>0.71875</v>
       </c>
       <c r="I187" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J187" s="18" t="s">
         <v>175</v>
@@ -37561,7 +37528,7 @@
         <v>0.71875</v>
       </c>
       <c r="I188" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J188" s="18" t="s">
         <v>175</v>
@@ -37593,7 +37560,7 @@
         <v>0.71875</v>
       </c>
       <c r="I189" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J189" s="18" t="s">
         <v>175</v>
@@ -37625,7 +37592,7 @@
         <v>0.71875</v>
       </c>
       <c r="I190" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J190" s="18" t="s">
         <v>175</v>
@@ -37657,7 +37624,7 @@
         <v>0.71875</v>
       </c>
       <c r="I191" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J191" s="18" t="s">
         <v>175</v>
@@ -37689,7 +37656,7 @@
         <v>0.71875</v>
       </c>
       <c r="I192" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J192" s="18" t="s">
         <v>175</v>
@@ -37721,7 +37688,7 @@
         <v>0.71875</v>
       </c>
       <c r="I193" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J193" s="18" t="s">
         <v>175</v>
@@ -37753,7 +37720,7 @@
         <v>0.71875</v>
       </c>
       <c r="I194" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J194" s="18" t="s">
         <v>175</v>
@@ -37785,7 +37752,7 @@
         <v>0.71875</v>
       </c>
       <c r="I195" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J195" s="18" t="s">
         <v>175</v>
@@ -37817,7 +37784,7 @@
         <v>0.71875</v>
       </c>
       <c r="I196" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J196" s="18" t="s">
         <v>175</v>
@@ -37849,7 +37816,7 @@
         <v>0.71875</v>
       </c>
       <c r="I197" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J197" s="18" t="s">
         <v>175</v>
@@ -37881,7 +37848,7 @@
         <v>0.71875</v>
       </c>
       <c r="I198" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J198" s="18" t="s">
         <v>175</v>
@@ -37913,7 +37880,7 @@
         <v>0.71875</v>
       </c>
       <c r="I199" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J199" s="18" t="s">
         <v>175</v>
@@ -37945,7 +37912,7 @@
         <v>0.71875</v>
       </c>
       <c r="I200" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J200" s="18" t="s">
         <v>175</v>
@@ -37977,7 +37944,7 @@
         <v>0.71875</v>
       </c>
       <c r="I201" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J201" s="18" t="s">
         <v>175</v>
@@ -38329,7 +38296,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I212" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J212" s="18" t="s">
         <v>175</v>
@@ -38361,7 +38328,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I213" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J213" s="18" t="s">
         <v>175</v>
@@ -38393,7 +38360,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I214" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J214" s="18" t="s">
         <v>175</v>
@@ -38425,7 +38392,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I215" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J215" s="18" t="s">
         <v>175</v>
@@ -38457,7 +38424,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I216" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J216" s="18" t="s">
         <v>175</v>
@@ -38489,7 +38456,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I217" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J217" s="18" t="s">
         <v>175</v>
@@ -38521,7 +38488,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I218" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J218" s="18" t="s">
         <v>175</v>
@@ -38553,7 +38520,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I219" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J219" s="18" t="s">
         <v>175</v>
@@ -38585,7 +38552,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I220" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J220" s="18" t="s">
         <v>175</v>
@@ -38617,7 +38584,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I221" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J221" s="18" t="s">
         <v>175</v>
@@ -38649,7 +38616,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I222" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J222" s="18" t="s">
         <v>175</v>
@@ -38681,7 +38648,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I223" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J223" s="18" t="s">
         <v>175</v>
@@ -38713,7 +38680,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I224" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J224" s="18" t="s">
         <v>175</v>
@@ -38745,7 +38712,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I225" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J225" s="18" t="s">
         <v>175</v>
@@ -38777,7 +38744,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I226" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J226" s="18" t="s">
         <v>175</v>
@@ -38809,7 +38776,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I227" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J227" s="18" t="s">
         <v>175</v>
@@ -38841,7 +38808,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I228" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J228" s="18" t="s">
         <v>175</v>
@@ -38873,7 +38840,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I229" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J229" s="18" t="s">
         <v>175</v>
@@ -38905,7 +38872,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I230" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J230" s="18" t="s">
         <v>175</v>
@@ -38937,7 +38904,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I231" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J231" s="18" t="s">
         <v>175</v>
@@ -38969,7 +38936,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I232" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J232" s="18" t="s">
         <v>175</v>
@@ -39001,7 +38968,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I233" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J233" s="18" t="s">
         <v>175</v>
@@ -39033,7 +39000,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I234" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J234" s="18" t="s">
         <v>175</v>
@@ -39065,7 +39032,7 @@
         <v>0.625</v>
       </c>
       <c r="I235" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J235" s="18" t="s">
         <v>175</v>
@@ -39097,7 +39064,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I236" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J236" s="18" t="s">
         <v>175</v>
@@ -39129,7 +39096,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I237" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J237" s="18" t="s">
         <v>175</v>
@@ -39161,7 +39128,7 @@
         <v>0.625</v>
       </c>
       <c r="I238" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J238" s="18" t="s">
         <v>175</v>
@@ -39193,7 +39160,7 @@
         <v>0.5</v>
       </c>
       <c r="I239" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J239" s="18" t="s">
         <v>175</v>
@@ -39225,7 +39192,7 @@
         <v>0.5</v>
       </c>
       <c r="I240" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J240" s="18" t="s">
         <v>175</v>
@@ -39257,7 +39224,7 @@
         <v>0.5</v>
       </c>
       <c r="I241" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J241" s="18" t="s">
         <v>175</v>
@@ -39289,7 +39256,7 @@
         <v>0.5</v>
       </c>
       <c r="I242" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J242" s="18" t="s">
         <v>175</v>
@@ -39321,7 +39288,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I243" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J243" s="18" t="s">
         <v>175</v>
@@ -39353,7 +39320,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I244" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J244" s="18" t="s">
         <v>175</v>
@@ -39385,7 +39352,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I245" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J245" s="18" t="s">
         <v>175</v>
@@ -39417,7 +39384,7 @@
         <v>0.5</v>
       </c>
       <c r="I246" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J246" s="18" t="s">
         <v>175</v>
@@ -39449,7 +39416,7 @@
         <v>0.5</v>
       </c>
       <c r="I247" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J247" s="18" t="s">
         <v>175</v>
@@ -39481,7 +39448,7 @@
         <v>0.5</v>
       </c>
       <c r="I248" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J248" s="18" t="s">
         <v>175</v>
@@ -39513,7 +39480,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I249" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J249" s="18" t="s">
         <v>175</v>
@@ -39545,7 +39512,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I250" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J250" s="18" t="s">
         <v>175</v>
@@ -39577,7 +39544,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I251" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J251" s="18" t="s">
         <v>175</v>
@@ -39609,7 +39576,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I252" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J252" s="18" t="s">
         <v>175</v>
@@ -39641,7 +39608,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I253" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J253" s="18" t="s">
         <v>175</v>
@@ -39673,7 +39640,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I254" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J254" s="18" t="s">
         <v>175</v>
@@ -39705,7 +39672,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I255" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J255" s="18" t="s">
         <v>175</v>
@@ -39737,7 +39704,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I256" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J256" s="18" t="s">
         <v>175</v>
@@ -39769,7 +39736,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I257" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J257" s="18" t="s">
         <v>175</v>
@@ -39801,7 +39768,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I258" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J258" s="18" t="s">
         <v>175</v>
@@ -39833,7 +39800,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I259" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J259" s="18" t="s">
         <v>175</v>
@@ -39865,7 +39832,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I260" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J260" s="18" t="s">
         <v>175</v>
@@ -39897,7 +39864,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I261" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J261" s="18" t="s">
         <v>175</v>
@@ -39929,7 +39896,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I262" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J262" s="18" t="s">
         <v>175</v>
@@ -39961,7 +39928,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I263" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J263" s="18" t="s">
         <v>175</v>
@@ -39993,7 +39960,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I264" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J264" s="18" t="s">
         <v>175</v>
@@ -40025,7 +39992,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I265" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J265" s="18" t="s">
         <v>175</v>
@@ -40057,7 +40024,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I266" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J266" s="18" t="s">
         <v>175</v>
@@ -40089,7 +40056,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I267" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J267" s="18" t="s">
         <v>175</v>
@@ -40121,7 +40088,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I268" s="19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J268" s="18" t="s">
         <v>175</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Isadora/Documents/GitHub/rehearsal-schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0A377B-7FF1-3B4B-9013-D4EA0C678E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D3DB49-3CE3-AB4E-908F-5036655D5049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4120" yWindow="780" windowWidth="27240" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3314" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3320" uniqueCount="324">
   <si>
     <t>class_name</t>
   </si>
@@ -993,6 +993,24 @@
   <si>
     <t>Izzy &amp; Bella</t>
   </si>
+  <si>
+    <t>Red t-shirt with silver jacket and black pants.</t>
+  </si>
+  <si>
+    <t>Black sequin tank top and black jazz pants.</t>
+  </si>
+  <si>
+    <t>Bright colored blazer.</t>
+  </si>
+  <si>
+    <t>Iridescent sequin dress and tan tights OR blue sequin top and white pants</t>
+  </si>
+  <si>
+    <t>Red sequin flapper dress and footed tights. Headband.</t>
+  </si>
+  <si>
+    <t>Black tank top and black blazer.</t>
+  </si>
 </sst>
 </file>
 
@@ -1088,7 +1106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1117,6 +1135,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1336,14 +1356,15 @@
   <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" customWidth="1"/>
-    <col min="4" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="107.33203125" customWidth="1"/>
-    <col min="7" max="7" width="51" customWidth="1"/>
-    <col min="8" max="8" width="94" customWidth="1"/>
-    <col min="9" max="23" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" style="20" customWidth="1"/>
+    <col min="4" max="5" width="15.83203125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="107.33203125" style="20" customWidth="1"/>
+    <col min="7" max="7" width="51" style="20" customWidth="1"/>
+    <col min="8" max="8" width="94" style="20" customWidth="1"/>
+    <col min="9" max="23" width="10.5" style="20" customWidth="1"/>
+    <col min="24" max="16384" width="11.1640625" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1368,1794 +1389,1812 @@
       <c r="G1" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="H1"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="21">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="20" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="21">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="21">
         <v>0.59375</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="21">
         <v>0.54166666666666663</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="21">
         <v>0.40625</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="21">
         <v>0.46875</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="21">
         <v>0.55208333333333337</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="21">
         <v>0.8125</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="20" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="21">
         <v>0.80208333333333337</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="20" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="21">
         <v>0.375</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="20" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="21">
         <v>0.79166666666666663</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="20" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="21">
         <v>0.6875</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="20" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="21">
         <v>0.8125</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="20" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="21">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="G16" s="20" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="21">
         <v>0.72916666666666663</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="G17" s="20" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="21">
         <v>0.65625</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="G18" s="20" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="A19" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="21">
         <v>0.8125</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="20" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="21">
         <v>0.66666666666666663</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="20" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="21">
         <v>0.72916666666666663</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="20" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="21">
         <v>0.375</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="20" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="A23" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="21">
         <v>0.65625</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="20" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="21">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="20" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="21">
         <v>0.75</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="20" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="21">
         <v>0.73958333333333337</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="20" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="21">
         <v>0.65625</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="20" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="A28" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="21">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="20" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="21">
         <v>0.71875</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="20" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="A30" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="21">
         <v>0.76041666666666663</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="20" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="A31" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="21">
         <v>0.70833333333333337</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="G31" s="20" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="A32" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="21">
         <v>0.65625</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="G32" s="20" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="A33" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="21">
         <v>0.72916666666666663</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="20" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="A34" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="21">
         <v>0.75</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="G34" s="20" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="A35" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="21">
         <v>0.6875</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="20" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="A36" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="21">
         <v>0.65625</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="20" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="A37" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="21">
         <v>0.75</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="A38" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="21">
         <v>0.80208333333333337</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="20" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="A39" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="21">
         <v>0.625</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="20" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="A40" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="21">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="A41" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="A42" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="21">
         <v>0.375</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="20" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="A43" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="20" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="21">
         <v>0.8125</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="20" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="A45" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="21">
         <v>0.65625</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="20" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="A46" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="21">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="20" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="49" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" s="20" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Isadora/Documents/GitHub/rehearsal-schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D3DB49-3CE3-AB4E-908F-5036655D5049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E08DA2-810C-8246-882D-4C894918BFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4120" yWindow="780" windowWidth="27240" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -931,9 +931,6 @@
     <t>Beige/skin-toned leotard or fitted tank.</t>
   </si>
   <si>
-    <t>Blakc socks and hip hop sneakers.</t>
-  </si>
-  <si>
     <t>Black jazz shoes. Tan bra or leotard if needed. Black socks if needed.</t>
   </si>
   <si>
@@ -941,9 +938,6 @@
   </si>
   <si>
     <t>Nude leotard or bra with black spandex shorts. Black jazz shoes.</t>
-  </si>
-  <si>
-    <t>Black socks and tap shoes.</t>
   </si>
   <si>
     <t>Tan bra or leotard if needed. Tap shoes.</t>
@@ -1010,6 +1004,12 @@
   </si>
   <si>
     <t>Black tank top and black blazer.</t>
+  </si>
+  <si>
+    <t>Black socks and hip hop sneakers.</t>
+  </si>
+  <si>
+    <t>Black socks if wearing pants. Tap shoes.</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1135,8 +1135,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1356,15 +1354,14 @@
   <dimension ref="A1:H947"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" style="20" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" style="20" customWidth="1"/>
-    <col min="4" max="5" width="15.83203125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="107.33203125" style="20" customWidth="1"/>
-    <col min="7" max="7" width="51" style="20" customWidth="1"/>
-    <col min="8" max="8" width="94" style="20" customWidth="1"/>
-    <col min="9" max="23" width="10.5" style="20" customWidth="1"/>
-    <col min="24" max="16384" width="11.1640625" style="20"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="107.33203125" customWidth="1"/>
+    <col min="7" max="7" width="51" customWidth="1"/>
+    <col min="8" max="8" width="94" customWidth="1"/>
+    <col min="9" max="23" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1389,1812 +1386,1812 @@
       <c r="G1" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="H1" s="20"/>
+      <c r="H1"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="13">
         <v>0.69791666666666663</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="13">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" t="s">
         <v>281</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="13">
+        <v>0.59375</v>
+      </c>
+      <c r="F4" t="s">
+        <v>282</v>
+      </c>
+      <c r="G4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="13">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0.40625</v>
+      </c>
+      <c r="F6" t="s">
+        <v>295</v>
+      </c>
+      <c r="G6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="13">
+        <v>0.46875</v>
+      </c>
+      <c r="F7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="13">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F8" t="s">
+        <v>263</v>
+      </c>
+      <c r="G8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F10" t="s">
+        <v>266</v>
+      </c>
+      <c r="G10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G11" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="F12" t="s">
+        <v>309</v>
+      </c>
+      <c r="G12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F13" t="s">
+        <v>267</v>
+      </c>
+      <c r="G13" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0.6875</v>
+      </c>
+      <c r="F14" t="s">
+        <v>283</v>
+      </c>
+      <c r="G14" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="20" t="s">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F15" t="s">
+        <v>275</v>
+      </c>
+      <c r="G15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F16" t="s">
+        <v>316</v>
+      </c>
+      <c r="G16" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="13">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F17" t="s">
+        <v>317</v>
+      </c>
+      <c r="G17" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F18" t="s">
+        <v>318</v>
+      </c>
+      <c r="G18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F19" t="s">
+        <v>270</v>
+      </c>
+      <c r="G19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F20" t="s">
+        <v>311</v>
+      </c>
+      <c r="G20" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="20" t="s">
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="F22" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F23" t="s">
+        <v>284</v>
+      </c>
+      <c r="G23" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F24" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F25" t="s">
+        <v>286</v>
+      </c>
+      <c r="G25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="13">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="F26" t="s">
+        <v>287</v>
+      </c>
+      <c r="G26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F27" t="s">
+        <v>288</v>
+      </c>
+      <c r="G27" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="13">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F28" t="s">
+        <v>277</v>
+      </c>
+      <c r="G28" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0.71875</v>
+      </c>
+      <c r="F29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="13">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F30" t="s">
+        <v>289</v>
+      </c>
+      <c r="G30" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F31" t="s">
+        <v>319</v>
+      </c>
+      <c r="G31" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>236</v>
+      </c>
+      <c r="B32" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F32" t="s">
+        <v>320</v>
+      </c>
+      <c r="G32" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="13">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F33" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F34" t="s">
+        <v>321</v>
+      </c>
+      <c r="G34" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="13">
+        <v>0.6875</v>
+      </c>
+      <c r="F35" t="s">
+        <v>302</v>
+      </c>
+      <c r="G35" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F36" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="F37" t="s">
+        <v>274</v>
+      </c>
+      <c r="G37" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="13">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="F38" t="s">
+        <v>273</v>
+      </c>
+      <c r="G38" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>238</v>
+      </c>
+      <c r="B39" t="s">
+        <v>187</v>
+      </c>
+      <c r="D39" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="21">
-        <v>0.59375</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" s="20" t="s">
+      <c r="E39" s="13">
+        <v>0.625</v>
+      </c>
+      <c r="F39" t="s">
+        <v>279</v>
+      </c>
+      <c r="G39" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="13">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F40" t="s">
+        <v>273</v>
+      </c>
+      <c r="G40" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="21">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="20" t="s">
+      <c r="E41" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F41" t="s">
+        <v>252</v>
+      </c>
+      <c r="G41" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s">
+        <v>315</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="13">
+        <v>0.375</v>
+      </c>
+      <c r="F42" t="s">
+        <v>293</v>
+      </c>
+      <c r="G42" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="21">
-        <v>0.40625</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="20" t="s">
+      <c r="F43" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>239</v>
+      </c>
+      <c r="B44" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="13">
+        <v>0.8125</v>
+      </c>
+      <c r="F44" t="s">
+        <v>292</v>
+      </c>
+      <c r="G44" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
+        <v>196</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="13">
+        <v>0.65625</v>
+      </c>
+      <c r="F45" t="s">
+        <v>290</v>
+      </c>
+      <c r="G45" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" t="s">
         <v>187</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="21">
-        <v>0.46875</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="21">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.8125</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0.375</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="21">
-        <v>0.6875</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="21">
-        <v>0.8125</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="D16" s="20" t="s">
+      <c r="D46" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="21">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="21">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="21">
-        <v>0.8125</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="21">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="21">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="21">
-        <v>0.375</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="21">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="21">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="21">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="21">
-        <v>0.71875</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="21">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="21">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="21">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="21">
-        <v>0.6875</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="21">
-        <v>0.80208333333333337</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="21">
-        <v>0.625</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="21">
+      <c r="E46" s="13">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F40" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="21">
-        <v>0.375</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="G42" s="20" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="21">
-        <v>0.8125</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="G44" s="20" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="21">
-        <v>0.65625</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="21">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" s="20" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -35475,7 +35472,7 @@
         <v>17</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F123" s="13">
         <v>0.65625</v>
@@ -35507,7 +35504,7 @@
         <v>18</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F124" s="13">
         <v>0.65625</v>
@@ -35539,7 +35536,7 @@
         <v>20</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F125" s="13">
         <v>0.65625</v>
@@ -35571,7 +35568,7 @@
         <v>73</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F126" s="13">
         <v>0.65625</v>
@@ -35603,7 +35600,7 @@
         <v>9</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F127" s="13">
         <v>0.69791666666666663</v>
@@ -35615,7 +35612,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I127" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J127" s="18" t="s">
         <v>167</v>
@@ -35635,7 +35632,7 @@
         <v>12</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F128" s="13">
         <v>0.69791666666666663</v>
@@ -35647,7 +35644,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I128" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J128" s="18" t="s">
         <v>167</v>
@@ -35667,7 +35664,7 @@
         <v>15</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F129" s="13">
         <v>0.69791666666666663</v>
@@ -35679,7 +35676,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I129" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J129" s="18" t="s">
         <v>167</v>
@@ -35699,7 +35696,7 @@
         <v>17</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F130" s="13">
         <v>0.69791666666666663</v>
@@ -35711,7 +35708,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I130" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J130" s="18" t="s">
         <v>167</v>
@@ -35731,7 +35728,7 @@
         <v>18</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F131" s="13">
         <v>0.69791666666666663</v>
@@ -35743,7 +35740,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I131" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J131" s="18" t="s">
         <v>167</v>
@@ -35763,7 +35760,7 @@
         <v>20</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F132" s="13">
         <v>0.69791666666666663</v>
@@ -35775,7 +35772,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I132" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J132" s="18" t="s">
         <v>167</v>
@@ -35795,7 +35792,7 @@
         <v>205</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F133" s="13">
         <v>0.69791666666666663</v>
@@ -35807,7 +35804,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I133" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J133" s="18" t="s">
         <v>167</v>
@@ -35827,7 +35824,7 @@
         <v>73</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F134" s="13">
         <v>0.69791666666666663</v>
@@ -35839,7 +35836,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I134" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J134" s="18" t="s">
         <v>167</v>
@@ -35859,7 +35856,7 @@
         <v>185</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F135" s="13">
         <v>0.69791666666666663</v>
@@ -35871,7 +35868,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I135" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J135" s="18" t="s">
         <v>167</v>
@@ -35891,7 +35888,7 @@
         <v>237</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F136" s="13">
         <v>0.69791666666666663</v>
@@ -35903,7 +35900,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I136" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J136" s="18" t="s">
         <v>167</v>
@@ -35923,7 +35920,7 @@
         <v>238</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F137" s="13">
         <v>0.69791666666666663</v>
@@ -35935,7 +35932,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I137" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J137" s="18" t="s">
         <v>167</v>
@@ -35955,7 +35952,7 @@
         <v>219</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F138" s="13">
         <v>0.75</v>
@@ -35967,7 +35964,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I138" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J138" s="18" t="s">
         <v>167</v>
@@ -35987,7 +35984,7 @@
         <v>225</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F139" s="13">
         <v>0.75</v>
@@ -35999,7 +35996,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I139" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J139" s="18" t="s">
         <v>167</v>
@@ -36019,7 +36016,7 @@
         <v>44</v>
       </c>
       <c r="E140" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F140" s="13">
         <v>0.75</v>
@@ -36031,7 +36028,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I140" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J140" s="18" t="s">
         <v>167</v>
@@ -36051,7 +36048,7 @@
         <v>229</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F141" s="13">
         <v>0.75</v>
@@ -36063,7 +36060,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I141" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J141" s="18" t="s">
         <v>167</v>
@@ -36083,7 +36080,7 @@
         <v>230</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F142" s="13">
         <v>0.75</v>
@@ -36095,7 +36092,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I142" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J142" s="18" t="s">
         <v>167</v>
@@ -36115,7 +36112,7 @@
         <v>231</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F143" s="13">
         <v>0.75</v>
@@ -36127,7 +36124,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I143" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J143" s="18" t="s">
         <v>167</v>
@@ -36147,7 +36144,7 @@
         <v>232</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F144" s="13">
         <v>0.75</v>
@@ -36159,7 +36156,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I144" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J144" s="18" t="s">
         <v>167</v>
@@ -36179,7 +36176,7 @@
         <v>233</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F145" s="13">
         <v>0.75</v>
@@ -36191,7 +36188,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I145" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J145" s="18" t="s">
         <v>167</v>
@@ -36211,7 +36208,7 @@
         <v>55</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F146" s="13">
         <v>0.75</v>
@@ -36223,7 +36220,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I146" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J146" s="18" t="s">
         <v>167</v>
@@ -36243,7 +36240,7 @@
         <v>59</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F147" s="13">
         <v>0.75</v>
@@ -36255,7 +36252,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I147" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J147" s="18" t="s">
         <v>167</v>
@@ -36275,7 +36272,7 @@
         <v>235</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F148" s="13">
         <v>0.75</v>
@@ -36287,7 +36284,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I148" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J148" s="18" t="s">
         <v>167</v>
@@ -36307,7 +36304,7 @@
         <v>236</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F149" s="13">
         <v>0.75</v>
@@ -36319,7 +36316,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I149" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J149" s="18" t="s">
         <v>167</v>
@@ -36339,7 +36336,7 @@
         <v>66</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F150" s="13">
         <v>0.75</v>
@@ -36351,7 +36348,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I150" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J150" s="18" t="s">
         <v>167</v>
@@ -36371,7 +36368,7 @@
         <v>71</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F151" s="13">
         <v>0.75</v>
@@ -36383,7 +36380,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I151" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J151" s="18" t="s">
         <v>167</v>
@@ -36403,7 +36400,7 @@
         <v>82</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F152" s="13">
         <v>0.75</v>
@@ -36415,7 +36412,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="I152" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J152" s="18" t="s">
         <v>167</v>
@@ -36435,7 +36432,7 @@
         <v>85</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F153" s="13">
         <v>0.75</v>
@@ -36447,7 +36444,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I153" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J153" s="18" t="s">
         <v>167</v>
@@ -36479,7 +36476,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I154" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J154" s="18" t="s">
         <v>167</v>
@@ -36511,7 +36508,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I155" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J155" s="18" t="s">
         <v>167</v>
@@ -36543,7 +36540,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I156" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J156" s="18" t="s">
         <v>167</v>
@@ -36575,7 +36572,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I157" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J157" s="18" t="s">
         <v>167</v>
@@ -36607,7 +36604,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I158" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J158" s="18" t="s">
         <v>167</v>
@@ -36639,7 +36636,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I159" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J159" s="18" t="s">
         <v>167</v>
@@ -36671,7 +36668,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I160" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J160" s="18" t="s">
         <v>167</v>
@@ -36703,7 +36700,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I161" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J161" s="18" t="s">
         <v>167</v>
@@ -36735,7 +36732,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I162" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J162" s="18" t="s">
         <v>167</v>
@@ -36767,7 +36764,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I163" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J163" s="18" t="s">
         <v>167</v>
@@ -36799,7 +36796,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I164" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J164" s="18" t="s">
         <v>167</v>
@@ -36831,7 +36828,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I165" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J165" s="18" t="s">
         <v>167</v>
@@ -36863,7 +36860,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I166" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J166" s="18" t="s">
         <v>167</v>
@@ -36895,7 +36892,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I167" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J167" s="18" t="s">
         <v>167</v>
@@ -36927,7 +36924,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I168" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J168" s="18" t="s">
         <v>167</v>
@@ -36959,7 +36956,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="I169" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J169" s="18" t="s">
         <v>167</v>
@@ -36991,7 +36988,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="I170" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J170" s="18" t="s">
         <v>167</v>
@@ -37023,7 +37020,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I171" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J171" s="18" t="s">
         <v>175</v>
@@ -37055,7 +37052,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I172" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J172" s="18" t="s">
         <v>175</v>
@@ -37087,7 +37084,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I173" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J173" s="18" t="s">
         <v>175</v>
@@ -37119,7 +37116,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I174" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J174" s="18" t="s">
         <v>175</v>
@@ -37151,7 +37148,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I175" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J175" s="18" t="s">
         <v>175</v>
@@ -37183,7 +37180,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I176" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J176" s="18" t="s">
         <v>175</v>
@@ -37215,7 +37212,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I177" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J177" s="18" t="s">
         <v>175</v>
@@ -37247,7 +37244,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I178" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J178" s="18" t="s">
         <v>175</v>
@@ -37279,7 +37276,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I179" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J179" s="18" t="s">
         <v>175</v>
@@ -37311,7 +37308,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I180" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J180" s="18" t="s">
         <v>175</v>
@@ -37343,7 +37340,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I181" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J181" s="18" t="s">
         <v>175</v>
@@ -37375,7 +37372,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I182" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J182" s="18" t="s">
         <v>175</v>
@@ -37407,7 +37404,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="I183" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J183" s="18" t="s">
         <v>175</v>
@@ -37439,7 +37436,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I184" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J184" s="18" t="s">
         <v>175</v>
@@ -37471,7 +37468,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="I185" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J185" s="18" t="s">
         <v>175</v>
@@ -37503,7 +37500,7 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="I186" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J186" s="18" t="s">
         <v>175</v>
@@ -37535,7 +37532,7 @@
         <v>0.71875</v>
       </c>
       <c r="I187" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J187" s="18" t="s">
         <v>175</v>
@@ -37567,7 +37564,7 @@
         <v>0.71875</v>
       </c>
       <c r="I188" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J188" s="18" t="s">
         <v>175</v>
@@ -37599,7 +37596,7 @@
         <v>0.71875</v>
       </c>
       <c r="I189" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J189" s="18" t="s">
         <v>175</v>
@@ -37631,7 +37628,7 @@
         <v>0.71875</v>
       </c>
       <c r="I190" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J190" s="18" t="s">
         <v>175</v>
@@ -37663,7 +37660,7 @@
         <v>0.71875</v>
       </c>
       <c r="I191" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J191" s="18" t="s">
         <v>175</v>
@@ -37695,7 +37692,7 @@
         <v>0.71875</v>
       </c>
       <c r="I192" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J192" s="18" t="s">
         <v>175</v>
@@ -37727,7 +37724,7 @@
         <v>0.71875</v>
       </c>
       <c r="I193" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J193" s="18" t="s">
         <v>175</v>
@@ -37759,7 +37756,7 @@
         <v>0.71875</v>
       </c>
       <c r="I194" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J194" s="18" t="s">
         <v>175</v>
@@ -37791,7 +37788,7 @@
         <v>0.71875</v>
       </c>
       <c r="I195" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J195" s="18" t="s">
         <v>175</v>
@@ -37823,7 +37820,7 @@
         <v>0.71875</v>
       </c>
       <c r="I196" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J196" s="18" t="s">
         <v>175</v>
@@ -37855,7 +37852,7 @@
         <v>0.71875</v>
       </c>
       <c r="I197" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J197" s="18" t="s">
         <v>175</v>
@@ -37887,7 +37884,7 @@
         <v>0.71875</v>
       </c>
       <c r="I198" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J198" s="18" t="s">
         <v>175</v>
@@ -37919,7 +37916,7 @@
         <v>0.71875</v>
       </c>
       <c r="I199" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J199" s="18" t="s">
         <v>175</v>
@@ -37951,7 +37948,7 @@
         <v>0.71875</v>
       </c>
       <c r="I200" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J200" s="18" t="s">
         <v>175</v>
@@ -37983,7 +37980,7 @@
         <v>0.71875</v>
       </c>
       <c r="I201" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J201" s="18" t="s">
         <v>175</v>
@@ -38335,7 +38332,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I212" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J212" s="18" t="s">
         <v>175</v>
@@ -38367,7 +38364,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I213" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J213" s="18" t="s">
         <v>175</v>
@@ -38399,7 +38396,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I214" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J214" s="18" t="s">
         <v>175</v>
@@ -38431,7 +38428,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I215" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J215" s="18" t="s">
         <v>175</v>
@@ -38463,7 +38460,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I216" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J216" s="18" t="s">
         <v>175</v>
@@ -38495,7 +38492,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I217" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J217" s="18" t="s">
         <v>175</v>
@@ -38527,7 +38524,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I218" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J218" s="18" t="s">
         <v>175</v>
@@ -38559,7 +38556,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I219" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J219" s="18" t="s">
         <v>175</v>
@@ -38591,7 +38588,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I220" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J220" s="18" t="s">
         <v>175</v>
@@ -38623,7 +38620,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I221" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J221" s="18" t="s">
         <v>175</v>
@@ -38655,7 +38652,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="I222" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J222" s="18" t="s">
         <v>175</v>
@@ -38687,7 +38684,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I223" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J223" s="18" t="s">
         <v>175</v>
@@ -38719,7 +38716,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I224" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J224" s="18" t="s">
         <v>175</v>
@@ -38751,7 +38748,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I225" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J225" s="18" t="s">
         <v>175</v>
@@ -38783,7 +38780,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I226" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J226" s="18" t="s">
         <v>175</v>
@@ -38815,7 +38812,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I227" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J227" s="18" t="s">
         <v>175</v>
@@ -38847,7 +38844,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I228" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J228" s="18" t="s">
         <v>175</v>
@@ -38879,7 +38876,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I229" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J229" s="18" t="s">
         <v>175</v>
@@ -38911,7 +38908,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I230" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J230" s="18" t="s">
         <v>175</v>
@@ -38943,7 +38940,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I231" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J231" s="18" t="s">
         <v>175</v>
@@ -38975,7 +38972,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I232" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J232" s="18" t="s">
         <v>175</v>
@@ -39007,7 +39004,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I233" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J233" s="18" t="s">
         <v>175</v>
@@ -39039,7 +39036,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I234" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J234" s="18" t="s">
         <v>175</v>
@@ -39071,7 +39068,7 @@
         <v>0.625</v>
       </c>
       <c r="I235" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J235" s="18" t="s">
         <v>175</v>
@@ -39103,7 +39100,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I236" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J236" s="18" t="s">
         <v>175</v>
@@ -39135,7 +39132,7 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="I237" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J237" s="18" t="s">
         <v>175</v>
@@ -39167,7 +39164,7 @@
         <v>0.625</v>
       </c>
       <c r="I238" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J238" s="18" t="s">
         <v>175</v>
@@ -39199,7 +39196,7 @@
         <v>0.5</v>
       </c>
       <c r="I239" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J239" s="18" t="s">
         <v>175</v>
@@ -39231,7 +39228,7 @@
         <v>0.5</v>
       </c>
       <c r="I240" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J240" s="18" t="s">
         <v>175</v>
@@ -39263,7 +39260,7 @@
         <v>0.5</v>
       </c>
       <c r="I241" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J241" s="18" t="s">
         <v>175</v>
@@ -39295,7 +39292,7 @@
         <v>0.5</v>
       </c>
       <c r="I242" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J242" s="18" t="s">
         <v>175</v>
@@ -39327,7 +39324,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I243" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J243" s="18" t="s">
         <v>175</v>
@@ -39359,7 +39356,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I244" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J244" s="18" t="s">
         <v>175</v>
@@ -39391,7 +39388,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I245" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J245" s="18" t="s">
         <v>175</v>
@@ -39423,7 +39420,7 @@
         <v>0.5</v>
       </c>
       <c r="I246" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J246" s="18" t="s">
         <v>175</v>
@@ -39455,7 +39452,7 @@
         <v>0.5</v>
       </c>
       <c r="I247" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J247" s="18" t="s">
         <v>175</v>
@@ -39487,7 +39484,7 @@
         <v>0.5</v>
       </c>
       <c r="I248" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J248" s="18" t="s">
         <v>175</v>
@@ -39519,7 +39516,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I249" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J249" s="18" t="s">
         <v>175</v>
@@ -39551,7 +39548,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I250" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J250" s="18" t="s">
         <v>175</v>
@@ -39583,7 +39580,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I251" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J251" s="18" t="s">
         <v>175</v>
@@ -39615,7 +39612,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I252" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J252" s="18" t="s">
         <v>175</v>
@@ -39647,7 +39644,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I253" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J253" s="18" t="s">
         <v>175</v>
@@ -39679,7 +39676,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I254" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J254" s="18" t="s">
         <v>175</v>
@@ -39711,7 +39708,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I255" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J255" s="18" t="s">
         <v>175</v>
@@ -39743,7 +39740,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I256" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J256" s="18" t="s">
         <v>175</v>
@@ -39775,7 +39772,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I257" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J257" s="18" t="s">
         <v>175</v>
@@ -39807,7 +39804,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I258" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J258" s="18" t="s">
         <v>175</v>
@@ -39839,7 +39836,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I259" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J259" s="18" t="s">
         <v>175</v>
@@ -39871,7 +39868,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I260" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J260" s="18" t="s">
         <v>175</v>
@@ -39903,7 +39900,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I261" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J261" s="18" t="s">
         <v>175</v>
@@ -39935,7 +39932,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I262" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J262" s="18" t="s">
         <v>175</v>
@@ -39967,7 +39964,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I263" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J263" s="18" t="s">
         <v>175</v>
@@ -39999,7 +39996,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I264" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J264" s="18" t="s">
         <v>175</v>
@@ -40031,7 +40028,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I265" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J265" s="18" t="s">
         <v>175</v>
@@ -40063,7 +40060,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I266" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J266" s="18" t="s">
         <v>175</v>
@@ -40095,7 +40092,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I267" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J267" s="18" t="s">
         <v>175</v>
@@ -40127,7 +40124,7 @@
         <v>0.55208333333333337</v>
       </c>
       <c r="I268" s="19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J268" s="18" t="s">
         <v>175</v>
